--- a/銀行債券_完整報表.xlsx
+++ b/銀行債券_完整報表.xlsx
@@ -9219,7 +9219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:BS12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9273,6 +9273,26 @@
     <col width="6" customWidth="1" min="49" max="49"/>
     <col width="6" customWidth="1" min="50" max="50"/>
     <col width="6" customWidth="1" min="51" max="51"/>
+    <col width="6" customWidth="1" min="52" max="52"/>
+    <col width="6" customWidth="1" min="53" max="53"/>
+    <col width="6" customWidth="1" min="54" max="54"/>
+    <col width="6" customWidth="1" min="55" max="55"/>
+    <col width="6" customWidth="1" min="56" max="56"/>
+    <col width="6" customWidth="1" min="57" max="57"/>
+    <col width="6" customWidth="1" min="58" max="58"/>
+    <col width="6" customWidth="1" min="59" max="59"/>
+    <col width="6" customWidth="1" min="60" max="60"/>
+    <col width="6" customWidth="1" min="61" max="61"/>
+    <col width="6" customWidth="1" min="62" max="62"/>
+    <col width="6" customWidth="1" min="63" max="63"/>
+    <col width="6" customWidth="1" min="64" max="64"/>
+    <col width="6" customWidth="1" min="65" max="65"/>
+    <col width="6" customWidth="1" min="66" max="66"/>
+    <col width="6" customWidth="1" min="67" max="67"/>
+    <col width="6" customWidth="1" min="68" max="68"/>
+    <col width="6" customWidth="1" min="69" max="69"/>
+    <col width="6" customWidth="1" min="70" max="70"/>
+    <col width="6" customWidth="1" min="71" max="71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9331,6 +9351,26 @@
           <t>2024H2</t>
         </is>
       </c>
+      <c r="AZ1" s="2" t="inlineStr">
+        <is>
+          <t>2025H1</t>
+        </is>
+      </c>
+      <c r="BE1" s="2" t="inlineStr">
+        <is>
+          <t>2025H2</t>
+        </is>
+      </c>
+      <c r="BJ1" s="2" t="inlineStr">
+        <is>
+          <t>2026H1</t>
+        </is>
+      </c>
+      <c r="BO1" s="2" t="inlineStr">
+        <is>
+          <t>2026H2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -9588,6 +9628,106 @@
           <t>玉山</t>
         </is>
       </c>
+      <c r="AZ2" s="2" t="inlineStr">
+        <is>
+          <t>中信</t>
+        </is>
+      </c>
+      <c r="BA2" s="2" t="inlineStr">
+        <is>
+          <t>兆豐</t>
+        </is>
+      </c>
+      <c r="BB2" s="2" t="inlineStr">
+        <is>
+          <t>國泰</t>
+        </is>
+      </c>
+      <c r="BC2" s="2" t="inlineStr">
+        <is>
+          <t>富邦</t>
+        </is>
+      </c>
+      <c r="BD2" s="2" t="inlineStr">
+        <is>
+          <t>玉山</t>
+        </is>
+      </c>
+      <c r="BE2" s="2" t="inlineStr">
+        <is>
+          <t>中信</t>
+        </is>
+      </c>
+      <c r="BF2" s="2" t="inlineStr">
+        <is>
+          <t>兆豐</t>
+        </is>
+      </c>
+      <c r="BG2" s="2" t="inlineStr">
+        <is>
+          <t>國泰</t>
+        </is>
+      </c>
+      <c r="BH2" s="2" t="inlineStr">
+        <is>
+          <t>富邦</t>
+        </is>
+      </c>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>玉山</t>
+        </is>
+      </c>
+      <c r="BJ2" s="2" t="inlineStr">
+        <is>
+          <t>中信</t>
+        </is>
+      </c>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>兆豐</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>國泰</t>
+        </is>
+      </c>
+      <c r="BM2" s="2" t="inlineStr">
+        <is>
+          <t>富邦</t>
+        </is>
+      </c>
+      <c r="BN2" s="2" t="inlineStr">
+        <is>
+          <t>玉山</t>
+        </is>
+      </c>
+      <c r="BO2" s="2" t="inlineStr">
+        <is>
+          <t>中信</t>
+        </is>
+      </c>
+      <c r="BP2" s="2" t="inlineStr">
+        <is>
+          <t>兆豐</t>
+        </is>
+      </c>
+      <c r="BQ2" s="2" t="inlineStr">
+        <is>
+          <t>國泰</t>
+        </is>
+      </c>
+      <c r="BR2" s="2" t="inlineStr">
+        <is>
+          <t>富邦</t>
+        </is>
+      </c>
+      <c r="BS2" s="2" t="inlineStr">
+        <is>
+          <t>玉山</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -9725,6 +9865,26 @@
       <c r="AY3" s="4" t="n">
         <v>1419</v>
       </c>
+      <c r="AZ3" s="4" t="inlineStr"/>
+      <c r="BA3" s="4" t="inlineStr"/>
+      <c r="BB3" s="4" t="inlineStr"/>
+      <c r="BC3" s="4" t="inlineStr"/>
+      <c r="BD3" s="4" t="inlineStr"/>
+      <c r="BE3" s="4" t="inlineStr"/>
+      <c r="BF3" s="4" t="inlineStr"/>
+      <c r="BG3" s="4" t="inlineStr"/>
+      <c r="BH3" s="4" t="inlineStr"/>
+      <c r="BI3" s="4" t="inlineStr"/>
+      <c r="BJ3" s="4" t="inlineStr"/>
+      <c r="BK3" s="4" t="inlineStr"/>
+      <c r="BL3" s="4" t="inlineStr"/>
+      <c r="BM3" s="4" t="inlineStr"/>
+      <c r="BN3" s="4" t="inlineStr"/>
+      <c r="BO3" s="4" t="inlineStr"/>
+      <c r="BP3" s="4" t="inlineStr"/>
+      <c r="BQ3" s="4" t="inlineStr"/>
+      <c r="BR3" s="4" t="inlineStr"/>
+      <c r="BS3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -9862,6 +10022,26 @@
       <c r="AY4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="AZ4" s="4" t="inlineStr"/>
+      <c r="BA4" s="4" t="inlineStr"/>
+      <c r="BB4" s="4" t="inlineStr"/>
+      <c r="BC4" s="4" t="inlineStr"/>
+      <c r="BD4" s="4" t="inlineStr"/>
+      <c r="BE4" s="4" t="inlineStr"/>
+      <c r="BF4" s="4" t="inlineStr"/>
+      <c r="BG4" s="4" t="inlineStr"/>
+      <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BI4" s="4" t="inlineStr"/>
+      <c r="BJ4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr"/>
+      <c r="BL4" s="4" t="inlineStr"/>
+      <c r="BM4" s="4" t="inlineStr"/>
+      <c r="BN4" s="4" t="inlineStr"/>
+      <c r="BO4" s="4" t="inlineStr"/>
+      <c r="BP4" s="4" t="inlineStr"/>
+      <c r="BQ4" s="4" t="inlineStr"/>
+      <c r="BR4" s="4" t="inlineStr"/>
+      <c r="BS4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -9999,6 +10179,26 @@
       <c r="AY5" s="4" t="n">
         <v>399</v>
       </c>
+      <c r="AZ5" s="4" t="inlineStr"/>
+      <c r="BA5" s="4" t="inlineStr"/>
+      <c r="BB5" s="4" t="inlineStr"/>
+      <c r="BC5" s="4" t="inlineStr"/>
+      <c r="BD5" s="4" t="inlineStr"/>
+      <c r="BE5" s="4" t="inlineStr"/>
+      <c r="BF5" s="4" t="inlineStr"/>
+      <c r="BG5" s="4" t="inlineStr"/>
+      <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr"/>
+      <c r="BL5" s="4" t="inlineStr"/>
+      <c r="BM5" s="4" t="inlineStr"/>
+      <c r="BN5" s="4" t="inlineStr"/>
+      <c r="BO5" s="4" t="inlineStr"/>
+      <c r="BP5" s="4" t="inlineStr"/>
+      <c r="BQ5" s="4" t="inlineStr"/>
+      <c r="BR5" s="4" t="inlineStr"/>
+      <c r="BS5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -10136,6 +10336,26 @@
       <c r="AY6" s="4" t="n">
         <v>386</v>
       </c>
+      <c r="AZ6" s="4" t="inlineStr"/>
+      <c r="BA6" s="4" t="inlineStr"/>
+      <c r="BB6" s="4" t="inlineStr"/>
+      <c r="BC6" s="4" t="inlineStr"/>
+      <c r="BD6" s="4" t="inlineStr"/>
+      <c r="BE6" s="4" t="inlineStr"/>
+      <c r="BF6" s="4" t="inlineStr"/>
+      <c r="BG6" s="4" t="inlineStr"/>
+      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr"/>
+      <c r="BL6" s="4" t="inlineStr"/>
+      <c r="BM6" s="4" t="inlineStr"/>
+      <c r="BN6" s="4" t="inlineStr"/>
+      <c r="BO6" s="4" t="inlineStr"/>
+      <c r="BP6" s="4" t="inlineStr"/>
+      <c r="BQ6" s="4" t="inlineStr"/>
+      <c r="BR6" s="4" t="inlineStr"/>
+      <c r="BS6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -10273,6 +10493,26 @@
       <c r="AY7" s="4" t="n">
         <v>420</v>
       </c>
+      <c r="AZ7" s="4" t="inlineStr"/>
+      <c r="BA7" s="4" t="inlineStr"/>
+      <c r="BB7" s="4" t="inlineStr"/>
+      <c r="BC7" s="4" t="inlineStr"/>
+      <c r="BD7" s="4" t="inlineStr"/>
+      <c r="BE7" s="4" t="inlineStr"/>
+      <c r="BF7" s="4" t="inlineStr"/>
+      <c r="BG7" s="4" t="inlineStr"/>
+      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI7" s="4" t="inlineStr"/>
+      <c r="BJ7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr"/>
+      <c r="BL7" s="4" t="inlineStr"/>
+      <c r="BM7" s="4" t="inlineStr"/>
+      <c r="BN7" s="4" t="inlineStr"/>
+      <c r="BO7" s="4" t="inlineStr"/>
+      <c r="BP7" s="4" t="inlineStr"/>
+      <c r="BQ7" s="4" t="inlineStr"/>
+      <c r="BR7" s="4" t="inlineStr"/>
+      <c r="BS7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -10410,6 +10650,26 @@
       <c r="AY8" s="4" t="n">
         <v>1115</v>
       </c>
+      <c r="AZ8" s="4" t="inlineStr"/>
+      <c r="BA8" s="4" t="inlineStr"/>
+      <c r="BB8" s="4" t="inlineStr"/>
+      <c r="BC8" s="4" t="inlineStr"/>
+      <c r="BD8" s="4" t="inlineStr"/>
+      <c r="BE8" s="4" t="inlineStr"/>
+      <c r="BF8" s="4" t="inlineStr"/>
+      <c r="BG8" s="4" t="inlineStr"/>
+      <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr"/>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr"/>
+      <c r="BL8" s="4" t="inlineStr"/>
+      <c r="BM8" s="4" t="inlineStr"/>
+      <c r="BN8" s="4" t="inlineStr"/>
+      <c r="BO8" s="4" t="inlineStr"/>
+      <c r="BP8" s="4" t="inlineStr"/>
+      <c r="BQ8" s="4" t="inlineStr"/>
+      <c r="BR8" s="4" t="inlineStr"/>
+      <c r="BS8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -10547,6 +10807,26 @@
       <c r="AY9" s="4" t="n">
         <v>1336</v>
       </c>
+      <c r="AZ9" s="4" t="inlineStr"/>
+      <c r="BA9" s="4" t="inlineStr"/>
+      <c r="BB9" s="4" t="inlineStr"/>
+      <c r="BC9" s="4" t="inlineStr"/>
+      <c r="BD9" s="4" t="inlineStr"/>
+      <c r="BE9" s="4" t="inlineStr"/>
+      <c r="BF9" s="4" t="inlineStr"/>
+      <c r="BG9" s="4" t="inlineStr"/>
+      <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BI9" s="4" t="inlineStr"/>
+      <c r="BJ9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr"/>
+      <c r="BL9" s="4" t="inlineStr"/>
+      <c r="BM9" s="4" t="inlineStr"/>
+      <c r="BN9" s="4" t="inlineStr"/>
+      <c r="BO9" s="4" t="inlineStr"/>
+      <c r="BP9" s="4" t="inlineStr"/>
+      <c r="BQ9" s="4" t="inlineStr"/>
+      <c r="BR9" s="4" t="inlineStr"/>
+      <c r="BS9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -10684,6 +10964,26 @@
       <c r="AY10" s="4" t="n">
         <v>239</v>
       </c>
+      <c r="AZ10" s="4" t="inlineStr"/>
+      <c r="BA10" s="4" t="inlineStr"/>
+      <c r="BB10" s="4" t="inlineStr"/>
+      <c r="BC10" s="4" t="inlineStr"/>
+      <c r="BD10" s="4" t="inlineStr"/>
+      <c r="BE10" s="4" t="inlineStr"/>
+      <c r="BF10" s="4" t="inlineStr"/>
+      <c r="BG10" s="4" t="inlineStr"/>
+      <c r="BH10" s="4" t="inlineStr"/>
+      <c r="BI10" s="4" t="inlineStr"/>
+      <c r="BJ10" s="4" t="inlineStr"/>
+      <c r="BK10" s="4" t="inlineStr"/>
+      <c r="BL10" s="4" t="inlineStr"/>
+      <c r="BM10" s="4" t="inlineStr"/>
+      <c r="BN10" s="4" t="inlineStr"/>
+      <c r="BO10" s="4" t="inlineStr"/>
+      <c r="BP10" s="4" t="inlineStr"/>
+      <c r="BQ10" s="4" t="inlineStr"/>
+      <c r="BR10" s="4" t="inlineStr"/>
+      <c r="BS10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -10821,6 +11121,26 @@
       <c r="AY11" s="4" t="n">
         <v>257</v>
       </c>
+      <c r="AZ11" s="4" t="inlineStr"/>
+      <c r="BA11" s="4" t="inlineStr"/>
+      <c r="BB11" s="4" t="inlineStr"/>
+      <c r="BC11" s="4" t="inlineStr"/>
+      <c r="BD11" s="4" t="inlineStr"/>
+      <c r="BE11" s="4" t="inlineStr"/>
+      <c r="BF11" s="4" t="inlineStr"/>
+      <c r="BG11" s="4" t="inlineStr"/>
+      <c r="BH11" s="4" t="inlineStr"/>
+      <c r="BI11" s="4" t="inlineStr"/>
+      <c r="BJ11" s="4" t="inlineStr"/>
+      <c r="BK11" s="4" t="inlineStr"/>
+      <c r="BL11" s="4" t="inlineStr"/>
+      <c r="BM11" s="4" t="inlineStr"/>
+      <c r="BN11" s="4" t="inlineStr"/>
+      <c r="BO11" s="4" t="inlineStr"/>
+      <c r="BP11" s="4" t="inlineStr"/>
+      <c r="BQ11" s="4" t="inlineStr"/>
+      <c r="BR11" s="4" t="inlineStr"/>
+      <c r="BS11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -10958,9 +11278,29 @@
       <c r="AY12" s="4" t="n">
         <v>670</v>
       </c>
+      <c r="AZ12" s="4" t="inlineStr"/>
+      <c r="BA12" s="4" t="inlineStr"/>
+      <c r="BB12" s="4" t="inlineStr"/>
+      <c r="BC12" s="4" t="inlineStr"/>
+      <c r="BD12" s="4" t="inlineStr"/>
+      <c r="BE12" s="4" t="inlineStr"/>
+      <c r="BF12" s="4" t="inlineStr"/>
+      <c r="BG12" s="4" t="inlineStr"/>
+      <c r="BH12" s="4" t="inlineStr"/>
+      <c r="BI12" s="4" t="inlineStr"/>
+      <c r="BJ12" s="4" t="inlineStr"/>
+      <c r="BK12" s="4" t="inlineStr"/>
+      <c r="BL12" s="4" t="inlineStr"/>
+      <c r="BM12" s="4" t="inlineStr"/>
+      <c r="BN12" s="4" t="inlineStr"/>
+      <c r="BO12" s="4" t="inlineStr"/>
+      <c r="BP12" s="4" t="inlineStr"/>
+      <c r="BQ12" s="4" t="inlineStr"/>
+      <c r="BR12" s="4" t="inlineStr"/>
+      <c r="BS12" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="14">
     <mergeCell ref="V1:Z1"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="AF1:AJ1"/>
@@ -10968,9 +11308,13 @@
     <mergeCell ref="AA1:AE1"/>
     <mergeCell ref="G1:K1"/>
     <mergeCell ref="AK1:AO1"/>
+    <mergeCell ref="AZ1:BD1"/>
+    <mergeCell ref="BE1:BI1"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="AP1:AT1"/>
+    <mergeCell ref="BJ1:BN1"/>
     <mergeCell ref="AU1:AY1"/>
+    <mergeCell ref="BO1:BS1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/銀行債券_完整報表.xlsx
+++ b/銀行債券_完整報表.xlsx
@@ -9865,16 +9865,32 @@
       <c r="AY3" s="4" t="n">
         <v>1419</v>
       </c>
-      <c r="AZ3" s="4" t="inlineStr"/>
+      <c r="AZ3" s="4" t="n">
+        <v>1853</v>
+      </c>
       <c r="BA3" s="4" t="inlineStr"/>
-      <c r="BB3" s="4" t="inlineStr"/>
-      <c r="BC3" s="4" t="inlineStr"/>
-      <c r="BD3" s="4" t="inlineStr"/>
-      <c r="BE3" s="4" t="inlineStr"/>
+      <c r="BB3" s="4" t="n">
+        <v>1356</v>
+      </c>
+      <c r="BC3" s="4" t="n">
+        <v>1354</v>
+      </c>
+      <c r="BD3" s="4" t="n">
+        <v>1506</v>
+      </c>
+      <c r="BE3" s="4" t="n">
+        <v>2118</v>
+      </c>
       <c r="BF3" s="4" t="inlineStr"/>
-      <c r="BG3" s="4" t="inlineStr"/>
-      <c r="BH3" s="4" t="inlineStr"/>
-      <c r="BI3" s="4" t="inlineStr"/>
+      <c r="BG3" s="4" t="n">
+        <v>2095</v>
+      </c>
+      <c r="BH3" s="4" t="n">
+        <v>1164</v>
+      </c>
+      <c r="BI3" s="4" t="n">
+        <v>1719</v>
+      </c>
       <c r="BJ3" s="4" t="inlineStr"/>
       <c r="BK3" s="4" t="inlineStr"/>
       <c r="BL3" s="4" t="inlineStr"/>
@@ -10022,16 +10038,32 @@
       <c r="AY4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AZ4" s="4" t="inlineStr"/>
+      <c r="AZ4" s="4" t="n">
+        <v>51</v>
+      </c>
       <c r="BA4" s="4" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr"/>
-      <c r="BC4" s="4" t="inlineStr"/>
-      <c r="BD4" s="4" t="inlineStr"/>
-      <c r="BE4" s="4" t="inlineStr"/>
+      <c r="BB4" s="4" t="n">
+        <v>146</v>
+      </c>
+      <c r="BC4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" s="4" t="n">
+        <v>14</v>
+      </c>
       <c r="BF4" s="4" t="inlineStr"/>
-      <c r="BG4" s="4" t="inlineStr"/>
-      <c r="BH4" s="4" t="inlineStr"/>
-      <c r="BI4" s="4" t="inlineStr"/>
+      <c r="BG4" s="4" t="n">
+        <v>231</v>
+      </c>
+      <c r="BH4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="BJ4" s="4" t="inlineStr"/>
       <c r="BK4" s="4" t="inlineStr"/>
       <c r="BL4" s="4" t="inlineStr"/>
@@ -10179,16 +10211,32 @@
       <c r="AY5" s="4" t="n">
         <v>399</v>
       </c>
-      <c r="AZ5" s="4" t="inlineStr"/>
+      <c r="AZ5" s="4" t="n">
+        <v>90</v>
+      </c>
       <c r="BA5" s="4" t="inlineStr"/>
-      <c r="BB5" s="4" t="inlineStr"/>
-      <c r="BC5" s="4" t="inlineStr"/>
-      <c r="BD5" s="4" t="inlineStr"/>
-      <c r="BE5" s="4" t="inlineStr"/>
+      <c r="BB5" s="4" t="n">
+        <v>259</v>
+      </c>
+      <c r="BC5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" s="4" t="n">
+        <v>335</v>
+      </c>
+      <c r="BE5" s="4" t="n">
+        <v>125</v>
+      </c>
       <c r="BF5" s="4" t="inlineStr"/>
-      <c r="BG5" s="4" t="inlineStr"/>
-      <c r="BH5" s="4" t="inlineStr"/>
-      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BG5" s="4" t="n">
+        <v>306</v>
+      </c>
+      <c r="BH5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" s="4" t="n">
+        <v>297</v>
+      </c>
       <c r="BJ5" s="4" t="inlineStr"/>
       <c r="BK5" s="4" t="inlineStr"/>
       <c r="BL5" s="4" t="inlineStr"/>
@@ -10336,16 +10384,32 @@
       <c r="AY6" s="4" t="n">
         <v>386</v>
       </c>
-      <c r="AZ6" s="4" t="inlineStr"/>
+      <c r="AZ6" s="4" t="n">
+        <v>55</v>
+      </c>
       <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr"/>
-      <c r="BC6" s="4" t="inlineStr"/>
-      <c r="BD6" s="4" t="inlineStr"/>
-      <c r="BE6" s="4" t="inlineStr"/>
+      <c r="BB6" s="4" t="n">
+        <v>356</v>
+      </c>
+      <c r="BC6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" s="4" t="n">
+        <v>328</v>
+      </c>
+      <c r="BE6" s="4" t="n">
+        <v>19</v>
+      </c>
       <c r="BF6" s="4" t="inlineStr"/>
-      <c r="BG6" s="4" t="inlineStr"/>
-      <c r="BH6" s="4" t="inlineStr"/>
-      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BG6" s="4" t="n">
+        <v>452</v>
+      </c>
+      <c r="BH6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" s="4" t="n">
+        <v>308</v>
+      </c>
       <c r="BJ6" s="4" t="inlineStr"/>
       <c r="BK6" s="4" t="inlineStr"/>
       <c r="BL6" s="4" t="inlineStr"/>
@@ -10493,16 +10557,32 @@
       <c r="AY7" s="4" t="n">
         <v>420</v>
       </c>
-      <c r="AZ7" s="4" t="inlineStr"/>
+      <c r="AZ7" s="4" t="n">
+        <v>1341</v>
+      </c>
       <c r="BA7" s="4" t="inlineStr"/>
-      <c r="BB7" s="4" t="inlineStr"/>
-      <c r="BC7" s="4" t="inlineStr"/>
-      <c r="BD7" s="4" t="inlineStr"/>
-      <c r="BE7" s="4" t="inlineStr"/>
+      <c r="BB7" s="4" t="n">
+        <v>1564</v>
+      </c>
+      <c r="BC7" s="4" t="n">
+        <v>599</v>
+      </c>
+      <c r="BD7" s="4" t="n">
+        <v>316</v>
+      </c>
+      <c r="BE7" s="4" t="n">
+        <v>1464</v>
+      </c>
       <c r="BF7" s="4" t="inlineStr"/>
-      <c r="BG7" s="4" t="inlineStr"/>
-      <c r="BH7" s="4" t="inlineStr"/>
-      <c r="BI7" s="4" t="inlineStr"/>
+      <c r="BG7" s="4" t="n">
+        <v>1668</v>
+      </c>
+      <c r="BH7" s="4" t="n">
+        <v>777</v>
+      </c>
+      <c r="BI7" s="4" t="n">
+        <v>292</v>
+      </c>
       <c r="BJ7" s="4" t="inlineStr"/>
       <c r="BK7" s="4" t="inlineStr"/>
       <c r="BL7" s="4" t="inlineStr"/>
@@ -10650,16 +10730,32 @@
       <c r="AY8" s="4" t="n">
         <v>1115</v>
       </c>
-      <c r="AZ8" s="4" t="inlineStr"/>
+      <c r="AZ8" s="4" t="n">
+        <v>104</v>
+      </c>
       <c r="BA8" s="4" t="inlineStr"/>
-      <c r="BB8" s="4" t="inlineStr"/>
-      <c r="BC8" s="4" t="inlineStr"/>
-      <c r="BD8" s="4" t="inlineStr"/>
-      <c r="BE8" s="4" t="inlineStr"/>
+      <c r="BB8" s="4" t="n">
+        <v>962</v>
+      </c>
+      <c r="BC8" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="BD8" s="4" t="n">
+        <v>1133</v>
+      </c>
+      <c r="BE8" s="4" t="n">
+        <v>103</v>
+      </c>
       <c r="BF8" s="4" t="inlineStr"/>
-      <c r="BG8" s="4" t="inlineStr"/>
-      <c r="BH8" s="4" t="inlineStr"/>
-      <c r="BI8" s="4" t="inlineStr"/>
+      <c r="BG8" s="4" t="n">
+        <v>958</v>
+      </c>
+      <c r="BH8" s="4" t="n">
+        <v>501</v>
+      </c>
+      <c r="BI8" s="4" t="n">
+        <v>1234</v>
+      </c>
       <c r="BJ8" s="4" t="inlineStr"/>
       <c r="BK8" s="4" t="inlineStr"/>
       <c r="BL8" s="4" t="inlineStr"/>
@@ -10807,16 +10903,32 @@
       <c r="AY9" s="4" t="n">
         <v>1336</v>
       </c>
-      <c r="AZ9" s="4" t="inlineStr"/>
+      <c r="AZ9" s="4" t="n">
+        <v>570</v>
+      </c>
       <c r="BA9" s="4" t="inlineStr"/>
-      <c r="BB9" s="4" t="inlineStr"/>
-      <c r="BC9" s="4" t="inlineStr"/>
-      <c r="BD9" s="4" t="inlineStr"/>
-      <c r="BE9" s="4" t="inlineStr"/>
+      <c r="BB9" s="4" t="n">
+        <v>215</v>
+      </c>
+      <c r="BC9" s="4" t="n">
+        <v>394</v>
+      </c>
+      <c r="BD9" s="4" t="n">
+        <v>1207</v>
+      </c>
+      <c r="BE9" s="4" t="n">
+        <v>633</v>
+      </c>
       <c r="BF9" s="4" t="inlineStr"/>
-      <c r="BG9" s="4" t="inlineStr"/>
-      <c r="BH9" s="4" t="inlineStr"/>
-      <c r="BI9" s="4" t="inlineStr"/>
+      <c r="BG9" s="4" t="n">
+        <v>165</v>
+      </c>
+      <c r="BH9" s="4" t="n">
+        <v>401</v>
+      </c>
+      <c r="BI9" s="4" t="n">
+        <v>1315</v>
+      </c>
       <c r="BJ9" s="4" t="inlineStr"/>
       <c r="BK9" s="4" t="inlineStr"/>
       <c r="BL9" s="4" t="inlineStr"/>
@@ -10964,16 +11076,32 @@
       <c r="AY10" s="4" t="n">
         <v>239</v>
       </c>
-      <c r="AZ10" s="4" t="inlineStr"/>
+      <c r="AZ10" s="4" t="n">
+        <v>2438</v>
+      </c>
       <c r="BA10" s="4" t="inlineStr"/>
-      <c r="BB10" s="4" t="inlineStr"/>
-      <c r="BC10" s="4" t="inlineStr"/>
-      <c r="BD10" s="4" t="inlineStr"/>
-      <c r="BE10" s="4" t="inlineStr"/>
+      <c r="BB10" s="4" t="n">
+        <v>446</v>
+      </c>
+      <c r="BC10" s="4" t="n">
+        <v>797</v>
+      </c>
+      <c r="BD10" s="4" t="n">
+        <v>238</v>
+      </c>
+      <c r="BE10" s="4" t="n">
+        <v>2341</v>
+      </c>
       <c r="BF10" s="4" t="inlineStr"/>
-      <c r="BG10" s="4" t="inlineStr"/>
-      <c r="BH10" s="4" t="inlineStr"/>
-      <c r="BI10" s="4" t="inlineStr"/>
+      <c r="BG10" s="4" t="n">
+        <v>427</v>
+      </c>
+      <c r="BH10" s="4" t="n">
+        <v>808</v>
+      </c>
+      <c r="BI10" s="4" t="n">
+        <v>238</v>
+      </c>
       <c r="BJ10" s="4" t="inlineStr"/>
       <c r="BK10" s="4" t="inlineStr"/>
       <c r="BL10" s="4" t="inlineStr"/>
@@ -11121,16 +11249,32 @@
       <c r="AY11" s="4" t="n">
         <v>257</v>
       </c>
-      <c r="AZ11" s="4" t="inlineStr"/>
+      <c r="AZ11" s="4" t="n">
+        <v>1047</v>
+      </c>
       <c r="BA11" s="4" t="inlineStr"/>
-      <c r="BB11" s="4" t="inlineStr"/>
-      <c r="BC11" s="4" t="inlineStr"/>
-      <c r="BD11" s="4" t="inlineStr"/>
-      <c r="BE11" s="4" t="inlineStr"/>
+      <c r="BB11" s="4" t="n">
+        <v>263</v>
+      </c>
+      <c r="BC11" s="4" t="n">
+        <v>2041</v>
+      </c>
+      <c r="BD11" s="4" t="n">
+        <v>232</v>
+      </c>
+      <c r="BE11" s="4" t="n">
+        <v>1308</v>
+      </c>
       <c r="BF11" s="4" t="inlineStr"/>
-      <c r="BG11" s="4" t="inlineStr"/>
-      <c r="BH11" s="4" t="inlineStr"/>
-      <c r="BI11" s="4" t="inlineStr"/>
+      <c r="BG11" s="4" t="n">
+        <v>277</v>
+      </c>
+      <c r="BH11" s="4" t="n">
+        <v>2096</v>
+      </c>
+      <c r="BI11" s="4" t="n">
+        <v>252</v>
+      </c>
       <c r="BJ11" s="4" t="inlineStr"/>
       <c r="BK11" s="4" t="inlineStr"/>
       <c r="BL11" s="4" t="inlineStr"/>
@@ -11278,16 +11422,32 @@
       <c r="AY12" s="4" t="n">
         <v>670</v>
       </c>
-      <c r="AZ12" s="4" t="inlineStr"/>
+      <c r="AZ12" s="4" t="n">
+        <v>626</v>
+      </c>
       <c r="BA12" s="4" t="inlineStr"/>
-      <c r="BB12" s="4" t="inlineStr"/>
-      <c r="BC12" s="4" t="inlineStr"/>
-      <c r="BD12" s="4" t="inlineStr"/>
-      <c r="BE12" s="4" t="inlineStr"/>
+      <c r="BB12" s="4" t="n">
+        <v>666</v>
+      </c>
+      <c r="BC12" s="4" t="n">
+        <v>1791</v>
+      </c>
+      <c r="BD12" s="4" t="n">
+        <v>664</v>
+      </c>
+      <c r="BE12" s="4" t="n">
+        <v>602</v>
+      </c>
       <c r="BF12" s="4" t="inlineStr"/>
-      <c r="BG12" s="4" t="inlineStr"/>
-      <c r="BH12" s="4" t="inlineStr"/>
-      <c r="BI12" s="4" t="inlineStr"/>
+      <c r="BG12" s="4" t="n">
+        <v>553</v>
+      </c>
+      <c r="BH12" s="4" t="n">
+        <v>2154</v>
+      </c>
+      <c r="BI12" s="4" t="n">
+        <v>698</v>
+      </c>
       <c r="BJ12" s="4" t="inlineStr"/>
       <c r="BK12" s="4" t="inlineStr"/>
       <c r="BL12" s="4" t="inlineStr"/>
@@ -11347,32 +11507,32 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2022H1</t>
+          <t>2023H1</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>2022H2</t>
+          <t>2023H2</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>2023H1</t>
+          <t>2024H1</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>2023H2</t>
+          <t>2024H2</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>2024H1</t>
+          <t>2025H1</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>2024H2</t>
+          <t>2025H2</t>
         </is>
       </c>
     </row>
@@ -11383,22 +11543,22 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>10800.4</v>
+        <v>10738.6</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>11060.6</v>
+        <v>10656.3</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>10738.6</v>
+        <v>10729.3</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>10656.3</v>
+        <v>12964.4</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>10729.3</v>
+        <v>12320.8</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>12964.4</v>
+        <v>12299.2</v>
       </c>
     </row>
     <row r="4">
@@ -11421,22 +11581,22 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>5593.7</v>
+        <v>6962.2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>6811.4</v>
+        <v>5886.7</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>6962.2</v>
+        <v>6034.1</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>5886.7</v>
+        <v>6020.3</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>6034.1</v>
+        <v>6095.9</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>6020.3</v>
+        <v>6458.6</v>
       </c>
     </row>
     <row r="6">
@@ -11446,22 +11606,22 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>8935.6</v>
+        <v>9435.9</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>8023.7</v>
+        <v>8824.200000000001</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>9435.9</v>
+        <v>8666.4</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>8824.200000000001</v>
+        <v>9103</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>8666.4</v>
+        <v>8981</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>9103</v>
+        <v>9830</v>
       </c>
     </row>
     <row r="7">
@@ -11471,22 +11631,22 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>8937.6</v>
+        <v>9136.1</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>9106.299999999999</v>
+        <v>8873.4</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>9136.1</v>
+        <v>8785.1</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>8873.4</v>
+        <v>8833.700000000001</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>8785.1</v>
+        <v>8371</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>8833.700000000001</v>
+        <v>8299.6</v>
       </c>
     </row>
     <row r="10">
@@ -11504,32 +11664,32 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2022H1</t>
+          <t>2023H1</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>2022H2</t>
+          <t>2023H2</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>2023H1</t>
+          <t>2024H1</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>2023H2</t>
+          <t>2024H2</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2024H1</t>
+          <t>2025H1</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>2024H2</t>
+          <t>2025H2</t>
         </is>
       </c>
     </row>
@@ -11540,22 +11700,22 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>39.7</v>
+        <v>228.8</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>111.3</v>
+        <v>600</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>228.8</v>
+        <v>518.3</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>600</v>
+        <v>1038.9</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>518.3</v>
+        <v>369.9</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>1038.9</v>
+        <v>307.1</v>
       </c>
     </row>
     <row r="13">
@@ -11578,22 +11738,22 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>768</v>
+        <v>1249.2</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>607</v>
+        <v>1000.7</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1249.2</v>
+        <v>691.5</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1000.7</v>
+        <v>579.6</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>691.5</v>
+        <v>926</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>579.6</v>
+        <v>1033.5</v>
       </c>
     </row>
     <row r="15">
@@ -11603,22 +11763,22 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>224.4</v>
+        <v>281.7</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>215.3</v>
+        <v>210.7</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>281.7</v>
+        <v>306.8</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>210.7</v>
+        <v>163.8</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>306.8</v>
+        <v>356.9</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>163.8</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16">
@@ -11628,22 +11788,22 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>2366.2</v>
+        <v>1450.7</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>1989.8</v>
+        <v>974.7</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>1450.7</v>
+        <v>1075.5</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>974.7</v>
+        <v>946.3</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>1075.5</v>
+        <v>1034.6</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>946.3</v>
+        <v>815.3</v>
       </c>
     </row>
     <row r="19">
@@ -11661,32 +11821,32 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>2022H1</t>
+          <t>2023H1</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>2022H2</t>
+          <t>2023H2</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>2023H1</t>
+          <t>2024H1</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>2023H2</t>
+          <t>2024H2</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2024H1</t>
+          <t>2025H1</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2024H2</t>
+          <t>2025H2</t>
         </is>
       </c>
     </row>
@@ -11697,22 +11857,22 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>1647.6</v>
+        <v>2041.4</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>1526.8</v>
+        <v>1962.2</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2041.4</v>
+        <v>1941.3</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>1962.2</v>
+        <v>2417.4</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1941.3</v>
+        <v>2764.8</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>2417.4</v>
+        <v>3124.3</v>
       </c>
     </row>
     <row r="22">
@@ -11735,22 +11895,22 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>3151.5</v>
+        <v>3743.8</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>4320.8</v>
+        <v>2421</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3743.8</v>
+        <v>2810.3</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>2421</v>
+        <v>3010</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>2810.3</v>
+        <v>3061.7</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>3010</v>
+        <v>3101.7</v>
       </c>
     </row>
     <row r="24">
@@ -11760,22 +11920,22 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>965.7</v>
+        <v>1179.5</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>70.90000000000001</v>
+        <v>1361</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>1179.5</v>
+        <v>1371.6</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>1361</v>
+        <v>1562.5</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>1371.6</v>
+        <v>1500.3</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>1562.5</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="25">
@@ -11785,22 +11945,22 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>3070.1</v>
+        <v>3276.8</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>3137.6</v>
+        <v>3160.9</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>3276.8</v>
+        <v>3355.2</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>3160.9</v>
+        <v>3239.1</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>3355.2</v>
+        <v>2906</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>3239.1</v>
+        <v>3067.6</v>
       </c>
     </row>
     <row r="28">
@@ -11818,32 +11978,32 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2022H1</t>
+          <t>2023H1</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>2022H2</t>
+          <t>2023H2</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>2023H1</t>
+          <t>2024H1</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>2023H2</t>
+          <t>2024H2</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2024H1</t>
+          <t>2025H1</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>2024H2</t>
+          <t>2025H2</t>
         </is>
       </c>
     </row>
@@ -11854,22 +12014,22 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>9113</v>
+        <v>8468.299999999999</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>9422.5</v>
+        <v>8094.1</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>8468.299999999999</v>
+        <v>8269.799999999999</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>8094.1</v>
+        <v>9508.200000000001</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>8269.799999999999</v>
+        <v>9186</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>9508.200000000001</v>
+        <v>8867.799999999999</v>
       </c>
     </row>
     <row r="31">
@@ -11892,22 +12052,22 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>1674.3</v>
+        <v>1969.2</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>1883.6</v>
+        <v>2465</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1969.2</v>
+        <v>2532.2</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>2465</v>
+        <v>2430.7</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>2532.2</v>
+        <v>2108.2</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>2430.7</v>
+        <v>2323.4</v>
       </c>
     </row>
     <row r="33">
@@ -11917,22 +12077,22 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>7745.6</v>
+        <v>7974.8</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>7737.6</v>
+        <v>7252.5</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>7974.8</v>
+        <v>6987.9</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>7252.5</v>
+        <v>7376.7</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>6987.9</v>
+        <v>7123.9</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>7376.7</v>
+        <v>7904.1</v>
       </c>
     </row>
     <row r="34">
@@ -11942,22 +12102,22 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>3501.3</v>
+        <v>4408.5</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>3979</v>
+        <v>4737.8</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>4408.5</v>
+        <v>4354.4</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>4737.8</v>
+        <v>4648.4</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>4354.4</v>
+        <v>4430.4</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>4648.4</v>
+        <v>4416.7</v>
       </c>
     </row>
     <row r="37">
@@ -11975,32 +12135,32 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>2022H1</t>
+          <t>2023H1</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>2022H2</t>
+          <t>2023H2</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>2023H1</t>
+          <t>2024H1</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>2023H2</t>
+          <t>2024H2</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2024H1</t>
+          <t>2025H1</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>2024H2</t>
+          <t>2025H2</t>
         </is>
       </c>
     </row>
@@ -12011,22 +12171,22 @@
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>0.0037</v>
+        <v>0.0213</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>0.0101</v>
+        <v>0.0563</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>0.0213</v>
+        <v>0.0483</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>0.0563</v>
+        <v>0.0801</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>0.0483</v>
+        <v>0.03</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>0.0801</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="40">
@@ -12049,22 +12209,22 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.1373</v>
+        <v>0.1794</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>0.0891</v>
+        <v>0.17</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0.1794</v>
+        <v>0.1146</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>0.17</v>
+        <v>0.0963</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>0.1146</v>
+        <v>0.1519</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>0.0963</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="42">
@@ -12074,22 +12234,22 @@
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>0.0251</v>
+        <v>0.0299</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>0.0268</v>
+        <v>0.0239</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>0.0299</v>
+        <v>0.0354</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>0.0239</v>
+        <v>0.018</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>0.0354</v>
+        <v>0.0397</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>0.018</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="43">
@@ -12099,22 +12259,22 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>0.2648</v>
+        <v>0.1588</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>0.2185</v>
+        <v>0.1098</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0.1588</v>
+        <v>0.1224</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>0.1098</v>
+        <v>0.1071</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>0.1224</v>
+        <v>0.1236</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>0.1071</v>
+        <v>0.0982</v>
       </c>
     </row>
     <row r="46">
@@ -12132,32 +12292,32 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2022H1</t>
+          <t>2023H1</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>2022H2</t>
+          <t>2023H2</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>2023H1</t>
+          <t>2024H1</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>2023H2</t>
+          <t>2024H2</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2024H1</t>
+          <t>2025H1</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>2024H2</t>
+          <t>2025H2</t>
         </is>
       </c>
     </row>
@@ -12168,22 +12328,22 @@
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>0.1526</v>
+        <v>0.1901</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>0.138</v>
+        <v>0.1841</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>0.1901</v>
+        <v>0.1809</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>0.1841</v>
+        <v>0.1865</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0.1809</v>
+        <v>0.2244</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>0.1865</v>
+        <v>0.254</v>
       </c>
     </row>
     <row r="49">
@@ -12206,22 +12366,22 @@
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>0.5634</v>
+        <v>0.5377</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>0.6344</v>
+        <v>0.4113</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0.5377</v>
+        <v>0.4657</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>0.4113</v>
+        <v>0.5</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>0.4657</v>
+        <v>0.5022</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>0.5</v>
+        <v>0.4802</v>
       </c>
     </row>
     <row r="51">
@@ -12231,22 +12391,22 @@
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>0.1081</v>
+        <v>0.125</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.1542</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0.125</v>
+        <v>0.1583</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>0.1542</v>
+        <v>0.1716</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>0.1583</v>
+        <v>0.1671</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>0.1716</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="52">
@@ -12256,22 +12416,22 @@
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>0.3435</v>
+        <v>0.3587</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>0.3445</v>
+        <v>0.3562</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>0.3587</v>
+        <v>0.3819</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>0.3562</v>
+        <v>0.3667</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>0.3819</v>
+        <v>0.3471</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>0.3667</v>
+        <v>0.3696</v>
       </c>
     </row>
     <row r="55">
@@ -12289,32 +12449,32 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>2022H1</t>
+          <t>2023H1</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>2022H2</t>
+          <t>2023H2</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>2023H1</t>
+          <t>2024H1</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>2023H2</t>
+          <t>2024H2</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>2024H1</t>
+          <t>2025H1</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>2024H2</t>
+          <t>2025H2</t>
         </is>
       </c>
     </row>
@@ -12325,22 +12485,22 @@
         </is>
       </c>
       <c r="B57" s="7" t="n">
-        <v>0.8438</v>
+        <v>0.7886</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>0.8519</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>0.7886</v>
+        <v>0.7708</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>0.7708</v>
+        <v>0.7456</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>0.7334000000000001</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="58">
@@ -12363,22 +12523,22 @@
         </is>
       </c>
       <c r="B59" s="7" t="n">
-        <v>0.2993</v>
+        <v>0.2828</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>0.2765</v>
+        <v>0.4187</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>0.2828</v>
+        <v>0.4196</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>0.4187</v>
+        <v>0.4038</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>0.4196</v>
+        <v>0.3458</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>0.4038</v>
+        <v>0.3597</v>
       </c>
     </row>
     <row r="60">
@@ -12388,22 +12548,22 @@
         </is>
       </c>
       <c r="B60" s="7" t="n">
-        <v>0.8668</v>
+        <v>0.8451</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>0.9643</v>
+        <v>0.8219</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>0.8451</v>
+        <v>0.8063</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>0.8219</v>
+        <v>0.8104</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>0.8063</v>
+        <v>0.7932</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0.8104</v>
+        <v>0.8041</v>
       </c>
     </row>
     <row r="61">
@@ -12413,22 +12573,22 @@
         </is>
       </c>
       <c r="B61" s="7" t="n">
-        <v>0.3917</v>
+        <v>0.4825</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>0.4369</v>
+        <v>0.5339</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>0.4825</v>
+        <v>0.4957</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>0.5339</v>
+        <v>0.5262</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>0.4957</v>
+        <v>0.5293</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>0.5262</v>
+        <v>0.5322</v>
       </c>
     </row>
   </sheetData>
@@ -12477,32 +12637,32 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2022H1</t>
+          <t>2023H1</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>2022H2</t>
+          <t>2023H2</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>2023H1</t>
+          <t>2024H1</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>2023H2</t>
+          <t>2024H2</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>2024H1</t>
+          <t>2025H1</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>2024H2</t>
+          <t>2025H2</t>
         </is>
       </c>
     </row>
@@ -12513,22 +12673,22 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>10800.4</v>
+        <v>10738.6</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>11060.6</v>
+        <v>10656.3</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>10738.6</v>
+        <v>10729.3</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>10656.3</v>
+        <v>12964.4</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>10729.3</v>
+        <v>12320.8</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>12964.4</v>
+        <v>12299.2</v>
       </c>
     </row>
     <row r="4">
@@ -12551,22 +12711,22 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>5593.7</v>
+        <v>6962.2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>6811.4</v>
+        <v>5886.7</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>6962.2</v>
+        <v>6034.1</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>5886.7</v>
+        <v>6020.3</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>6034.1</v>
+        <v>6095.9</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>6020.3</v>
+        <v>6458.6</v>
       </c>
     </row>
     <row r="6">
@@ -12576,22 +12736,22 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>8935.6</v>
+        <v>9435.9</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>8023.7</v>
+        <v>8824.200000000001</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>9435.9</v>
+        <v>8666.4</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>8824.200000000001</v>
+        <v>9103</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>8666.4</v>
+        <v>8981</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>9103</v>
+        <v>9830</v>
       </c>
     </row>
     <row r="7">
@@ -12601,22 +12761,22 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>8937.6</v>
+        <v>9136.1</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>9106.299999999999</v>
+        <v>8873.4</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>9136.1</v>
+        <v>8785.1</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>8873.4</v>
+        <v>8833.700000000001</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>8785.1</v>
+        <v>8371</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>8833.700000000001</v>
+        <v>8299.6</v>
       </c>
     </row>
     <row r="10">
@@ -12634,32 +12794,32 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2022H1</t>
+          <t>2023H1</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>2022H2</t>
+          <t>2023H2</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>2023H1</t>
+          <t>2024H1</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>2023H2</t>
+          <t>2024H2</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2024H1</t>
+          <t>2025H1</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>2024H2</t>
+          <t>2025H2</t>
         </is>
       </c>
     </row>
@@ -12670,22 +12830,22 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>2395</v>
+        <v>3380.1</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>2669.5</v>
+        <v>3430.5</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>3380.1</v>
+        <v>3440.9</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>3430.5</v>
+        <v>3659.5</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>3440.9</v>
+        <v>3829.1</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>3659.5</v>
+        <v>3818.5</v>
       </c>
     </row>
     <row r="13">
@@ -12708,22 +12868,22 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>1137.9</v>
+        <v>1296.4</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1290.7</v>
+        <v>1517.5</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1296.4</v>
+        <v>1610.9</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1517.5</v>
+        <v>2072.9</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>1610.9</v>
+        <v>2155.7</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>2072.9</v>
+        <v>2326.6</v>
       </c>
     </row>
     <row r="15">
@@ -12733,22 +12893,22 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>800</v>
+        <v>1127.5</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>640.1</v>
+        <v>1137.8</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>1127.5</v>
+        <v>1131.3</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1137.8</v>
+        <v>1361.4</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1131.3</v>
+        <v>1395.9</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>1361.4</v>
+        <v>1585.3</v>
       </c>
     </row>
     <row r="16">
@@ -12758,22 +12918,22 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>647.1</v>
+        <v>759.4</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>730.6</v>
+        <v>691.3</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>759.4</v>
+        <v>644</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>691.3</v>
+        <v>658.2</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>644</v>
+        <v>554.5</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>658.2</v>
+        <v>530.5</v>
       </c>
     </row>
     <row r="19">
@@ -12791,32 +12951,32 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>2022H1</t>
+          <t>2023H1</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>2022H2</t>
+          <t>2023H2</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>2023H1</t>
+          <t>2024H1</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>2023H2</t>
+          <t>2024H2</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2024H1</t>
+          <t>2025H1</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2024H2</t>
+          <t>2025H2</t>
         </is>
       </c>
     </row>
@@ -12827,22 +12987,22 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>2181.6</v>
+        <v>2426.9</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>2313.4</v>
+        <v>2442.3</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2426.9</v>
+        <v>2335.1</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>2442.3</v>
+        <v>2490.4</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>2335.1</v>
+        <v>2491.5</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>2490.4</v>
+        <v>2789.7</v>
       </c>
     </row>
     <row r="22">
@@ -12865,22 +13025,22 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>2477.2</v>
+        <v>2937.6</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>2283.2</v>
+        <v>3030</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2937.6</v>
+        <v>3123.8</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>3030</v>
+        <v>2893.6</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>3123.8</v>
+        <v>2720.7</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>2893.6</v>
+        <v>2711.1</v>
       </c>
     </row>
     <row r="24">
@@ -12890,22 +13050,22 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>4342.5</v>
+        <v>4862.8</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>3822.3</v>
+        <v>4929.2</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>4862.8</v>
+        <v>5082.3</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>4929.2</v>
+        <v>4970.5</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>5082.3</v>
+        <v>4675.9</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>4970.5</v>
+        <v>5152.4</v>
       </c>
     </row>
     <row r="25">
@@ -12915,22 +13075,22 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>4161.7</v>
+        <v>4315.4</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>4254.1</v>
+        <v>4217.1</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>4315.4</v>
+        <v>4338.7</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>4217.1</v>
+        <v>4163.8</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>4338.7</v>
+        <v>3898.1</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>4163.8</v>
+        <v>4102.9</v>
       </c>
     </row>
     <row r="28">
@@ -12948,32 +13108,32 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2022H1</t>
+          <t>2023H1</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>2022H2</t>
+          <t>2023H2</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>2023H1</t>
+          <t>2024H1</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>2023H2</t>
+          <t>2024H2</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2024H1</t>
+          <t>2025H1</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>2024H2</t>
+          <t>2025H2</t>
         </is>
       </c>
     </row>
@@ -12984,22 +13144,22 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>1298.5</v>
+        <v>1489</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>1420.9</v>
+        <v>1476</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>1489</v>
+        <v>1343.6</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>1476</v>
+        <v>1281.5</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>1343.6</v>
+        <v>1251.1</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>1281.5</v>
+        <v>1253.8</v>
       </c>
     </row>
     <row r="31">
@@ -13022,22 +13182,22 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>1238.8</v>
+        <v>1631.7</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>1196.6</v>
+        <v>1850.7</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1631.7</v>
+        <v>1850.5</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>1850.7</v>
+        <v>1442.8</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>1850.5</v>
+        <v>1236.8</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>1442.8</v>
+        <v>1170.4</v>
       </c>
     </row>
     <row r="33">
@@ -13047,22 +13207,22 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>1841.6</v>
+        <v>2120.1</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>1591.1</v>
+        <v>2081</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>2120.1</v>
+        <v>2358.4</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>2081</v>
+        <v>2311.1</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>2358.4</v>
+        <v>2184.6</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>2311.1</v>
+        <v>2555.3</v>
       </c>
     </row>
     <row r="34">
@@ -13072,22 +13232,22 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>2379.2</v>
+        <v>2464.9</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>2432</v>
+        <v>2386.5</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>2464.9</v>
+        <v>2441.8</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>2386.5</v>
+        <v>2392.2</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>2441.8</v>
+        <v>2198</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>2392.2</v>
+        <v>2320.3</v>
       </c>
     </row>
     <row r="37">
@@ -13105,32 +13265,32 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>2022H1</t>
+          <t>2023H1</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>2022H2</t>
+          <t>2023H2</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>2023H1</t>
+          <t>2024H1</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>2023H2</t>
+          <t>2024H2</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2024H1</t>
+          <t>2025H1</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>2024H2</t>
+          <t>2025H2</t>
         </is>
       </c>
     </row>
@@ -13141,22 +13301,22 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>883.1</v>
+        <v>938</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>892.6</v>
+        <v>966.2</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>938</v>
+        <v>991.5</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>966.2</v>
+        <v>1208.9</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>991.5</v>
+        <v>1240.4</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>1208.9</v>
+        <v>1535.9</v>
       </c>
     </row>
     <row r="40">
@@ -13179,22 +13339,22 @@
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>1238.4</v>
+        <v>1305.9</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>1086.6</v>
+        <v>1179.3</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>1305.9</v>
+        <v>1273.3</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>1179.3</v>
+        <v>1450.8</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1273.3</v>
+        <v>1483.9</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>1450.8</v>
+        <v>1540.7</v>
       </c>
     </row>
     <row r="42">
@@ -13204,22 +13364,22 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>2500.9</v>
+        <v>2742.7</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>2231.1</v>
+        <v>2848.2</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>2742.7</v>
+        <v>2723.9</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>2848.2</v>
+        <v>2659.4</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>2723.9</v>
+        <v>2491.3</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>2659.4</v>
+        <v>2597.1</v>
       </c>
     </row>
     <row r="43">
@@ -13229,22 +13389,22 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>1782.5</v>
+        <v>1850.5</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>1822.2</v>
+        <v>1830.6</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>1850.5</v>
+        <v>1896.9</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>1830.6</v>
+        <v>1771.6</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>1896.9</v>
+        <v>1700.1</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>1771.6</v>
+        <v>1782.6</v>
       </c>
     </row>
     <row r="46">
@@ -13262,32 +13422,32 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2022H1</t>
+          <t>2023H1</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>2022H2</t>
+          <t>2023H2</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>2023H1</t>
+          <t>2024H1</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>2023H2</t>
+          <t>2024H2</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2024H1</t>
+          <t>2025H1</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>2024H2</t>
+          <t>2025H2</t>
         </is>
       </c>
     </row>
@@ -13298,22 +13458,22 @@
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>6223.8</v>
+        <v>4931.6</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>6077.7</v>
+        <v>4783.5</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>4931.6</v>
+        <v>4953.4</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>4783.5</v>
+        <v>6814.5</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>4953.4</v>
+        <v>6000.1</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>6814.5</v>
+        <v>5691</v>
       </c>
     </row>
     <row r="49">
@@ -13336,22 +13496,22 @@
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>1978.6</v>
+        <v>2728.2</v>
       </c>
       <c r="C50" s="6" t="n">
-        <v>3237.5</v>
+        <v>1339.3</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>2728.2</v>
+        <v>1299.4</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>1339.3</v>
+        <v>1053.8</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>1299.4</v>
+        <v>1219.6</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>1053.8</v>
+        <v>1420.9</v>
       </c>
     </row>
     <row r="51">
@@ -13361,22 +13521,22 @@
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>3793.1</v>
+        <v>3445.6</v>
       </c>
       <c r="C51" s="6" t="n">
-        <v>3561.3</v>
+        <v>2757.2</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>3445.6</v>
+        <v>2452.8</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>2757.2</v>
+        <v>2771.2</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>2452.8</v>
+        <v>2909.2</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>2771.2</v>
+        <v>3092.3</v>
       </c>
     </row>
     <row r="52">
@@ -13386,22 +13546,22 @@
         </is>
       </c>
       <c r="B52" s="6" t="n">
-        <v>4128.7</v>
+        <v>4061.2</v>
       </c>
       <c r="C52" s="6" t="n">
-        <v>4121.5</v>
+        <v>3965.1</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>4061.2</v>
+        <v>3802.4</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>3965.1</v>
+        <v>4011.6</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>3802.4</v>
+        <v>3918.5</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>4011.6</v>
+        <v>3666.3</v>
       </c>
     </row>
     <row r="55">
@@ -13419,32 +13579,32 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>2022H1</t>
+          <t>2023H1</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>2022H2</t>
+          <t>2023H2</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>2023H1</t>
+          <t>2024H1</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>2023H2</t>
+          <t>2024H2</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>2024H1</t>
+          <t>2025H1</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>2024H2</t>
+          <t>2025H2</t>
         </is>
       </c>
     </row>
@@ -13455,22 +13615,22 @@
         </is>
       </c>
       <c r="B57" s="7" t="n">
-        <v>0.2218</v>
+        <v>0.3148</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>0.2414</v>
+        <v>0.3219</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>0.3148</v>
+        <v>0.3207</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>0.3219</v>
+        <v>0.2823</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>0.3207</v>
+        <v>0.3108</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>0.2823</v>
+        <v>0.3105</v>
       </c>
     </row>
     <row r="58">
@@ -13493,22 +13653,22 @@
         </is>
       </c>
       <c r="B59" s="7" t="n">
-        <v>0.2034</v>
+        <v>0.1862</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>0.1895</v>
+        <v>0.2578</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>0.1862</v>
+        <v>0.267</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>0.2578</v>
+        <v>0.3443</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>0.267</v>
+        <v>0.3536</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>0.3443</v>
+        <v>0.3602</v>
       </c>
     </row>
     <row r="60">
@@ -13518,22 +13678,22 @@
         </is>
       </c>
       <c r="B60" s="7" t="n">
-        <v>0.0895</v>
+        <v>0.1195</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>0.0798</v>
+        <v>0.1289</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>0.1195</v>
+        <v>0.1305</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>0.1289</v>
+        <v>0.1495</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>0.1305</v>
+        <v>0.1554</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0.1495</v>
+        <v>0.1613</v>
       </c>
     </row>
     <row r="61">
@@ -13543,22 +13703,22 @@
         </is>
       </c>
       <c r="B61" s="7" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.0779</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0733</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>0.0779</v>
+        <v>0.0745</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>0.0733</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>0.0745</v>
+        <v>0.0639</v>
       </c>
     </row>
     <row r="64">
@@ -13576,32 +13736,32 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>2022H1</t>
+          <t>2023H1</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>2022H2</t>
+          <t>2023H2</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>2023H1</t>
+          <t>2024H1</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>2023H2</t>
+          <t>2024H2</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>2024H1</t>
+          <t>2025H1</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>2024H2</t>
+          <t>2025H2</t>
         </is>
       </c>
     </row>
@@ -13612,22 +13772,22 @@
         </is>
       </c>
       <c r="B66" s="7" t="n">
-        <v>0.202</v>
+        <v>0.226</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>0.2092</v>
+        <v>0.2292</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>0.226</v>
+        <v>0.2176</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>0.2292</v>
+        <v>0.1921</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>0.2176</v>
+        <v>0.2022</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>0.1921</v>
+        <v>0.2268</v>
       </c>
     </row>
     <row r="67">
@@ -13650,22 +13810,22 @@
         </is>
       </c>
       <c r="B68" s="7" t="n">
-        <v>0.4429</v>
+        <v>0.4219</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>0.3352</v>
+        <v>0.5147</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>0.4219</v>
+        <v>0.5177</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>0.5147</v>
+        <v>0.4806</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>0.5177</v>
+        <v>0.4463</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>0.4806</v>
+        <v>0.4198</v>
       </c>
     </row>
     <row r="69">
@@ -13675,22 +13835,22 @@
         </is>
       </c>
       <c r="B69" s="7" t="n">
-        <v>0.486</v>
+        <v>0.5154</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>0.4764</v>
+        <v>0.5586</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>0.5154</v>
+        <v>0.5864</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>0.5586</v>
+        <v>0.546</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>0.5864</v>
+        <v>0.5206</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>0.546</v>
+        <v>0.5242</v>
       </c>
     </row>
     <row r="70">
@@ -13700,22 +13860,22 @@
         </is>
       </c>
       <c r="B70" s="7" t="n">
-        <v>0.4656</v>
+        <v>0.4723</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>0.4672</v>
+        <v>0.4752</v>
       </c>
       <c r="D70" s="7" t="n">
-        <v>0.4723</v>
+        <v>0.4939</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>0.4752</v>
+        <v>0.4714</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>0.4939</v>
+        <v>0.4657</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>0.4714</v>
+        <v>0.4944</v>
       </c>
     </row>
   </sheetData>

--- a/銀行債券_完整報表.xlsx
+++ b/銀行債券_完整報表.xlsx
@@ -9790,7 +9790,9 @@
       <c r="V3" s="4" t="n">
         <v>1516</v>
       </c>
-      <c r="W3" s="4" t="inlineStr"/>
+      <c r="W3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="X3" s="4" t="n">
         <v>1008</v>
       </c>
@@ -9803,7 +9805,9 @@
       <c r="AA3" s="4" t="n">
         <v>1463</v>
       </c>
-      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AB3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AC3" s="4" t="n">
         <v>956</v>
       </c>
@@ -9816,7 +9820,9 @@
       <c r="AF3" s="4" t="n">
         <v>2099</v>
       </c>
-      <c r="AG3" s="4" t="inlineStr"/>
+      <c r="AG3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AH3" s="4" t="n">
         <v>1334</v>
       </c>
@@ -9829,7 +9835,9 @@
       <c r="AK3" s="4" t="n">
         <v>3411</v>
       </c>
-      <c r="AL3" s="4" t="inlineStr"/>
+      <c r="AL3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AM3" s="4" t="n">
         <v>1524</v>
       </c>
@@ -9842,7 +9850,9 @@
       <c r="AP3" s="4" t="n">
         <v>2918</v>
       </c>
-      <c r="AQ3" s="4" t="inlineStr"/>
+      <c r="AQ3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AR3" s="4" t="n">
         <v>1005</v>
       </c>
@@ -9855,7 +9865,9 @@
       <c r="AU3" s="4" t="n">
         <v>3090</v>
       </c>
-      <c r="AV3" s="4" t="inlineStr"/>
+      <c r="AV3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AW3" s="4" t="n">
         <v>1085</v>
       </c>
@@ -9868,7 +9880,9 @@
       <c r="AZ3" s="4" t="n">
         <v>1853</v>
       </c>
-      <c r="BA3" s="4" t="inlineStr"/>
+      <c r="BA3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="BB3" s="4" t="n">
         <v>1356</v>
       </c>
@@ -9881,7 +9895,9 @@
       <c r="BE3" s="4" t="n">
         <v>2118</v>
       </c>
-      <c r="BF3" s="4" t="inlineStr"/>
+      <c r="BF3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="BG3" s="4" t="n">
         <v>2095</v>
       </c>
@@ -9963,7 +9979,9 @@
       <c r="V4" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="W4" s="4" t="inlineStr"/>
+      <c r="W4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="X4" s="4" t="n">
         <v>26</v>
       </c>
@@ -9976,7 +9994,9 @@
       <c r="AA4" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AB4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AC4" s="4" t="n">
         <v>81</v>
       </c>
@@ -9989,7 +10009,9 @@
       <c r="AF4" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG4" s="4" t="inlineStr"/>
+      <c r="AG4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AH4" s="4" t="n">
         <v>6</v>
       </c>
@@ -10002,7 +10024,9 @@
       <c r="AK4" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="AL4" s="4" t="inlineStr"/>
+      <c r="AL4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AM4" s="4" t="n">
         <v>23</v>
       </c>
@@ -10015,7 +10039,9 @@
       <c r="AP4" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="AQ4" s="4" t="inlineStr"/>
+      <c r="AQ4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AR4" s="4" t="n">
         <v>29</v>
       </c>
@@ -10028,7 +10054,9 @@
       <c r="AU4" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="AV4" s="4" t="inlineStr"/>
+      <c r="AV4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AW4" s="4" t="n">
         <v>136</v>
       </c>
@@ -10041,7 +10069,9 @@
       <c r="AZ4" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="BA4" s="4" t="inlineStr"/>
+      <c r="BA4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="BB4" s="4" t="n">
         <v>146</v>
       </c>
@@ -10054,7 +10084,9 @@
       <c r="BE4" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="BF4" s="4" t="inlineStr"/>
+      <c r="BF4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="BG4" s="4" t="n">
         <v>231</v>
       </c>
@@ -10136,7 +10168,9 @@
       <c r="V5" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="W5" s="4" t="inlineStr"/>
+      <c r="W5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="X5" s="4" t="n">
         <v>192</v>
       </c>
@@ -10149,7 +10183,9 @@
       <c r="AA5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AC5" s="4" t="n">
         <v>104</v>
       </c>
@@ -10162,7 +10198,9 @@
       <c r="AF5" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="AG5" s="4" t="inlineStr"/>
+      <c r="AG5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AH5" s="4" t="n">
         <v>203</v>
       </c>
@@ -10175,7 +10213,9 @@
       <c r="AK5" s="4" t="n">
         <v>132</v>
       </c>
-      <c r="AL5" s="4" t="inlineStr"/>
+      <c r="AL5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AM5" s="4" t="n">
         <v>180</v>
       </c>
@@ -10188,7 +10228,9 @@
       <c r="AP5" s="4" t="n">
         <v>131</v>
       </c>
-      <c r="AQ5" s="4" t="inlineStr"/>
+      <c r="AQ5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AR5" s="4" t="n">
         <v>80</v>
       </c>
@@ -10201,7 +10243,9 @@
       <c r="AU5" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="AV5" s="4" t="inlineStr"/>
+      <c r="AV5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AW5" s="4" t="n">
         <v>215</v>
       </c>
@@ -10214,7 +10258,9 @@
       <c r="AZ5" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="BA5" s="4" t="inlineStr"/>
+      <c r="BA5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="BB5" s="4" t="n">
         <v>259</v>
       </c>
@@ -10227,7 +10273,9 @@
       <c r="BE5" s="4" t="n">
         <v>125</v>
       </c>
-      <c r="BF5" s="4" t="inlineStr"/>
+      <c r="BF5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="BG5" s="4" t="n">
         <v>306</v>
       </c>
@@ -10309,7 +10357,9 @@
       <c r="V6" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="W6" s="4" t="inlineStr"/>
+      <c r="W6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="X6" s="4" t="n">
         <v>378</v>
       </c>
@@ -10322,7 +10372,9 @@
       <c r="AA6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AC6" s="4" t="n">
         <v>334</v>
       </c>
@@ -10335,7 +10387,9 @@
       <c r="AF6" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="AG6" s="4" t="inlineStr"/>
+      <c r="AG6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AH6" s="4" t="n">
         <v>724</v>
       </c>
@@ -10348,7 +10402,9 @@
       <c r="AK6" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AL6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AM6" s="4" t="n">
         <v>608</v>
       </c>
@@ -10361,7 +10417,9 @@
       <c r="AP6" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AQ6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AR6" s="4" t="n">
         <v>448</v>
       </c>
@@ -10374,7 +10432,9 @@
       <c r="AU6" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="AV6" s="4" t="inlineStr"/>
+      <c r="AV6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AW6" s="4" t="n">
         <v>228</v>
       </c>
@@ -10387,7 +10447,9 @@
       <c r="AZ6" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="BA6" s="4" t="inlineStr"/>
+      <c r="BA6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="BB6" s="4" t="n">
         <v>356</v>
       </c>
@@ -10400,7 +10462,9 @@
       <c r="BE6" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="BF6" s="4" t="inlineStr"/>
+      <c r="BF6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="BG6" s="4" t="n">
         <v>452</v>
       </c>
@@ -10482,7 +10546,9 @@
       <c r="V7" s="4" t="n">
         <v>239</v>
       </c>
-      <c r="W7" s="4" t="inlineStr"/>
+      <c r="W7" s="4" t="n">
+        <v>541</v>
+      </c>
       <c r="X7" s="4" t="n">
         <v>691</v>
       </c>
@@ -10495,7 +10561,9 @@
       <c r="AA7" s="4" t="n">
         <v>185</v>
       </c>
-      <c r="AB7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="n">
+        <v>540</v>
+      </c>
       <c r="AC7" s="4" t="n">
         <v>741</v>
       </c>
@@ -10508,7 +10576,9 @@
       <c r="AF7" s="4" t="n">
         <v>616</v>
       </c>
-      <c r="AG7" s="4" t="inlineStr"/>
+      <c r="AG7" s="4" t="n">
+        <v>531</v>
+      </c>
       <c r="AH7" s="4" t="n">
         <v>792</v>
       </c>
@@ -10521,7 +10591,9 @@
       <c r="AK7" s="4" t="n">
         <v>633</v>
       </c>
-      <c r="AL7" s="4" t="inlineStr"/>
+      <c r="AL7" s="4" t="n">
+        <v>490</v>
+      </c>
       <c r="AM7" s="4" t="n">
         <v>882</v>
       </c>
@@ -10534,7 +10606,9 @@
       <c r="AP7" s="4" t="n">
         <v>615</v>
       </c>
-      <c r="AQ7" s="4" t="inlineStr"/>
+      <c r="AQ7" s="4" t="n">
+        <v>484</v>
+      </c>
       <c r="AR7" s="4" t="n">
         <v>1137</v>
       </c>
@@ -10547,7 +10621,9 @@
       <c r="AU7" s="4" t="n">
         <v>938</v>
       </c>
-      <c r="AV7" s="4" t="inlineStr"/>
+      <c r="AV7" s="4" t="n">
+        <v>463</v>
+      </c>
       <c r="AW7" s="4" t="n">
         <v>1469</v>
       </c>
@@ -10560,7 +10636,9 @@
       <c r="AZ7" s="4" t="n">
         <v>1341</v>
       </c>
-      <c r="BA7" s="4" t="inlineStr"/>
+      <c r="BA7" s="4" t="n">
+        <v>457</v>
+      </c>
       <c r="BB7" s="4" t="n">
         <v>1564</v>
       </c>
@@ -10573,7 +10651,9 @@
       <c r="BE7" s="4" t="n">
         <v>1464</v>
       </c>
-      <c r="BF7" s="4" t="inlineStr"/>
+      <c r="BF7" s="4" t="n">
+        <v>459</v>
+      </c>
       <c r="BG7" s="4" t="n">
         <v>1668</v>
       </c>
@@ -10655,7 +10735,9 @@
       <c r="V8" s="4" t="n">
         <v>119</v>
       </c>
-      <c r="W8" s="4" t="inlineStr"/>
+      <c r="W8" s="4" t="n">
+        <v>1106</v>
+      </c>
       <c r="X8" s="4" t="n">
         <v>881</v>
       </c>
@@ -10668,7 +10750,9 @@
       <c r="AA8" s="4" t="n">
         <v>106</v>
       </c>
-      <c r="AB8" s="4" t="inlineStr"/>
+      <c r="AB8" s="4" t="n">
+        <v>1014</v>
+      </c>
       <c r="AC8" s="4" t="n">
         <v>725</v>
       </c>
@@ -10681,7 +10765,9 @@
       <c r="AF8" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="AG8" s="4" t="inlineStr"/>
+      <c r="AG8" s="4" t="n">
+        <v>987</v>
+      </c>
       <c r="AH8" s="4" t="n">
         <v>832</v>
       </c>
@@ -10694,7 +10780,9 @@
       <c r="AK8" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="AL8" s="4" t="inlineStr"/>
+      <c r="AL8" s="4" t="n">
+        <v>968</v>
+      </c>
       <c r="AM8" s="4" t="n">
         <v>747</v>
       </c>
@@ -10707,7 +10795,9 @@
       <c r="AP8" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="AQ8" s="4" t="inlineStr"/>
+      <c r="AQ8" s="4" t="n">
+        <v>901</v>
+      </c>
       <c r="AR8" s="4" t="n">
         <v>902</v>
       </c>
@@ -10720,7 +10810,9 @@
       <c r="AU8" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="AV8" s="4" t="inlineStr"/>
+      <c r="AV8" s="4" t="n">
+        <v>795</v>
+      </c>
       <c r="AW8" s="4" t="n">
         <v>942</v>
       </c>
@@ -10733,7 +10825,9 @@
       <c r="AZ8" s="4" t="n">
         <v>104</v>
       </c>
-      <c r="BA8" s="4" t="inlineStr"/>
+      <c r="BA8" s="4" t="n">
+        <v>690</v>
+      </c>
       <c r="BB8" s="4" t="n">
         <v>962</v>
       </c>
@@ -10746,7 +10840,9 @@
       <c r="BE8" s="4" t="n">
         <v>103</v>
       </c>
-      <c r="BF8" s="4" t="inlineStr"/>
+      <c r="BF8" s="4" t="n">
+        <v>640</v>
+      </c>
       <c r="BG8" s="4" t="n">
         <v>958</v>
       </c>
@@ -10828,7 +10924,9 @@
       <c r="V9" s="4" t="n">
         <v>1011</v>
       </c>
-      <c r="W9" s="4" t="inlineStr"/>
+      <c r="W9" s="4" t="n">
+        <v>17</v>
+      </c>
       <c r="X9" s="4" t="n">
         <v>377</v>
       </c>
@@ -10841,7 +10939,9 @@
       <c r="AA9" s="4" t="n">
         <v>979</v>
       </c>
-      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="n">
+        <v>17</v>
+      </c>
       <c r="AC9" s="4" t="n">
         <v>351</v>
       </c>
@@ -10854,7 +10954,9 @@
       <c r="AF9" s="4" t="n">
         <v>929</v>
       </c>
-      <c r="AG9" s="4" t="inlineStr"/>
+      <c r="AG9" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="AH9" s="4" t="n">
         <v>378</v>
       </c>
@@ -10867,7 +10969,9 @@
       <c r="AK9" s="4" t="n">
         <v>750</v>
       </c>
-      <c r="AL9" s="4" t="inlineStr"/>
+      <c r="AL9" s="4" t="n">
+        <v>29</v>
+      </c>
       <c r="AM9" s="4" t="n">
         <v>350</v>
       </c>
@@ -10880,7 +10984,9 @@
       <c r="AP9" s="4" t="n">
         <v>608</v>
       </c>
-      <c r="AQ9" s="4" t="inlineStr"/>
+      <c r="AQ9" s="4" t="n">
+        <v>40</v>
+      </c>
       <c r="AR9" s="4" t="n">
         <v>350</v>
       </c>
@@ -10893,7 +10999,9 @@
       <c r="AU9" s="4" t="n">
         <v>597</v>
       </c>
-      <c r="AV9" s="4" t="inlineStr"/>
+      <c r="AV9" s="4" t="n">
+        <v>49</v>
+      </c>
       <c r="AW9" s="4" t="n">
         <v>291</v>
       </c>
@@ -10906,7 +11014,9 @@
       <c r="AZ9" s="4" t="n">
         <v>570</v>
       </c>
-      <c r="BA9" s="4" t="inlineStr"/>
+      <c r="BA9" s="4" t="n">
+        <v>60</v>
+      </c>
       <c r="BB9" s="4" t="n">
         <v>215</v>
       </c>
@@ -10919,7 +11029,9 @@
       <c r="BE9" s="4" t="n">
         <v>633</v>
       </c>
-      <c r="BF9" s="4" t="inlineStr"/>
+      <c r="BF9" s="4" t="n">
+        <v>58</v>
+      </c>
       <c r="BG9" s="4" t="n">
         <v>165</v>
       </c>
@@ -11001,7 +11113,9 @@
       <c r="V10" s="4" t="n">
         <v>2151</v>
       </c>
-      <c r="W10" s="4" t="inlineStr"/>
+      <c r="W10" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="X10" s="4" t="n">
         <v>421</v>
       </c>
@@ -11014,7 +11128,9 @@
       <c r="AA10" s="4" t="n">
         <v>2475</v>
       </c>
-      <c r="AB10" s="4" t="inlineStr"/>
+      <c r="AB10" s="4" t="n">
+        <v>13</v>
+      </c>
       <c r="AC10" s="4" t="n">
         <v>469</v>
       </c>
@@ -11027,7 +11143,9 @@
       <c r="AF10" s="4" t="n">
         <v>2749</v>
       </c>
-      <c r="AG10" s="4" t="inlineStr"/>
+      <c r="AG10" s="4" t="n">
+        <v>33</v>
+      </c>
       <c r="AH10" s="4" t="n">
         <v>498</v>
       </c>
@@ -11040,7 +11158,9 @@
       <c r="AK10" s="4" t="n">
         <v>2742</v>
       </c>
-      <c r="AL10" s="4" t="inlineStr"/>
+      <c r="AL10" s="4" t="n">
+        <v>34</v>
+      </c>
       <c r="AM10" s="4" t="n">
         <v>612</v>
       </c>
@@ -11053,7 +11173,9 @@
       <c r="AP10" s="4" t="n">
         <v>2813</v>
       </c>
-      <c r="AQ10" s="4" t="inlineStr"/>
+      <c r="AQ10" s="4" t="n">
+        <v>59</v>
+      </c>
       <c r="AR10" s="4" t="n">
         <v>444</v>
       </c>
@@ -11066,7 +11188,9 @@
       <c r="AU10" s="4" t="n">
         <v>2702</v>
       </c>
-      <c r="AV10" s="4" t="inlineStr"/>
+      <c r="AV10" s="4" t="n">
+        <v>73</v>
+      </c>
       <c r="AW10" s="4" t="n">
         <v>468</v>
       </c>
@@ -11079,7 +11203,9 @@
       <c r="AZ10" s="4" t="n">
         <v>2438</v>
       </c>
-      <c r="BA10" s="4" t="inlineStr"/>
+      <c r="BA10" s="4" t="n">
+        <v>66</v>
+      </c>
       <c r="BB10" s="4" t="n">
         <v>446</v>
       </c>
@@ -11092,7 +11218,9 @@
       <c r="BE10" s="4" t="n">
         <v>2341</v>
       </c>
-      <c r="BF10" s="4" t="inlineStr"/>
+      <c r="BF10" s="4" t="n">
+        <v>66</v>
+      </c>
       <c r="BG10" s="4" t="n">
         <v>427</v>
       </c>
@@ -11174,7 +11302,9 @@
       <c r="V11" s="4" t="n">
         <v>755</v>
       </c>
-      <c r="W11" s="4" t="inlineStr"/>
+      <c r="W11" s="4" t="n">
+        <v>9</v>
+      </c>
       <c r="X11" s="4" t="n">
         <v>166</v>
       </c>
@@ -11187,7 +11317,9 @@
       <c r="AA11" s="4" t="n">
         <v>785</v>
       </c>
-      <c r="AB11" s="4" t="inlineStr"/>
+      <c r="AB11" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="AC11" s="4" t="n">
         <v>258</v>
       </c>
@@ -11200,7 +11332,9 @@
       <c r="AF11" s="4" t="n">
         <v>797</v>
       </c>
-      <c r="AG11" s="4" t="inlineStr"/>
+      <c r="AG11" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="AH11" s="4" t="n">
         <v>271</v>
       </c>
@@ -11213,7 +11347,9 @@
       <c r="AK11" s="4" t="n">
         <v>784</v>
       </c>
-      <c r="AL11" s="4" t="inlineStr"/>
+      <c r="AL11" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="AM11" s="4" t="n">
         <v>252</v>
       </c>
@@ -11226,7 +11362,9 @@
       <c r="AP11" s="4" t="n">
         <v>796</v>
       </c>
-      <c r="AQ11" s="4" t="inlineStr"/>
+      <c r="AQ11" s="4" t="n">
+        <v>30</v>
+      </c>
       <c r="AR11" s="4" t="n">
         <v>292</v>
       </c>
@@ -11239,7 +11377,9 @@
       <c r="AU11" s="4" t="n">
         <v>1052</v>
       </c>
-      <c r="AV11" s="4" t="inlineStr"/>
+      <c r="AV11" s="4" t="n">
+        <v>48</v>
+      </c>
       <c r="AW11" s="4" t="n">
         <v>293</v>
       </c>
@@ -11252,7 +11392,9 @@
       <c r="AZ11" s="4" t="n">
         <v>1047</v>
       </c>
-      <c r="BA11" s="4" t="inlineStr"/>
+      <c r="BA11" s="4" t="n">
+        <v>46</v>
+      </c>
       <c r="BB11" s="4" t="n">
         <v>263</v>
       </c>
@@ -11265,7 +11407,9 @@
       <c r="BE11" s="4" t="n">
         <v>1308</v>
       </c>
-      <c r="BF11" s="4" t="inlineStr"/>
+      <c r="BF11" s="4" t="n">
+        <v>51</v>
+      </c>
       <c r="BG11" s="4" t="n">
         <v>277</v>
       </c>
@@ -11347,7 +11491,9 @@
       <c r="V12" s="4" t="n">
         <v>282</v>
       </c>
-      <c r="W12" s="4" t="inlineStr"/>
+      <c r="W12" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="X12" s="4" t="n">
         <v>484</v>
       </c>
@@ -11360,7 +11506,9 @@
       <c r="AA12" s="4" t="n">
         <v>437</v>
       </c>
-      <c r="AB12" s="4" t="inlineStr"/>
+      <c r="AB12" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AC12" s="4" t="n">
         <v>511</v>
       </c>
@@ -11373,7 +11521,9 @@
       <c r="AF12" s="4" t="n">
         <v>547</v>
       </c>
-      <c r="AG12" s="4" t="inlineStr"/>
+      <c r="AG12" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AH12" s="4" t="n">
         <v>530</v>
       </c>
@@ -11386,7 +11536,9 @@
       <c r="AK12" s="4" t="n">
         <v>640</v>
       </c>
-      <c r="AL12" s="4" t="inlineStr"/>
+      <c r="AL12" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AM12" s="4" t="n">
         <v>893</v>
       </c>
@@ -11399,7 +11551,9 @@
       <c r="AP12" s="4" t="n">
         <v>676</v>
       </c>
-      <c r="AQ12" s="4" t="inlineStr"/>
+      <c r="AQ12" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AR12" s="4" t="n">
         <v>1052</v>
       </c>
@@ -11412,7 +11566,9 @@
       <c r="AU12" s="4" t="n">
         <v>671</v>
       </c>
-      <c r="AV12" s="4" t="inlineStr"/>
+      <c r="AV12" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AW12" s="4" t="n">
         <v>924</v>
       </c>
@@ -11425,7 +11581,9 @@
       <c r="AZ12" s="4" t="n">
         <v>626</v>
       </c>
-      <c r="BA12" s="4" t="inlineStr"/>
+      <c r="BA12" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="BB12" s="4" t="n">
         <v>666</v>
       </c>
@@ -11438,7 +11596,9 @@
       <c r="BE12" s="4" t="n">
         <v>602</v>
       </c>
-      <c r="BF12" s="4" t="inlineStr"/>
+      <c r="BF12" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="BG12" s="4" t="n">
         <v>553</v>
       </c>
@@ -11567,12 +11727,24 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
+      <c r="B4" s="6" t="n">
+        <v>1601.4</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1545.7</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1514</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1428.5</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1324.8</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1279.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -11724,12 +11896,24 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
+      <c r="B13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -11881,12 +12065,24 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
+      <c r="B22" s="6" t="n">
+        <v>1543</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>1486.7</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>1424.5</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1307.1</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>1206.9</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>1156.5</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -12038,12 +12234,24 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
-      <c r="G31" s="6" t="n"/>
+      <c r="B31" s="6" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>121.4</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>123.4</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -12195,12 +12403,24 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B40" s="7" t="n"/>
-      <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
-      <c r="E40" s="7" t="n"/>
-      <c r="F40" s="7" t="n"/>
-      <c r="G40" s="7" t="n"/>
+      <c r="B40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -12352,12 +12572,24 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B49" s="7" t="n"/>
-      <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
-      <c r="E49" s="7" t="n"/>
-      <c r="F49" s="7" t="n"/>
-      <c r="G49" s="7" t="n"/>
+      <c r="B49" s="7" t="n">
+        <v>0.9635</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>0.9619</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>0.9409</v>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>0.9036</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -12509,12 +12741,24 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B58" s="7" t="n"/>
-      <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="n"/>
-      <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="n"/>
-      <c r="G58" s="7" t="n"/>
+      <c r="B58" s="7" t="n">
+        <v>0.0365</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>0.0591</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>0.0964</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -12697,12 +12941,24 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
+      <c r="B4" s="6" t="n">
+        <v>1601.4</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1545.7</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1514</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1428.5</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1324.8</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1279.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -12854,12 +13110,24 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
+      <c r="B13" s="6" t="n">
+        <v>564.8</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>523.5</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>543.3</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>536.5</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>523.2</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>525.1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -13011,12 +13279,24 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
+      <c r="B22" s="6" t="n">
+        <v>1036.7</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>1022.2</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>970.7</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>892</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>801.6</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>754.8</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -13168,12 +13448,24 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
-      <c r="G31" s="6" t="n"/>
+      <c r="B31" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -13325,12 +13617,24 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B40" s="6" t="n"/>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6" t="n"/>
-      <c r="E40" s="6" t="n"/>
-      <c r="F40" s="6" t="n"/>
-      <c r="G40" s="6" t="n"/>
+      <c r="B40" s="6" t="n">
+        <v>1011.7</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>993.2</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>930.7</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>843.1</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>735.6</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>690.8</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -13482,12 +13786,24 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B49" s="6" t="n"/>
-      <c r="C49" s="6" t="n"/>
-      <c r="D49" s="6" t="n"/>
-      <c r="E49" s="6" t="n"/>
-      <c r="F49" s="6" t="n"/>
-      <c r="G49" s="6" t="n"/>
+      <c r="B49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -13639,12 +13955,24 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B58" s="7" t="n"/>
-      <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="n"/>
-      <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="n"/>
-      <c r="G58" s="7" t="n"/>
+      <c r="B58" s="7" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>0.4102</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -13796,12 +14124,24 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B67" s="7" t="n"/>
-      <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="n"/>
-      <c r="E67" s="7" t="n"/>
-      <c r="F67" s="7" t="n"/>
-      <c r="G67" s="7" t="n"/>
+      <c r="B67" s="7" t="n">
+        <v>0.6473</v>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>0.6613</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>0.6412</v>
+      </c>
+      <c r="E67" s="7" t="n">
+        <v>0.6245000000000001</v>
+      </c>
+      <c r="F67" s="7" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="G67" s="7" t="n">
+        <v>0.5898</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">

--- a/銀行債券_完整報表.xlsx
+++ b/銀行債券_完整報表.xlsx
@@ -9738,7 +9738,9 @@
       <c r="B3" s="4" t="n">
         <v>1316</v>
       </c>
-      <c r="C3" s="4" t="inlineStr"/>
+      <c r="C3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="D3" s="4" t="n">
         <v>0</v>
       </c>
@@ -9751,7 +9753,9 @@
       <c r="G3" s="4" t="n">
         <v>1206</v>
       </c>
-      <c r="H3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I3" s="4" t="n">
         <v>1957</v>
       </c>
@@ -9764,7 +9768,9 @@
       <c r="L3" s="4" t="n">
         <v>902</v>
       </c>
-      <c r="M3" s="4" t="inlineStr"/>
+      <c r="M3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="N3" s="4" t="n">
         <v>1817</v>
       </c>
@@ -9777,7 +9783,9 @@
       <c r="Q3" s="4" t="n">
         <v>1231</v>
       </c>
-      <c r="R3" s="4" t="inlineStr"/>
+      <c r="R3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="S3" s="4" t="n">
         <v>1684</v>
       </c>
@@ -9927,7 +9935,9 @@
       <c r="B4" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="D4" s="4" t="n">
         <v>0</v>
       </c>
@@ -9940,7 +9950,9 @@
       <c r="G4" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="H4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I4" s="4" t="n">
         <v>355</v>
       </c>
@@ -9953,7 +9965,9 @@
       <c r="L4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="N4" s="4" t="n">
         <v>239</v>
       </c>
@@ -9966,7 +9980,9 @@
       <c r="Q4" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="R4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="S4" s="4" t="n">
         <v>174</v>
       </c>
@@ -10116,7 +10132,9 @@
       <c r="B5" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
       </c>
@@ -10129,7 +10147,9 @@
       <c r="G5" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="H5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I5" s="4" t="n">
         <v>63</v>
       </c>
@@ -10142,7 +10162,9 @@
       <c r="L5" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="M5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="N5" s="4" t="n">
         <v>136</v>
       </c>
@@ -10155,7 +10177,9 @@
       <c r="Q5" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="R5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="S5" s="4" t="n">
         <v>188</v>
       </c>
@@ -10305,7 +10329,9 @@
       <c r="B6" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="C6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="D6" s="4" t="n">
         <v>0</v>
       </c>
@@ -10318,7 +10344,9 @@
       <c r="G6" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I6" s="4" t="n">
         <v>84</v>
       </c>
@@ -10331,7 +10359,9 @@
       <c r="L6" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="M6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="N6" s="4" t="n">
         <v>234</v>
       </c>
@@ -10344,7 +10374,9 @@
       <c r="Q6" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="R6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="S6" s="4" t="n">
         <v>369</v>
       </c>
@@ -10494,7 +10526,9 @@
       <c r="B7" s="4" t="n">
         <v>445</v>
       </c>
-      <c r="C7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="n">
+        <v>501</v>
+      </c>
       <c r="D7" s="4" t="n">
         <v>0</v>
       </c>
@@ -10507,7 +10541,9 @@
       <c r="G7" s="4" t="n">
         <v>541</v>
       </c>
-      <c r="H7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="n">
+        <v>364</v>
+      </c>
       <c r="I7" s="4" t="n">
         <v>709</v>
       </c>
@@ -10520,7 +10556,9 @@
       <c r="L7" s="4" t="n">
         <v>367</v>
       </c>
-      <c r="M7" s="4" t="inlineStr"/>
+      <c r="M7" s="4" t="n">
+        <v>402</v>
+      </c>
       <c r="N7" s="4" t="n">
         <v>416</v>
       </c>
@@ -10533,7 +10571,9 @@
       <c r="Q7" s="4" t="n">
         <v>330</v>
       </c>
-      <c r="R7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="n">
+        <v>498</v>
+      </c>
       <c r="S7" s="4" t="n">
         <v>368</v>
       </c>
@@ -10683,7 +10723,9 @@
       <c r="B8" s="4" t="n">
         <v>101</v>
       </c>
-      <c r="C8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="n">
+        <v>962</v>
+      </c>
       <c r="D8" s="4" t="n">
         <v>0</v>
       </c>
@@ -10696,7 +10738,9 @@
       <c r="G8" s="4" t="n">
         <v>176</v>
       </c>
-      <c r="H8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="n">
+        <v>1024</v>
+      </c>
       <c r="I8" s="4" t="n">
         <v>947</v>
       </c>
@@ -10709,7 +10753,9 @@
       <c r="L8" s="4" t="n">
         <v>149</v>
       </c>
-      <c r="M8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="n">
+        <v>1045</v>
+      </c>
       <c r="N8" s="4" t="n">
         <v>1120</v>
       </c>
@@ -10722,7 +10768,9 @@
       <c r="Q8" s="4" t="n">
         <v>114</v>
       </c>
-      <c r="R8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="n">
+        <v>1053</v>
+      </c>
       <c r="S8" s="4" t="n">
         <v>134</v>
       </c>
@@ -10872,7 +10920,9 @@
       <c r="B9" s="4" t="n">
         <v>1445</v>
       </c>
-      <c r="C9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="D9" s="4" t="n">
         <v>0</v>
       </c>
@@ -10885,7 +10935,9 @@
       <c r="G9" s="4" t="n">
         <v>1485</v>
       </c>
-      <c r="H9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="n">
+        <v>9</v>
+      </c>
       <c r="I9" s="4" t="n">
         <v>626</v>
       </c>
@@ -10898,7 +10950,9 @@
       <c r="L9" s="4" t="n">
         <v>1132</v>
       </c>
-      <c r="M9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="n">
+        <v>11</v>
+      </c>
       <c r="N9" s="4" t="n">
         <v>593</v>
       </c>
@@ -10911,7 +10965,9 @@
       <c r="Q9" s="4" t="n">
         <v>1080</v>
       </c>
-      <c r="R9" s="4" t="inlineStr"/>
+      <c r="R9" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="S9" s="4" t="n">
         <v>168</v>
       </c>
@@ -11061,7 +11117,9 @@
       <c r="B10" s="4" t="n">
         <v>1822</v>
       </c>
-      <c r="C10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="D10" s="4" t="n">
         <v>0</v>
       </c>
@@ -11074,7 +11132,9 @@
       <c r="G10" s="4" t="n">
         <v>1803</v>
       </c>
-      <c r="H10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I10" s="4" t="n">
         <v>96</v>
       </c>
@@ -11087,7 +11147,9 @@
       <c r="L10" s="4" t="n">
         <v>1902</v>
       </c>
-      <c r="M10" s="4" t="inlineStr"/>
+      <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="N10" s="4" t="n">
         <v>288</v>
       </c>
@@ -11100,7 +11162,9 @@
       <c r="Q10" s="4" t="n">
         <v>2088</v>
       </c>
-      <c r="R10" s="4" t="inlineStr"/>
+      <c r="R10" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="S10" s="4" t="n">
         <v>377</v>
       </c>
@@ -11250,7 +11314,9 @@
       <c r="B11" s="4" t="n">
         <v>586</v>
       </c>
-      <c r="C11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="D11" s="4" t="n">
         <v>0</v>
       </c>
@@ -11263,7 +11329,9 @@
       <c r="G11" s="4" t="n">
         <v>571</v>
       </c>
-      <c r="H11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I11" s="4" t="n">
         <v>123</v>
       </c>
@@ -11276,7 +11344,9 @@
       <c r="L11" s="4" t="n">
         <v>665</v>
       </c>
-      <c r="M11" s="4" t="inlineStr"/>
+      <c r="M11" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="N11" s="4" t="n">
         <v>137</v>
       </c>
@@ -11289,7 +11359,9 @@
       <c r="Q11" s="4" t="n">
         <v>657</v>
       </c>
-      <c r="R11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="S11" s="4" t="n">
         <v>135</v>
       </c>
@@ -11439,7 +11511,9 @@
       <c r="B12" s="4" t="n">
         <v>162</v>
       </c>
-      <c r="C12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="D12" s="4" t="n">
         <v>0</v>
       </c>
@@ -11452,7 +11526,9 @@
       <c r="G12" s="4" t="n">
         <v>175</v>
       </c>
-      <c r="H12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I12" s="4" t="n">
         <v>106</v>
       </c>
@@ -11465,7 +11541,9 @@
       <c r="L12" s="4" t="n">
         <v>267</v>
       </c>
-      <c r="M12" s="4" t="inlineStr"/>
+      <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="N12" s="4" t="n">
         <v>178</v>
       </c>
@@ -11478,7 +11556,9 @@
       <c r="Q12" s="4" t="n">
         <v>259</v>
       </c>
-      <c r="R12" s="4" t="inlineStr"/>
+      <c r="R12" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="S12" s="4" t="n">
         <v>171</v>
       </c>

--- a/銀行債券_完整報表.xlsx
+++ b/銀行債券_完整報表.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="寬表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料_按分類" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="圖-按分類" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料_按債種" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="圖-按債種" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="寬表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="資料_按分類" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="圖-按分類" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="資料_按債種" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="圖-按債種" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -171,13 +171,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -201,17 +201,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -219,10 +219,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -230,10 +230,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -241,10 +241,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -252,10 +252,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -280,17 +280,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -298,10 +298,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -309,10 +309,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -320,10 +320,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -331,10 +331,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -359,17 +359,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -377,10 +377,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -388,10 +388,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -399,10 +399,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -410,10 +410,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -438,17 +438,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -456,10 +456,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -467,10 +467,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -478,10 +478,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -489,10 +489,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -517,17 +517,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -535,10 +535,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -546,10 +546,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -557,10 +557,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -568,10 +568,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -596,17 +596,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -614,10 +614,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -625,10 +625,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -636,10 +636,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -647,10 +647,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -680,8 +680,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -708,8 +708,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -732,13 +732,13 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -762,17 +762,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -780,10 +780,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -791,10 +791,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -802,10 +802,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -813,10 +813,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -841,17 +841,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -859,10 +859,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -870,10 +870,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -881,10 +881,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -892,10 +892,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -920,17 +920,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -938,10 +938,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -949,10 +949,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -960,10 +960,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -971,10 +971,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -999,17 +999,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1017,10 +1017,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1028,10 +1028,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1039,10 +1039,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1050,10 +1050,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1078,17 +1078,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1096,10 +1096,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1107,10 +1107,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1118,10 +1118,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1129,10 +1129,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1157,17 +1157,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1175,10 +1175,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1186,10 +1186,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1197,10 +1197,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1208,10 +1208,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1241,8 +1241,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1269,8 +1269,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1293,13 +1293,13 @@
 </file>
 
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1323,17 +1323,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1341,10 +1341,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1352,10 +1352,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1363,10 +1363,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1374,10 +1374,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1402,17 +1402,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1420,10 +1420,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1431,10 +1431,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1442,10 +1442,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1453,10 +1453,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1481,17 +1481,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1499,10 +1499,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1510,10 +1510,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1521,10 +1521,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1532,10 +1532,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1560,17 +1560,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1578,10 +1578,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1589,10 +1589,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1600,10 +1600,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1611,10 +1611,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1639,17 +1639,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1657,10 +1657,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1668,10 +1668,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1679,10 +1679,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1690,10 +1690,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1718,17 +1718,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1736,10 +1736,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1747,10 +1747,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1758,10 +1758,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1769,10 +1769,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1802,8 +1802,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1830,8 +1830,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1854,13 +1854,13 @@
 </file>
 
 <file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1884,17 +1884,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1902,10 +1902,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1913,10 +1913,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1924,10 +1924,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1935,10 +1935,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1963,17 +1963,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1981,10 +1981,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1992,10 +1992,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2003,10 +2003,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2014,10 +2014,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2042,17 +2042,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2060,10 +2060,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2071,10 +2071,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2082,10 +2082,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2093,10 +2093,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2121,17 +2121,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2139,10 +2139,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2150,10 +2150,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2161,10 +2161,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2172,10 +2172,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2200,17 +2200,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2218,10 +2218,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2229,10 +2229,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2240,10 +2240,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2251,10 +2251,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2279,17 +2279,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2297,10 +2297,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2308,10 +2308,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2319,10 +2319,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2330,10 +2330,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2363,8 +2363,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -2391,8 +2391,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -2415,13 +2415,13 @@
 </file>
 
 <file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -2445,17 +2445,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2463,10 +2463,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2474,10 +2474,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2485,10 +2485,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2496,10 +2496,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2524,17 +2524,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2542,10 +2542,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2553,10 +2553,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2564,10 +2564,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2575,10 +2575,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2603,17 +2603,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2621,10 +2621,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2632,10 +2632,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2643,10 +2643,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2654,10 +2654,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2682,17 +2682,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2700,10 +2700,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2711,10 +2711,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2722,10 +2722,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2733,10 +2733,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2761,17 +2761,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2779,10 +2779,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2790,10 +2790,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2801,10 +2801,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2812,10 +2812,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2840,17 +2840,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2858,10 +2858,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2869,10 +2869,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2880,10 +2880,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2891,10 +2891,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2924,8 +2924,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -2952,8 +2952,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -2976,13 +2976,13 @@
 </file>
 
 <file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -3006,17 +3006,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3024,10 +3024,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3035,10 +3035,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3046,10 +3046,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3057,10 +3057,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3085,17 +3085,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3103,10 +3103,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3114,10 +3114,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3125,10 +3125,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3136,10 +3136,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3164,17 +3164,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3182,10 +3182,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3193,10 +3193,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3204,10 +3204,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3215,10 +3215,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3243,17 +3243,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3261,10 +3261,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3272,10 +3272,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3283,10 +3283,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3294,10 +3294,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3322,17 +3322,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3340,10 +3340,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3351,10 +3351,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3362,10 +3362,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3373,10 +3373,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3401,17 +3401,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3419,10 +3419,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3430,10 +3430,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3441,10 +3441,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3452,10 +3452,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3485,8 +3485,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -3513,8 +3513,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -3538,13 +3538,13 @@
 </file>
 
 <file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -3568,17 +3568,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3586,10 +3586,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3597,10 +3597,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3608,10 +3608,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3619,10 +3619,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3647,17 +3647,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3665,10 +3665,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3676,10 +3676,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3687,10 +3687,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3698,10 +3698,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3726,17 +3726,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3744,10 +3744,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3755,10 +3755,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3766,10 +3766,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3777,10 +3777,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3805,17 +3805,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3823,10 +3823,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3834,10 +3834,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3845,10 +3845,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3856,10 +3856,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3884,17 +3884,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3902,10 +3902,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3913,10 +3913,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3924,10 +3924,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3935,10 +3935,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3963,17 +3963,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3981,10 +3981,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3992,10 +3992,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4003,10 +4003,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4014,10 +4014,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4047,8 +4047,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -4075,8 +4075,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -4100,13 +4100,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -4130,17 +4130,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4148,10 +4148,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4159,10 +4159,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4170,10 +4170,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4181,10 +4181,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4209,17 +4209,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4227,10 +4227,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4238,10 +4238,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4249,10 +4249,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4260,10 +4260,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4288,17 +4288,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4306,10 +4306,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4317,10 +4317,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4328,10 +4328,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4339,10 +4339,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4367,17 +4367,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4385,10 +4385,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4396,10 +4396,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4407,10 +4407,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4418,10 +4418,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4446,17 +4446,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4464,10 +4464,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4475,10 +4475,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4486,10 +4486,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4497,10 +4497,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4525,17 +4525,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4543,10 +4543,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4554,10 +4554,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4565,10 +4565,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4576,10 +4576,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4609,8 +4609,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -4637,8 +4637,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -4661,13 +4661,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -4691,17 +4691,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4709,10 +4709,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4720,10 +4720,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4731,10 +4731,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4742,10 +4742,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4770,17 +4770,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4788,10 +4788,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4799,10 +4799,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4810,10 +4810,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4821,10 +4821,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4849,17 +4849,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4867,10 +4867,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4878,10 +4878,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4889,10 +4889,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4900,10 +4900,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4928,17 +4928,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4946,10 +4946,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4957,10 +4957,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4968,10 +4968,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4979,10 +4979,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5007,17 +5007,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5025,10 +5025,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5036,10 +5036,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5047,10 +5047,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5058,10 +5058,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5086,17 +5086,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5104,10 +5104,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5115,10 +5115,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5126,10 +5126,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5137,10 +5137,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5170,8 +5170,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -5198,8 +5198,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -5222,13 +5222,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -5252,17 +5252,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5270,10 +5270,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5281,10 +5281,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5292,10 +5292,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5303,10 +5303,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5331,17 +5331,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5349,10 +5349,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5360,10 +5360,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5371,10 +5371,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5382,10 +5382,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5410,17 +5410,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5428,10 +5428,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5439,10 +5439,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5450,10 +5450,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5461,10 +5461,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5489,17 +5489,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5507,10 +5507,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5518,10 +5518,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5529,10 +5529,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5540,10 +5540,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5568,17 +5568,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5586,10 +5586,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5597,10 +5597,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5608,10 +5608,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5619,10 +5619,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5647,17 +5647,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5665,10 +5665,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5676,10 +5676,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5687,10 +5687,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5698,10 +5698,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5731,8 +5731,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -5759,8 +5759,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -5783,13 +5783,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -5813,17 +5813,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5831,10 +5831,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5842,10 +5842,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5853,10 +5853,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5864,10 +5864,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5892,17 +5892,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5910,10 +5910,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5921,10 +5921,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5932,10 +5932,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5943,10 +5943,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5971,17 +5971,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5989,10 +5989,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6000,10 +6000,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6011,10 +6011,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6022,10 +6022,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6050,17 +6050,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6068,10 +6068,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6079,10 +6079,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6090,10 +6090,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6101,10 +6101,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6129,17 +6129,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6147,10 +6147,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6158,10 +6158,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6169,10 +6169,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6180,10 +6180,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6208,17 +6208,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6226,10 +6226,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6237,10 +6237,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6248,10 +6248,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6259,10 +6259,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6292,8 +6292,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -6320,8 +6320,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -6345,13 +6345,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -6375,17 +6375,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6393,10 +6393,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6404,10 +6404,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6415,10 +6415,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6426,10 +6426,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6454,17 +6454,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6472,10 +6472,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6483,10 +6483,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6494,10 +6494,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6505,10 +6505,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6533,17 +6533,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6551,10 +6551,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6562,10 +6562,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6573,10 +6573,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6584,10 +6584,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6612,17 +6612,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6630,10 +6630,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6641,10 +6641,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6652,10 +6652,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6663,10 +6663,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6691,17 +6691,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6709,10 +6709,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6720,10 +6720,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6731,10 +6731,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6742,10 +6742,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6770,17 +6770,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6788,10 +6788,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6799,10 +6799,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6810,10 +6810,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6821,10 +6821,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6854,8 +6854,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -6882,8 +6882,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -6907,13 +6907,13 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -6937,17 +6937,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6955,10 +6955,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6966,10 +6966,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6977,10 +6977,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -6988,10 +6988,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7016,17 +7016,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7034,10 +7034,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7045,10 +7045,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7056,10 +7056,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7067,10 +7067,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7095,17 +7095,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7113,10 +7113,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7124,10 +7124,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7135,10 +7135,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7146,10 +7146,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7174,17 +7174,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7192,10 +7192,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7203,10 +7203,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7214,10 +7214,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7225,10 +7225,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7253,17 +7253,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7271,10 +7271,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7282,10 +7282,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7293,10 +7293,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7304,10 +7304,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7332,17 +7332,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7350,10 +7350,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7361,10 +7361,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7372,10 +7372,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7383,10 +7383,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7416,8 +7416,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -7444,8 +7444,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -7469,13 +7469,13 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -7499,17 +7499,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7517,10 +7517,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7528,10 +7528,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7539,10 +7539,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7550,10 +7550,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7578,17 +7578,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7596,10 +7596,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7607,10 +7607,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7618,10 +7618,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7629,10 +7629,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7657,17 +7657,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7675,10 +7675,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7686,10 +7686,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7697,10 +7697,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7708,10 +7708,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7736,17 +7736,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7754,10 +7754,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7765,10 +7765,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7776,10 +7776,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7787,10 +7787,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7815,17 +7815,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7833,10 +7833,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7844,10 +7844,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7855,10 +7855,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7866,10 +7866,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7894,17 +7894,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7912,10 +7912,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7923,10 +7923,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7934,10 +7934,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7945,10 +7945,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -7978,8 +7978,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -8006,8 +8006,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -8030,13 +8030,13 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -8060,17 +8060,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8078,10 +8078,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8089,10 +8089,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8100,10 +8100,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8111,10 +8111,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8139,17 +8139,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8157,10 +8157,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8168,10 +8168,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8179,10 +8179,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8190,10 +8190,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8218,17 +8218,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8236,10 +8236,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8247,10 +8247,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8258,10 +8258,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8269,10 +8269,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8297,17 +8297,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8315,10 +8315,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8326,10 +8326,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8337,10 +8337,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8348,10 +8348,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8376,17 +8376,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8394,10 +8394,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8405,10 +8405,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8416,10 +8416,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8427,10 +8427,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8455,17 +8455,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4a5e2a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8473,10 +8473,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8a8a3a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8484,10 +8484,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="e8c020"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8495,10 +8495,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3a8fd0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8506,10 +8506,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8bc34a"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -8539,8 +8539,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -8567,8 +8567,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -8591,7 +8591,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -8606,9 +8606,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -8628,9 +8628,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -8650,9 +8650,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -8672,9 +8672,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -8694,9 +8694,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <c:chart r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -8716,9 +8716,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+          <c:chart r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -8738,9 +8738,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+          <c:chart r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -8750,7 +8750,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -8765,9 +8765,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -8787,9 +8787,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -8809,9 +8809,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -8831,9 +8831,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -8853,9 +8853,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <c:chart r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -8875,9 +8875,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+          <c:chart r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -8897,9 +8897,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+          <c:chart r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -8919,9 +8919,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+          <c:chart r:id="rId8"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9738,24 +9738,16 @@
       <c r="B3" s="4" t="n">
         <v>1316</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="C3" s="4" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr"/>
       <c r="E3" s="4" t="n">
         <v>464</v>
       </c>
-      <c r="F3" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="F3" s="4" t="inlineStr"/>
       <c r="G3" s="4" t="n">
         <v>1206</v>
       </c>
-      <c r="H3" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="4" t="n">
         <v>1957</v>
       </c>
@@ -9768,9 +9760,7 @@
       <c r="L3" s="4" t="n">
         <v>902</v>
       </c>
-      <c r="M3" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="M3" s="4" t="inlineStr"/>
       <c r="N3" s="4" t="n">
         <v>1817</v>
       </c>
@@ -9798,9 +9788,7 @@
       <c r="V3" s="4" t="n">
         <v>1516</v>
       </c>
-      <c r="W3" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="W3" s="4" t="inlineStr"/>
       <c r="X3" s="4" t="n">
         <v>1008</v>
       </c>
@@ -9813,9 +9801,7 @@
       <c r="AA3" s="4" t="n">
         <v>1463</v>
       </c>
-      <c r="AB3" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB3" s="4" t="inlineStr"/>
       <c r="AC3" s="4" t="n">
         <v>956</v>
       </c>
@@ -9828,9 +9814,7 @@
       <c r="AF3" s="4" t="n">
         <v>2099</v>
       </c>
-      <c r="AG3" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG3" s="4" t="inlineStr"/>
       <c r="AH3" s="4" t="n">
         <v>1334</v>
       </c>
@@ -9843,9 +9827,7 @@
       <c r="AK3" s="4" t="n">
         <v>3411</v>
       </c>
-      <c r="AL3" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AL3" s="4" t="inlineStr"/>
       <c r="AM3" s="4" t="n">
         <v>1524</v>
       </c>
@@ -9858,9 +9840,7 @@
       <c r="AP3" s="4" t="n">
         <v>2918</v>
       </c>
-      <c r="AQ3" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AQ3" s="4" t="inlineStr"/>
       <c r="AR3" s="4" t="n">
         <v>1005</v>
       </c>
@@ -9873,9 +9853,7 @@
       <c r="AU3" s="4" t="n">
         <v>3090</v>
       </c>
-      <c r="AV3" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AV3" s="4" t="inlineStr"/>
       <c r="AW3" s="4" t="n">
         <v>1085</v>
       </c>
@@ -9888,9 +9866,7 @@
       <c r="AZ3" s="4" t="n">
         <v>1853</v>
       </c>
-      <c r="BA3" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA3" s="4" t="inlineStr"/>
       <c r="BB3" s="4" t="n">
         <v>1356</v>
       </c>
@@ -9935,24 +9911,16 @@
       <c r="B4" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
       <c r="E4" s="4" t="n">
         <v>138</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="H4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="H4" s="4" t="inlineStr"/>
       <c r="I4" s="4" t="n">
         <v>355</v>
       </c>
@@ -9965,9 +9933,7 @@
       <c r="L4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="M4" s="4" t="inlineStr"/>
       <c r="N4" s="4" t="n">
         <v>239</v>
       </c>
@@ -9995,9 +9961,7 @@
       <c r="V4" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="W4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="W4" s="4" t="inlineStr"/>
       <c r="X4" s="4" t="n">
         <v>26</v>
       </c>
@@ -10010,9 +9974,7 @@
       <c r="AA4" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AB4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB4" s="4" t="inlineStr"/>
       <c r="AC4" s="4" t="n">
         <v>81</v>
       </c>
@@ -10025,9 +9987,7 @@
       <c r="AF4" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG4" s="4" t="inlineStr"/>
       <c r="AH4" s="4" t="n">
         <v>6</v>
       </c>
@@ -10040,9 +10000,7 @@
       <c r="AK4" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="AL4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AL4" s="4" t="inlineStr"/>
       <c r="AM4" s="4" t="n">
         <v>23</v>
       </c>
@@ -10055,9 +10013,7 @@
       <c r="AP4" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="AQ4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AQ4" s="4" t="inlineStr"/>
       <c r="AR4" s="4" t="n">
         <v>29</v>
       </c>
@@ -10070,9 +10026,7 @@
       <c r="AU4" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="AV4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AV4" s="4" t="inlineStr"/>
       <c r="AW4" s="4" t="n">
         <v>136</v>
       </c>
@@ -10085,9 +10039,7 @@
       <c r="AZ4" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="BA4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA4" s="4" t="inlineStr"/>
       <c r="BB4" s="4" t="n">
         <v>146</v>
       </c>
@@ -10132,24 +10084,16 @@
       <c r="B5" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="4" t="n">
         <v>137</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="H5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="n">
         <v>63</v>
       </c>
@@ -10162,9 +10106,7 @@
       <c r="L5" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="M5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="M5" s="4" t="inlineStr"/>
       <c r="N5" s="4" t="n">
         <v>136</v>
       </c>
@@ -10192,9 +10134,7 @@
       <c r="V5" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="W5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="n">
         <v>192</v>
       </c>
@@ -10207,9 +10147,7 @@
       <c r="AA5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="AB5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB5" s="4" t="inlineStr"/>
       <c r="AC5" s="4" t="n">
         <v>104</v>
       </c>
@@ -10222,9 +10160,7 @@
       <c r="AF5" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="AG5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG5" s="4" t="inlineStr"/>
       <c r="AH5" s="4" t="n">
         <v>203</v>
       </c>
@@ -10237,9 +10173,7 @@
       <c r="AK5" s="4" t="n">
         <v>132</v>
       </c>
-      <c r="AL5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AL5" s="4" t="inlineStr"/>
       <c r="AM5" s="4" t="n">
         <v>180</v>
       </c>
@@ -10252,9 +10186,7 @@
       <c r="AP5" s="4" t="n">
         <v>131</v>
       </c>
-      <c r="AQ5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AQ5" s="4" t="inlineStr"/>
       <c r="AR5" s="4" t="n">
         <v>80</v>
       </c>
@@ -10267,9 +10199,7 @@
       <c r="AU5" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="AV5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AV5" s="4" t="inlineStr"/>
       <c r="AW5" s="4" t="n">
         <v>215</v>
       </c>
@@ -10282,9 +10212,7 @@
       <c r="AZ5" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="BA5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA5" s="4" t="inlineStr"/>
       <c r="BB5" s="4" t="n">
         <v>259</v>
       </c>
@@ -10329,24 +10257,16 @@
       <c r="B6" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
       <c r="E6" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H6" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="H6" s="4" t="inlineStr"/>
       <c r="I6" s="4" t="n">
         <v>84</v>
       </c>
@@ -10359,9 +10279,7 @@
       <c r="L6" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="M6" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="M6" s="4" t="inlineStr"/>
       <c r="N6" s="4" t="n">
         <v>234</v>
       </c>
@@ -10389,9 +10307,7 @@
       <c r="V6" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="W6" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="W6" s="4" t="inlineStr"/>
       <c r="X6" s="4" t="n">
         <v>378</v>
       </c>
@@ -10404,9 +10320,7 @@
       <c r="AA6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AB6" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB6" s="4" t="inlineStr"/>
       <c r="AC6" s="4" t="n">
         <v>334</v>
       </c>
@@ -10419,9 +10333,7 @@
       <c r="AF6" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="AG6" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG6" s="4" t="inlineStr"/>
       <c r="AH6" s="4" t="n">
         <v>724</v>
       </c>
@@ -10434,9 +10346,7 @@
       <c r="AK6" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="AL6" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AL6" s="4" t="inlineStr"/>
       <c r="AM6" s="4" t="n">
         <v>608</v>
       </c>
@@ -10449,9 +10359,7 @@
       <c r="AP6" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="AQ6" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AQ6" s="4" t="inlineStr"/>
       <c r="AR6" s="4" t="n">
         <v>448</v>
       </c>
@@ -10464,9 +10372,7 @@
       <c r="AU6" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="AV6" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AV6" s="4" t="inlineStr"/>
       <c r="AW6" s="4" t="n">
         <v>228</v>
       </c>
@@ -10479,9 +10385,7 @@
       <c r="AZ6" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="BA6" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA6" s="4" t="inlineStr"/>
       <c r="BB6" s="4" t="n">
         <v>356</v>
       </c>
@@ -10526,24 +10430,16 @@
       <c r="B7" s="4" t="n">
         <v>445</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>501</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="4" t="n">
         <v>111</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="n">
         <v>541</v>
       </c>
-      <c r="H7" s="4" t="n">
-        <v>364</v>
-      </c>
+      <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="n">
         <v>709</v>
       </c>
@@ -10556,9 +10452,7 @@
       <c r="L7" s="4" t="n">
         <v>367</v>
       </c>
-      <c r="M7" s="4" t="n">
-        <v>402</v>
-      </c>
+      <c r="M7" s="4" t="inlineStr"/>
       <c r="N7" s="4" t="n">
         <v>416</v>
       </c>
@@ -10572,7 +10466,7 @@
         <v>330</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>498</v>
+        <v>822</v>
       </c>
       <c r="S7" s="4" t="n">
         <v>368</v>
@@ -10586,9 +10480,7 @@
       <c r="V7" s="4" t="n">
         <v>239</v>
       </c>
-      <c r="W7" s="4" t="n">
-        <v>541</v>
-      </c>
+      <c r="W7" s="4" t="inlineStr"/>
       <c r="X7" s="4" t="n">
         <v>691</v>
       </c>
@@ -10601,9 +10493,7 @@
       <c r="AA7" s="4" t="n">
         <v>185</v>
       </c>
-      <c r="AB7" s="4" t="n">
-        <v>540</v>
-      </c>
+      <c r="AB7" s="4" t="inlineStr"/>
       <c r="AC7" s="4" t="n">
         <v>741</v>
       </c>
@@ -10616,9 +10506,7 @@
       <c r="AF7" s="4" t="n">
         <v>616</v>
       </c>
-      <c r="AG7" s="4" t="n">
-        <v>531</v>
-      </c>
+      <c r="AG7" s="4" t="inlineStr"/>
       <c r="AH7" s="4" t="n">
         <v>792</v>
       </c>
@@ -10631,9 +10519,7 @@
       <c r="AK7" s="4" t="n">
         <v>633</v>
       </c>
-      <c r="AL7" s="4" t="n">
-        <v>490</v>
-      </c>
+      <c r="AL7" s="4" t="inlineStr"/>
       <c r="AM7" s="4" t="n">
         <v>882</v>
       </c>
@@ -10646,9 +10532,7 @@
       <c r="AP7" s="4" t="n">
         <v>615</v>
       </c>
-      <c r="AQ7" s="4" t="n">
-        <v>484</v>
-      </c>
+      <c r="AQ7" s="4" t="inlineStr"/>
       <c r="AR7" s="4" t="n">
         <v>1137</v>
       </c>
@@ -10661,9 +10545,7 @@
       <c r="AU7" s="4" t="n">
         <v>938</v>
       </c>
-      <c r="AV7" s="4" t="n">
-        <v>463</v>
-      </c>
+      <c r="AV7" s="4" t="inlineStr"/>
       <c r="AW7" s="4" t="n">
         <v>1469</v>
       </c>
@@ -10676,9 +10558,7 @@
       <c r="AZ7" s="4" t="n">
         <v>1341</v>
       </c>
-      <c r="BA7" s="4" t="n">
-        <v>457</v>
-      </c>
+      <c r="BA7" s="4" t="inlineStr"/>
       <c r="BB7" s="4" t="n">
         <v>1564</v>
       </c>
@@ -10692,7 +10572,7 @@
         <v>1464</v>
       </c>
       <c r="BF7" s="4" t="n">
-        <v>459</v>
+        <v>818</v>
       </c>
       <c r="BG7" s="4" t="n">
         <v>1668</v>
@@ -10723,24 +10603,16 @@
       <c r="B8" s="4" t="n">
         <v>101</v>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>962</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
       <c r="E8" s="4" t="n">
         <v>297</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="n">
         <v>176</v>
       </c>
-      <c r="H8" s="4" t="n">
-        <v>1024</v>
-      </c>
+      <c r="H8" s="4" t="inlineStr"/>
       <c r="I8" s="4" t="n">
         <v>947</v>
       </c>
@@ -10753,9 +10625,7 @@
       <c r="L8" s="4" t="n">
         <v>149</v>
       </c>
-      <c r="M8" s="4" t="n">
-        <v>1045</v>
-      </c>
+      <c r="M8" s="4" t="inlineStr"/>
       <c r="N8" s="4" t="n">
         <v>1120</v>
       </c>
@@ -10769,7 +10639,7 @@
         <v>114</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1053</v>
+        <v>1388</v>
       </c>
       <c r="S8" s="4" t="n">
         <v>134</v>
@@ -10783,9 +10653,7 @@
       <c r="V8" s="4" t="n">
         <v>119</v>
       </c>
-      <c r="W8" s="4" t="n">
-        <v>1106</v>
-      </c>
+      <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="n">
         <v>881</v>
       </c>
@@ -10798,9 +10666,7 @@
       <c r="AA8" s="4" t="n">
         <v>106</v>
       </c>
-      <c r="AB8" s="4" t="n">
-        <v>1014</v>
-      </c>
+      <c r="AB8" s="4" t="inlineStr"/>
       <c r="AC8" s="4" t="n">
         <v>725</v>
       </c>
@@ -10813,9 +10679,7 @@
       <c r="AF8" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="AG8" s="4" t="n">
-        <v>987</v>
-      </c>
+      <c r="AG8" s="4" t="inlineStr"/>
       <c r="AH8" s="4" t="n">
         <v>832</v>
       </c>
@@ -10828,9 +10692,7 @@
       <c r="AK8" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="AL8" s="4" t="n">
-        <v>968</v>
-      </c>
+      <c r="AL8" s="4" t="inlineStr"/>
       <c r="AM8" s="4" t="n">
         <v>747</v>
       </c>
@@ -10843,9 +10705,7 @@
       <c r="AP8" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="AQ8" s="4" t="n">
-        <v>901</v>
-      </c>
+      <c r="AQ8" s="4" t="inlineStr"/>
       <c r="AR8" s="4" t="n">
         <v>902</v>
       </c>
@@ -10858,9 +10718,7 @@
       <c r="AU8" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="AV8" s="4" t="n">
-        <v>795</v>
-      </c>
+      <c r="AV8" s="4" t="inlineStr"/>
       <c r="AW8" s="4" t="n">
         <v>942</v>
       </c>
@@ -10873,9 +10731,7 @@
       <c r="AZ8" s="4" t="n">
         <v>104</v>
       </c>
-      <c r="BA8" s="4" t="n">
-        <v>690</v>
-      </c>
+      <c r="BA8" s="4" t="inlineStr"/>
       <c r="BB8" s="4" t="n">
         <v>962</v>
       </c>
@@ -10889,7 +10745,7 @@
         <v>103</v>
       </c>
       <c r="BF8" s="4" t="n">
-        <v>640</v>
+        <v>1056</v>
       </c>
       <c r="BG8" s="4" t="n">
         <v>958</v>
@@ -10920,24 +10776,16 @@
       <c r="B9" s="4" t="n">
         <v>1445</v>
       </c>
-      <c r="C9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="n">
         <v>444</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="n">
         <v>1485</v>
       </c>
-      <c r="H9" s="4" t="n">
-        <v>9</v>
-      </c>
+      <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="4" t="n">
         <v>626</v>
       </c>
@@ -10950,9 +10798,7 @@
       <c r="L9" s="4" t="n">
         <v>1132</v>
       </c>
-      <c r="M9" s="4" t="n">
-        <v>11</v>
-      </c>
+      <c r="M9" s="4" t="inlineStr"/>
       <c r="N9" s="4" t="n">
         <v>593</v>
       </c>
@@ -10966,7 +10812,7 @@
         <v>1080</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>8</v>
+        <v>921</v>
       </c>
       <c r="S9" s="4" t="n">
         <v>168</v>
@@ -10980,9 +10826,7 @@
       <c r="V9" s="4" t="n">
         <v>1011</v>
       </c>
-      <c r="W9" s="4" t="n">
-        <v>17</v>
-      </c>
+      <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="n">
         <v>377</v>
       </c>
@@ -10995,9 +10839,7 @@
       <c r="AA9" s="4" t="n">
         <v>979</v>
       </c>
-      <c r="AB9" s="4" t="n">
-        <v>17</v>
-      </c>
+      <c r="AB9" s="4" t="inlineStr"/>
       <c r="AC9" s="4" t="n">
         <v>351</v>
       </c>
@@ -11010,9 +10852,7 @@
       <c r="AF9" s="4" t="n">
         <v>929</v>
       </c>
-      <c r="AG9" s="4" t="n">
-        <v>25</v>
-      </c>
+      <c r="AG9" s="4" t="inlineStr"/>
       <c r="AH9" s="4" t="n">
         <v>378</v>
       </c>
@@ -11025,9 +10865,7 @@
       <c r="AK9" s="4" t="n">
         <v>750</v>
       </c>
-      <c r="AL9" s="4" t="n">
-        <v>29</v>
-      </c>
+      <c r="AL9" s="4" t="inlineStr"/>
       <c r="AM9" s="4" t="n">
         <v>350</v>
       </c>
@@ -11040,9 +10878,7 @@
       <c r="AP9" s="4" t="n">
         <v>608</v>
       </c>
-      <c r="AQ9" s="4" t="n">
-        <v>40</v>
-      </c>
+      <c r="AQ9" s="4" t="inlineStr"/>
       <c r="AR9" s="4" t="n">
         <v>350</v>
       </c>
@@ -11055,9 +10891,7 @@
       <c r="AU9" s="4" t="n">
         <v>597</v>
       </c>
-      <c r="AV9" s="4" t="n">
-        <v>49</v>
-      </c>
+      <c r="AV9" s="4" t="inlineStr"/>
       <c r="AW9" s="4" t="n">
         <v>291</v>
       </c>
@@ -11070,9 +10904,7 @@
       <c r="AZ9" s="4" t="n">
         <v>570</v>
       </c>
-      <c r="BA9" s="4" t="n">
-        <v>60</v>
-      </c>
+      <c r="BA9" s="4" t="inlineStr"/>
       <c r="BB9" s="4" t="n">
         <v>215</v>
       </c>
@@ -11086,7 +10918,7 @@
         <v>633</v>
       </c>
       <c r="BF9" s="4" t="n">
-        <v>58</v>
+        <v>944</v>
       </c>
       <c r="BG9" s="4" t="n">
         <v>165</v>
@@ -11117,24 +10949,16 @@
       <c r="B10" s="4" t="n">
         <v>1822</v>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
       <c r="E10" s="4" t="n">
         <v>439</v>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="n">
         <v>1803</v>
       </c>
-      <c r="H10" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="H10" s="4" t="inlineStr"/>
       <c r="I10" s="4" t="n">
         <v>96</v>
       </c>
@@ -11147,9 +10971,7 @@
       <c r="L10" s="4" t="n">
         <v>1902</v>
       </c>
-      <c r="M10" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="M10" s="4" t="inlineStr"/>
       <c r="N10" s="4" t="n">
         <v>288</v>
       </c>
@@ -11163,7 +10985,7 @@
         <v>2088</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="S10" s="4" t="n">
         <v>377</v>
@@ -11177,9 +10999,7 @@
       <c r="V10" s="4" t="n">
         <v>2151</v>
       </c>
-      <c r="W10" s="4" t="n">
-        <v>4</v>
-      </c>
+      <c r="W10" s="4" t="inlineStr"/>
       <c r="X10" s="4" t="n">
         <v>421</v>
       </c>
@@ -11192,9 +11012,7 @@
       <c r="AA10" s="4" t="n">
         <v>2475</v>
       </c>
-      <c r="AB10" s="4" t="n">
-        <v>13</v>
-      </c>
+      <c r="AB10" s="4" t="inlineStr"/>
       <c r="AC10" s="4" t="n">
         <v>469</v>
       </c>
@@ -11207,9 +11025,7 @@
       <c r="AF10" s="4" t="n">
         <v>2749</v>
       </c>
-      <c r="AG10" s="4" t="n">
-        <v>33</v>
-      </c>
+      <c r="AG10" s="4" t="inlineStr"/>
       <c r="AH10" s="4" t="n">
         <v>498</v>
       </c>
@@ -11222,9 +11038,7 @@
       <c r="AK10" s="4" t="n">
         <v>2742</v>
       </c>
-      <c r="AL10" s="4" t="n">
-        <v>34</v>
-      </c>
+      <c r="AL10" s="4" t="inlineStr"/>
       <c r="AM10" s="4" t="n">
         <v>612</v>
       </c>
@@ -11237,9 +11051,7 @@
       <c r="AP10" s="4" t="n">
         <v>2813</v>
       </c>
-      <c r="AQ10" s="4" t="n">
-        <v>59</v>
-      </c>
+      <c r="AQ10" s="4" t="inlineStr"/>
       <c r="AR10" s="4" t="n">
         <v>444</v>
       </c>
@@ -11252,9 +11064,7 @@
       <c r="AU10" s="4" t="n">
         <v>2702</v>
       </c>
-      <c r="AV10" s="4" t="n">
-        <v>73</v>
-      </c>
+      <c r="AV10" s="4" t="inlineStr"/>
       <c r="AW10" s="4" t="n">
         <v>468</v>
       </c>
@@ -11267,9 +11077,7 @@
       <c r="AZ10" s="4" t="n">
         <v>2438</v>
       </c>
-      <c r="BA10" s="4" t="n">
-        <v>66</v>
-      </c>
+      <c r="BA10" s="4" t="inlineStr"/>
       <c r="BB10" s="4" t="n">
         <v>446</v>
       </c>
@@ -11283,7 +11091,7 @@
         <v>2341</v>
       </c>
       <c r="BF10" s="4" t="n">
-        <v>66</v>
+        <v>373</v>
       </c>
       <c r="BG10" s="4" t="n">
         <v>427</v>
@@ -11314,24 +11122,16 @@
       <c r="B11" s="4" t="n">
         <v>586</v>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="n">
         <v>1796</v>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="n">
         <v>571</v>
       </c>
-      <c r="H11" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="n">
         <v>123</v>
       </c>
@@ -11344,9 +11144,7 @@
       <c r="L11" s="4" t="n">
         <v>665</v>
       </c>
-      <c r="M11" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="M11" s="4" t="inlineStr"/>
       <c r="N11" s="4" t="n">
         <v>137</v>
       </c>
@@ -11360,7 +11158,7 @@
         <v>657</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S11" s="4" t="n">
         <v>135</v>
@@ -11374,9 +11172,7 @@
       <c r="V11" s="4" t="n">
         <v>755</v>
       </c>
-      <c r="W11" s="4" t="n">
-        <v>9</v>
-      </c>
+      <c r="W11" s="4" t="inlineStr"/>
       <c r="X11" s="4" t="n">
         <v>166</v>
       </c>
@@ -11389,9 +11185,7 @@
       <c r="AA11" s="4" t="n">
         <v>785</v>
       </c>
-      <c r="AB11" s="4" t="n">
-        <v>15</v>
-      </c>
+      <c r="AB11" s="4" t="inlineStr"/>
       <c r="AC11" s="4" t="n">
         <v>258</v>
       </c>
@@ -11404,9 +11198,7 @@
       <c r="AF11" s="4" t="n">
         <v>797</v>
       </c>
-      <c r="AG11" s="4" t="n">
-        <v>25</v>
-      </c>
+      <c r="AG11" s="4" t="inlineStr"/>
       <c r="AH11" s="4" t="n">
         <v>271</v>
       </c>
@@ -11419,9 +11211,7 @@
       <c r="AK11" s="4" t="n">
         <v>784</v>
       </c>
-      <c r="AL11" s="4" t="n">
-        <v>25</v>
-      </c>
+      <c r="AL11" s="4" t="inlineStr"/>
       <c r="AM11" s="4" t="n">
         <v>252</v>
       </c>
@@ -11434,9 +11224,7 @@
       <c r="AP11" s="4" t="n">
         <v>796</v>
       </c>
-      <c r="AQ11" s="4" t="n">
-        <v>30</v>
-      </c>
+      <c r="AQ11" s="4" t="inlineStr"/>
       <c r="AR11" s="4" t="n">
         <v>292</v>
       </c>
@@ -11449,9 +11237,7 @@
       <c r="AU11" s="4" t="n">
         <v>1052</v>
       </c>
-      <c r="AV11" s="4" t="n">
-        <v>48</v>
-      </c>
+      <c r="AV11" s="4" t="inlineStr"/>
       <c r="AW11" s="4" t="n">
         <v>293</v>
       </c>
@@ -11464,9 +11250,7 @@
       <c r="AZ11" s="4" t="n">
         <v>1047</v>
       </c>
-      <c r="BA11" s="4" t="n">
-        <v>46</v>
-      </c>
+      <c r="BA11" s="4" t="inlineStr"/>
       <c r="BB11" s="4" t="n">
         <v>263</v>
       </c>
@@ -11480,7 +11264,7 @@
         <v>1308</v>
       </c>
       <c r="BF11" s="4" t="n">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="BG11" s="4" t="n">
         <v>277</v>
@@ -11511,24 +11295,16 @@
       <c r="B12" s="4" t="n">
         <v>162</v>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
       <c r="E12" s="4" t="n">
         <v>898</v>
       </c>
-      <c r="F12" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="n">
         <v>175</v>
       </c>
-      <c r="H12" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="H12" s="4" t="inlineStr"/>
       <c r="I12" s="4" t="n">
         <v>106</v>
       </c>
@@ -11541,9 +11317,7 @@
       <c r="L12" s="4" t="n">
         <v>267</v>
       </c>
-      <c r="M12" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="M12" s="4" t="inlineStr"/>
       <c r="N12" s="4" t="n">
         <v>178</v>
       </c>
@@ -11557,7 +11331,7 @@
         <v>259</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="S12" s="4" t="n">
         <v>171</v>
@@ -11571,9 +11345,7 @@
       <c r="V12" s="4" t="n">
         <v>282</v>
       </c>
-      <c r="W12" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="W12" s="4" t="inlineStr"/>
       <c r="X12" s="4" t="n">
         <v>484</v>
       </c>
@@ -11586,9 +11358,7 @@
       <c r="AA12" s="4" t="n">
         <v>437</v>
       </c>
-      <c r="AB12" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB12" s="4" t="inlineStr"/>
       <c r="AC12" s="4" t="n">
         <v>511</v>
       </c>
@@ -11601,9 +11371,7 @@
       <c r="AF12" s="4" t="n">
         <v>547</v>
       </c>
-      <c r="AG12" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG12" s="4" t="inlineStr"/>
       <c r="AH12" s="4" t="n">
         <v>530</v>
       </c>
@@ -11616,9 +11384,7 @@
       <c r="AK12" s="4" t="n">
         <v>640</v>
       </c>
-      <c r="AL12" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AL12" s="4" t="inlineStr"/>
       <c r="AM12" s="4" t="n">
         <v>893</v>
       </c>
@@ -11631,9 +11397,7 @@
       <c r="AP12" s="4" t="n">
         <v>676</v>
       </c>
-      <c r="AQ12" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AQ12" s="4" t="inlineStr"/>
       <c r="AR12" s="4" t="n">
         <v>1052</v>
       </c>
@@ -11646,9 +11410,7 @@
       <c r="AU12" s="4" t="n">
         <v>671</v>
       </c>
-      <c r="AV12" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AV12" s="4" t="inlineStr"/>
       <c r="AW12" s="4" t="n">
         <v>924</v>
       </c>
@@ -11661,9 +11423,7 @@
       <c r="AZ12" s="4" t="n">
         <v>626</v>
       </c>
-      <c r="BA12" s="4" t="n">
-        <v>6</v>
-      </c>
+      <c r="BA12" s="4" t="inlineStr"/>
       <c r="BB12" s="4" t="n">
         <v>666</v>
       </c>
@@ -11677,7 +11437,7 @@
         <v>602</v>
       </c>
       <c r="BF12" s="4" t="n">
-        <v>6</v>
+        <v>161</v>
       </c>
       <c r="BG12" s="4" t="n">
         <v>553</v>
@@ -11807,23 +11567,13 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
-        <v>1601.4</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>1545.7</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1514</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1428.5</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1324.8</v>
-      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
       <c r="G4" s="6" t="n">
-        <v>1279.9</v>
+        <v>10714.2</v>
       </c>
     </row>
     <row r="5">
@@ -11833,22 +11583,22 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>6962.2</v>
+        <v>10173.9</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>5886.7</v>
+        <v>10179.3</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>6034.1</v>
+        <v>8878.299999999999</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>6020.3</v>
+        <v>9341.5</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>6095.9</v>
+        <v>11340.3</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>6458.6</v>
+        <v>11002.8</v>
       </c>
     </row>
     <row r="6">
@@ -11864,7 +11614,7 @@
         <v>8824.200000000001</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>8666.4</v>
+        <v>8739.9</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>9103</v>
@@ -11976,21 +11726,11 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n">
         <v>0</v>
       </c>
@@ -12145,23 +11885,13 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n">
-        <v>1543</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>1486.7</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>1424.5</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>1307.1</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>1206.9</v>
-      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="n">
-        <v>1156.5</v>
+        <v>3488.3</v>
       </c>
     </row>
     <row r="23">
@@ -12202,7 +11932,7 @@
         <v>1361</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>1371.6</v>
+        <v>1445.1</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>1562.5</v>
@@ -12314,23 +12044,13 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="C31" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="D31" s="6" t="n">
-        <v>89.5</v>
-      </c>
-      <c r="E31" s="6" t="n">
-        <v>121.4</v>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>117.9</v>
-      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
       <c r="G31" s="6" t="n">
-        <v>123.4</v>
+        <v>7225.9</v>
       </c>
     </row>
     <row r="32">
@@ -12340,22 +12060,22 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>1969.2</v>
+        <v>5180.9</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>2465</v>
+        <v>6757.6</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>2532.2</v>
+        <v>5376.4</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>2430.7</v>
+        <v>5751.9</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>2108.2</v>
+        <v>7352.6</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>2323.4</v>
+        <v>6867.6</v>
       </c>
     </row>
     <row r="33">
@@ -12483,21 +12203,11 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="B40" s="7" t="n"/>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n">
         <v>0</v>
       </c>
@@ -12509,22 +12219,22 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.1794</v>
+        <v>0.1228</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>0.17</v>
+        <v>0.0983</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0.1146</v>
+        <v>0.0779</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>0.0963</v>
+        <v>0.062</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>0.1519</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>0.16</v>
+        <v>0.0939</v>
       </c>
     </row>
     <row r="42">
@@ -12540,7 +12250,7 @@
         <v>0.0239</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>0.0354</v>
+        <v>0.0351</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>0.018</v>
@@ -12652,23 +12362,13 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B49" s="7" t="n">
-        <v>0.9635</v>
-      </c>
-      <c r="C49" s="7" t="n">
-        <v>0.9619</v>
-      </c>
-      <c r="D49" s="7" t="n">
-        <v>0.9409</v>
-      </c>
-      <c r="E49" s="7" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="F49" s="7" t="n">
-        <v>0.911</v>
-      </c>
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="7" t="n"/>
+      <c r="E49" s="7" t="n"/>
+      <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n">
-        <v>0.9036</v>
+        <v>0.3256</v>
       </c>
     </row>
     <row r="50">
@@ -12678,22 +12378,22 @@
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>0.5377</v>
+        <v>0.368</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>0.4113</v>
+        <v>0.2378</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0.4657</v>
+        <v>0.3165</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>0.5</v>
+        <v>0.3222</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>0.5022</v>
+        <v>0.27</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>0.4802</v>
+        <v>0.2819</v>
       </c>
     </row>
     <row r="51">
@@ -12709,7 +12409,7 @@
         <v>0.1542</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0.1583</v>
+        <v>0.1653</v>
       </c>
       <c r="E51" s="7" t="n">
         <v>0.1716</v>
@@ -12821,23 +12521,13 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B58" s="7" t="n">
-        <v>0.0365</v>
-      </c>
-      <c r="C58" s="7" t="n">
-        <v>0.0381</v>
-      </c>
-      <c r="D58" s="7" t="n">
-        <v>0.0591</v>
-      </c>
-      <c r="E58" s="7" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="F58" s="7" t="n">
-        <v>0.089</v>
-      </c>
+      <c r="B58" s="7" t="n"/>
+      <c r="C58" s="7" t="n"/>
+      <c r="D58" s="7" t="n"/>
+      <c r="E58" s="7" t="n"/>
+      <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n">
-        <v>0.0964</v>
+        <v>0.6744</v>
       </c>
     </row>
     <row r="59">
@@ -12847,22 +12537,22 @@
         </is>
       </c>
       <c r="B59" s="7" t="n">
-        <v>0.2828</v>
+        <v>0.5092</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>0.4187</v>
+        <v>0.6639</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>0.4196</v>
+        <v>0.6056</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>0.4038</v>
+        <v>0.6157</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>0.3458</v>
+        <v>0.6484</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>0.3597</v>
+        <v>0.6242</v>
       </c>
     </row>
     <row r="60">
@@ -12878,7 +12568,7 @@
         <v>0.8219</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>0.8063</v>
+        <v>0.7995</v>
       </c>
       <c r="E60" s="7" t="n">
         <v>0.8104</v>
@@ -13021,23 +12711,13 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
-        <v>1601.4</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>1545.7</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1514</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1428.5</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1324.8</v>
-      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
       <c r="G4" s="6" t="n">
-        <v>1279.9</v>
+        <v>10714.2</v>
       </c>
     </row>
     <row r="5">
@@ -13047,22 +12727,22 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>6962.2</v>
+        <v>10173.9</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>5886.7</v>
+        <v>10179.3</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>6034.1</v>
+        <v>8878.299999999999</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>6020.3</v>
+        <v>9341.5</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>6095.9</v>
+        <v>11340.3</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>6458.6</v>
+        <v>11002.8</v>
       </c>
     </row>
     <row r="6">
@@ -13078,7 +12758,7 @@
         <v>8824.200000000001</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>8666.4</v>
+        <v>8739.9</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>9103</v>
@@ -13190,23 +12870,13 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
-        <v>564.8</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>523.5</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>543.3</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>536.5</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>523.2</v>
-      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n">
-        <v>525.1</v>
+        <v>1190.9</v>
       </c>
     </row>
     <row r="14">
@@ -13359,23 +13029,13 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n">
-        <v>1036.7</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>1022.2</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>970.7</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>892</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>801.6</v>
-      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="n">
-        <v>754.8</v>
+        <v>2262.1</v>
       </c>
     </row>
     <row r="23">
@@ -13528,23 +13188,13 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="C31" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="D31" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="E31" s="6" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>66</v>
-      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
       <c r="G31" s="6" t="n">
-        <v>64</v>
+        <v>1105.2</v>
       </c>
     </row>
     <row r="32">
@@ -13697,23 +13347,13 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B40" s="6" t="n">
-        <v>1011.7</v>
-      </c>
-      <c r="C40" s="6" t="n">
-        <v>993.2</v>
-      </c>
-      <c r="D40" s="6" t="n">
-        <v>930.7</v>
-      </c>
-      <c r="E40" s="6" t="n">
-        <v>843.1</v>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v>735.6</v>
-      </c>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
       <c r="G40" s="6" t="n">
-        <v>690.8</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="41">
@@ -13866,23 +13506,13 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="n"/>
       <c r="G49" s="6" t="n">
-        <v>0</v>
+        <v>7261.2</v>
       </c>
     </row>
     <row r="50">
@@ -13892,22 +13522,22 @@
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>2728.2</v>
+        <v>5939.9</v>
       </c>
       <c r="C50" s="6" t="n">
-        <v>1339.3</v>
+        <v>5631.9</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>1299.4</v>
+        <v>4143.6</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>1053.8</v>
+        <v>4375</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>1219.6</v>
+        <v>6463.9</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>1420.9</v>
+        <v>5965.1</v>
       </c>
     </row>
     <row r="51">
@@ -13923,7 +13553,7 @@
         <v>2757.2</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>2452.8</v>
+        <v>2526.2</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>2771.2</v>
@@ -14035,23 +13665,13 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B58" s="7" t="n">
-        <v>0.3527</v>
-      </c>
-      <c r="C58" s="7" t="n">
-        <v>0.3387</v>
-      </c>
-      <c r="D58" s="7" t="n">
-        <v>0.3588</v>
-      </c>
-      <c r="E58" s="7" t="n">
-        <v>0.3755</v>
-      </c>
-      <c r="F58" s="7" t="n">
-        <v>0.395</v>
-      </c>
+      <c r="B58" s="7" t="n"/>
+      <c r="C58" s="7" t="n"/>
+      <c r="D58" s="7" t="n"/>
+      <c r="E58" s="7" t="n"/>
+      <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n">
-        <v>0.4102</v>
+        <v>0.1112</v>
       </c>
     </row>
     <row r="59">
@@ -14061,22 +13681,22 @@
         </is>
       </c>
       <c r="B59" s="7" t="n">
-        <v>0.1862</v>
+        <v>0.1274</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>0.2578</v>
+        <v>0.1491</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>0.267</v>
+        <v>0.1814</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>0.3443</v>
+        <v>0.2219</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>0.3536</v>
+        <v>0.1901</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>0.3602</v>
+        <v>0.2115</v>
       </c>
     </row>
     <row r="60">
@@ -14092,7 +13712,7 @@
         <v>0.1289</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>0.1305</v>
+        <v>0.1294</v>
       </c>
       <c r="E60" s="7" t="n">
         <v>0.1495</v>
@@ -14204,23 +13824,13 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B67" s="7" t="n">
-        <v>0.6473</v>
-      </c>
-      <c r="C67" s="7" t="n">
-        <v>0.6613</v>
-      </c>
-      <c r="D67" s="7" t="n">
-        <v>0.6412</v>
-      </c>
-      <c r="E67" s="7" t="n">
-        <v>0.6245000000000001</v>
-      </c>
-      <c r="F67" s="7" t="n">
-        <v>0.605</v>
-      </c>
+      <c r="B67" s="7" t="n"/>
+      <c r="C67" s="7" t="n"/>
+      <c r="D67" s="7" t="n"/>
+      <c r="E67" s="7" t="n"/>
+      <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n">
-        <v>0.5898</v>
+        <v>0.2111</v>
       </c>
     </row>
     <row r="68">
@@ -14230,22 +13840,22 @@
         </is>
       </c>
       <c r="B68" s="7" t="n">
-        <v>0.4219</v>
+        <v>0.2887</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>0.5147</v>
+        <v>0.2977</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>0.5177</v>
+        <v>0.3519</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>0.4806</v>
+        <v>0.3098</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>0.4463</v>
+        <v>0.2399</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>0.4198</v>
+        <v>0.2464</v>
       </c>
     </row>
     <row r="69">
@@ -14261,7 +13871,7 @@
         <v>0.5586</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>0.5864</v>
+        <v>0.5815</v>
       </c>
       <c r="E69" s="7" t="n">
         <v>0.546</v>

--- a/銀行債券_完整報表.xlsx
+++ b/銀行債券_完整報表.xlsx
@@ -10053,7 +10053,7 @@
         <v>14</v>
       </c>
       <c r="BF4" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BG4" s="4" t="n">
         <v>231</v>
@@ -10226,7 +10226,7 @@
         <v>125</v>
       </c>
       <c r="BF5" s="4" t="n">
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="BG5" s="4" t="n">
         <v>306</v>
@@ -10399,7 +10399,7 @@
         <v>19</v>
       </c>
       <c r="BF6" s="4" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BG6" s="4" t="n">
         <v>452</v>
@@ -11573,7 +11573,7 @@
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
       <c r="G4" s="6" t="n">
-        <v>10714.2</v>
+        <v>11138.7</v>
       </c>
     </row>
     <row r="5">
@@ -11732,7 +11732,7 @@
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n">
-        <v>0</v>
+        <v>424.5</v>
       </c>
     </row>
     <row r="14">
@@ -12209,7 +12209,7 @@
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n">
-        <v>0</v>
+        <v>0.0381</v>
       </c>
     </row>
     <row r="41">
@@ -12368,7 +12368,7 @@
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n">
-        <v>0.3256</v>
+        <v>0.3132</v>
       </c>
     </row>
     <row r="50">
@@ -12527,7 +12527,7 @@
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n">
-        <v>0.6744</v>
+        <v>0.6487000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -12717,7 +12717,7 @@
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
       <c r="G4" s="6" t="n">
-        <v>10714.2</v>
+        <v>11138.7</v>
       </c>
     </row>
     <row r="5">
@@ -12876,7 +12876,7 @@
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n">
-        <v>1190.9</v>
+        <v>1195.7</v>
       </c>
     </row>
     <row r="14">
@@ -13035,7 +13035,7 @@
       <c r="E22" s="6" t="n"/>
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="n">
-        <v>2262.1</v>
+        <v>2679.2</v>
       </c>
     </row>
     <row r="23">
@@ -13194,7 +13194,7 @@
       <c r="E31" s="6" t="n"/>
       <c r="F31" s="6" t="n"/>
       <c r="G31" s="6" t="n">
-        <v>1105.2</v>
+        <v>1215.4</v>
       </c>
     </row>
     <row r="32">
@@ -13353,7 +13353,7 @@
       <c r="E40" s="6" t="n"/>
       <c r="F40" s="6" t="n"/>
       <c r="G40" s="6" t="n">
-        <v>1157</v>
+        <v>1463.7</v>
       </c>
     </row>
     <row r="41">
@@ -13512,7 +13512,7 @@
       <c r="E49" s="6" t="n"/>
       <c r="F49" s="6" t="n"/>
       <c r="G49" s="6" t="n">
-        <v>7261.2</v>
+        <v>7263.8</v>
       </c>
     </row>
     <row r="50">
@@ -13671,7 +13671,7 @@
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n">
-        <v>0.1112</v>
+        <v>0.1073</v>
       </c>
     </row>
     <row r="59">
@@ -13830,7 +13830,7 @@
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n">
-        <v>0.2111</v>
+        <v>0.2405</v>
       </c>
     </row>
     <row r="68">

--- a/銀行債券_完整報表.xlsx
+++ b/銀行債券_完整報表.xlsx
@@ -9754,9 +9754,7 @@
       <c r="J3" s="4" t="n">
         <v>309</v>
       </c>
-      <c r="K3" s="4" t="n">
-        <v>5491</v>
-      </c>
+      <c r="K3" s="4" t="inlineStr"/>
       <c r="L3" s="4" t="n">
         <v>902</v>
       </c>
@@ -9767,9 +9765,7 @@
       <c r="O3" s="4" t="n">
         <v>151</v>
       </c>
-      <c r="P3" s="4" t="n">
-        <v>4810</v>
-      </c>
+      <c r="P3" s="4" t="inlineStr"/>
       <c r="Q3" s="4" t="n">
         <v>1231</v>
       </c>
@@ -9927,9 +9923,7 @@
       <c r="J4" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="4" t="n">
         <v>3</v>
       </c>
@@ -9940,14 +9934,12 @@
       <c r="O4" s="4" t="n">
         <v>127</v>
       </c>
-      <c r="P4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="P4" s="4" t="inlineStr"/>
       <c r="Q4" s="4" t="n">
         <v>10</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S4" s="4" t="n">
         <v>174</v>
@@ -10087,72 +10079,68 @@
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="4" t="n">
-        <v>137</v>
+        <v>207</v>
       </c>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="n">
         <v>63</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>829</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="K5" s="4" t="inlineStr"/>
       <c r="L5" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M5" s="4" t="inlineStr"/>
       <c r="N5" s="4" t="n">
         <v>136</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>731</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="P5" s="4" t="inlineStr"/>
       <c r="Q5" s="4" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="S5" s="4" t="n">
         <v>188</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>61</v>
+        <v>328</v>
       </c>
       <c r="U5" s="4" t="n">
         <v>694</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="n">
         <v>192</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>52</v>
+        <v>269</v>
       </c>
       <c r="Z5" s="4" t="n">
         <v>681</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="AB5" s="4" t="inlineStr"/>
       <c r="AC5" s="4" t="n">
         <v>104</v>
       </c>
       <c r="AD5" s="4" t="n">
-        <v>95</v>
+        <v>254</v>
       </c>
       <c r="AE5" s="4" t="n">
         <v>635</v>
@@ -10165,7 +10153,7 @@
         <v>203</v>
       </c>
       <c r="AI5" s="4" t="n">
-        <v>60</v>
+        <v>192</v>
       </c>
       <c r="AJ5" s="4" t="n">
         <v>550</v>
@@ -10178,52 +10166,52 @@
         <v>180</v>
       </c>
       <c r="AN5" s="4" t="n">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="AO5" s="4" t="n">
         <v>509</v>
       </c>
       <c r="AP5" s="4" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="AQ5" s="4" t="inlineStr"/>
       <c r="AR5" s="4" t="n">
         <v>80</v>
       </c>
       <c r="AS5" s="4" t="n">
-        <v>69</v>
+        <v>131</v>
       </c>
       <c r="AT5" s="4" t="n">
         <v>477</v>
       </c>
       <c r="AU5" s="4" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AV5" s="4" t="inlineStr"/>
       <c r="AW5" s="4" t="n">
         <v>215</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="AY5" s="4" t="n">
         <v>399</v>
       </c>
       <c r="AZ5" s="4" t="n">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="BA5" s="4" t="inlineStr"/>
       <c r="BB5" s="4" t="n">
         <v>259</v>
       </c>
       <c r="BC5" s="4" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="BD5" s="4" t="n">
         <v>335</v>
       </c>
       <c r="BE5" s="4" t="n">
-        <v>125</v>
+        <v>185</v>
       </c>
       <c r="BF5" s="4" t="n">
         <v>307</v>
@@ -10232,7 +10220,7 @@
         <v>306</v>
       </c>
       <c r="BH5" s="4" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="BI5" s="4" t="n">
         <v>297</v>
@@ -10273,9 +10261,7 @@
       <c r="J6" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="K6" s="4" t="n">
-        <v>554</v>
-      </c>
+      <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="4" t="n">
         <v>6</v>
       </c>
@@ -10286,14 +10272,12 @@
       <c r="O6" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="P6" s="4" t="n">
-        <v>538</v>
-      </c>
+      <c r="P6" s="4" t="inlineStr"/>
       <c r="Q6" s="4" t="n">
         <v>12</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S6" s="4" t="n">
         <v>369</v>
@@ -10446,9 +10430,7 @@
       <c r="J7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="4" t="n">
-        <v>9</v>
-      </c>
+      <c r="K7" s="4" t="inlineStr"/>
       <c r="L7" s="4" t="n">
         <v>367</v>
       </c>
@@ -10459,9 +10441,7 @@
       <c r="O7" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="P7" s="4" t="n">
-        <v>786</v>
-      </c>
+      <c r="P7" s="4" t="inlineStr"/>
       <c r="Q7" s="4" t="n">
         <v>330</v>
       </c>
@@ -10619,9 +10599,7 @@
       <c r="J8" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="K8" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="4" t="n">
         <v>149</v>
       </c>
@@ -10632,9 +10610,7 @@
       <c r="O8" s="4" t="n">
         <v>336</v>
       </c>
-      <c r="P8" s="4" t="n">
-        <v>653</v>
-      </c>
+      <c r="P8" s="4" t="inlineStr"/>
       <c r="Q8" s="4" t="n">
         <v>114</v>
       </c>
@@ -10792,9 +10768,7 @@
       <c r="J9" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="K9" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="4" t="n">
         <v>1132</v>
       </c>
@@ -10805,9 +10779,7 @@
       <c r="O9" s="4" t="n">
         <v>375</v>
       </c>
-      <c r="P9" s="4" t="n">
-        <v>1211</v>
-      </c>
+      <c r="P9" s="4" t="inlineStr"/>
       <c r="Q9" s="4" t="n">
         <v>1080</v>
       </c>
@@ -10965,9 +10937,7 @@
       <c r="J10" s="4" t="n">
         <v>437</v>
       </c>
-      <c r="K10" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="4" t="n">
         <v>1902</v>
       </c>
@@ -10978,9 +10948,7 @@
       <c r="O10" s="4" t="n">
         <v>457</v>
       </c>
-      <c r="P10" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="P10" s="4" t="inlineStr"/>
       <c r="Q10" s="4" t="n">
         <v>2088</v>
       </c>
@@ -11138,9 +11106,7 @@
       <c r="J11" s="4" t="n">
         <v>1749</v>
       </c>
-      <c r="K11" s="4" t="n">
-        <v>6</v>
-      </c>
+      <c r="K11" s="4" t="inlineStr"/>
       <c r="L11" s="4" t="n">
         <v>665</v>
       </c>
@@ -11151,9 +11117,7 @@
       <c r="O11" s="4" t="n">
         <v>1911</v>
       </c>
-      <c r="P11" s="4" t="n">
-        <v>32</v>
-      </c>
+      <c r="P11" s="4" t="inlineStr"/>
       <c r="Q11" s="4" t="n">
         <v>657</v>
       </c>
@@ -11311,9 +11275,7 @@
       <c r="J12" s="4" t="n">
         <v>910</v>
       </c>
-      <c r="K12" s="4" t="n">
-        <v>33</v>
-      </c>
+      <c r="K12" s="4" t="inlineStr"/>
       <c r="L12" s="4" t="n">
         <v>267</v>
       </c>
@@ -11324,9 +11286,7 @@
       <c r="O12" s="4" t="n">
         <v>1158</v>
       </c>
-      <c r="P12" s="4" t="n">
-        <v>171</v>
-      </c>
+      <c r="P12" s="4" t="inlineStr"/>
       <c r="Q12" s="4" t="n">
         <v>259</v>
       </c>
@@ -11549,16 +11509,16 @@
         <v>10656.3</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>10729.3</v>
+        <v>10739.1</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>12964.4</v>
+        <v>12974.2</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>12320.8</v>
+        <v>12344.7</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>12299.2</v>
+        <v>12359.1</v>
       </c>
     </row>
     <row r="4">
@@ -11608,22 +11568,22 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>9435.9</v>
+        <v>9567.5</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>8824.200000000001</v>
+        <v>8933.700000000001</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>8739.9</v>
+        <v>8801.5</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>9103</v>
+        <v>9221.299999999999</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>8981</v>
+        <v>9129.9</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>9830</v>
+        <v>10023</v>
       </c>
     </row>
     <row r="7">
@@ -11639,16 +11599,16 @@
         <v>8873.4</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>8785.1</v>
+        <v>8864.200000000001</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>8833.700000000001</v>
+        <v>9023.1</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>8371</v>
+        <v>8903.700000000001</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>8299.6</v>
+        <v>9400.200000000001</v>
       </c>
     </row>
     <row r="10">
@@ -11708,16 +11668,16 @@
         <v>600</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>518.3</v>
+        <v>528</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>1038.9</v>
+        <v>1048.7</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>369.9</v>
+        <v>393.9</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>307.1</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13">
@@ -11767,22 +11727,22 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>281.7</v>
+        <v>413.3</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>210.7</v>
+        <v>320.2</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>306.8</v>
+        <v>368.5</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>163.8</v>
+        <v>282</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>356.9</v>
+        <v>505.7</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>206</v>
+        <v>399</v>
       </c>
     </row>
     <row r="16">
@@ -11957,16 +11917,16 @@
         <v>3160.9</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>3355.2</v>
+        <v>3358.4</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>3239.1</v>
+        <v>3248.5</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>2906</v>
+        <v>2929.4</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>3067.6</v>
+        <v>3363.5</v>
       </c>
     </row>
     <row r="28">
@@ -12116,16 +12076,16 @@
         <v>4737.8</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>4354.4</v>
+        <v>4430.4</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>4648.4</v>
+        <v>4828.3</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>4430.4</v>
+        <v>4939.7</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>4416.7</v>
+        <v>5221.4</v>
       </c>
     </row>
     <row r="37">
@@ -12185,16 +12145,16 @@
         <v>0.0563</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>0.0483</v>
+        <v>0.0492</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>0.0801</v>
+        <v>0.0808</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>0.03</v>
+        <v>0.0319</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>0.025</v>
+        <v>0.0297</v>
       </c>
     </row>
     <row r="40">
@@ -12244,22 +12204,22 @@
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>0.0299</v>
+        <v>0.0432</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>0.0239</v>
+        <v>0.0358</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>0.0351</v>
+        <v>0.0419</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>0.018</v>
+        <v>0.0306</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>0.0397</v>
+        <v>0.0554</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>0.021</v>
+        <v>0.0398</v>
       </c>
     </row>
     <row r="43">
@@ -12275,16 +12235,16 @@
         <v>0.1098</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0.1224</v>
+        <v>0.1213</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>0.1071</v>
+        <v>0.1049</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>0.1236</v>
+        <v>0.1162</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>0.0982</v>
+        <v>0.0867</v>
       </c>
     </row>
     <row r="46">
@@ -12344,16 +12304,16 @@
         <v>0.1841</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>0.1809</v>
+        <v>0.1808</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>0.1865</v>
+        <v>0.1863</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0.2244</v>
+        <v>0.224</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>0.254</v>
+        <v>0.2528</v>
       </c>
     </row>
     <row r="49">
@@ -12403,22 +12363,22 @@
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>0.125</v>
+        <v>0.1233</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>0.1542</v>
+        <v>0.1523</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0.1653</v>
+        <v>0.1642</v>
       </c>
       <c r="E51" s="7" t="n">
+        <v>0.1694</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>0.1643</v>
+      </c>
+      <c r="G51" s="7" t="n">
         <v>0.1716</v>
-      </c>
-      <c r="F51" s="7" t="n">
-        <v>0.1671</v>
-      </c>
-      <c r="G51" s="7" t="n">
-        <v>0.175</v>
       </c>
     </row>
     <row r="52">
@@ -12434,16 +12394,16 @@
         <v>0.3562</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>0.3819</v>
+        <v>0.3789</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>0.3667</v>
+        <v>0.36</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>0.3471</v>
+        <v>0.329</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>0.3696</v>
+        <v>0.3578</v>
       </c>
     </row>
     <row r="55">
@@ -12503,16 +12463,16 @@
         <v>0.7596000000000001</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>0.7708</v>
+        <v>0.7701</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>0.7334000000000001</v>
+        <v>0.7329</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>0.7456</v>
+        <v>0.7441</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>0.721</v>
+        <v>0.7175</v>
       </c>
     </row>
     <row r="58">
@@ -12562,22 +12522,22 @@
         </is>
       </c>
       <c r="B60" s="7" t="n">
-        <v>0.8451</v>
+        <v>0.8335</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>0.8219</v>
+        <v>0.8118</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>0.7995</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>0.8104</v>
+        <v>0.8</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>0.7932</v>
+        <v>0.7803</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0.8041</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="61">
@@ -12593,16 +12553,16 @@
         <v>0.5339</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>0.4957</v>
+        <v>0.4998</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>0.5262</v>
+        <v>0.5351</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>0.5293</v>
+        <v>0.5548</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>0.5322</v>
+        <v>0.5555</v>
       </c>
     </row>
   </sheetData>
@@ -12693,16 +12653,16 @@
         <v>10656.3</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>10729.3</v>
+        <v>10739.1</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>12964.4</v>
+        <v>12974.2</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>12320.8</v>
+        <v>12344.7</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>12299.2</v>
+        <v>12359.1</v>
       </c>
     </row>
     <row r="4">
@@ -12752,22 +12712,22 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>9435.9</v>
+        <v>9567.5</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>8824.200000000001</v>
+        <v>8933.700000000001</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>8739.9</v>
+        <v>8801.5</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>9103</v>
+        <v>9221.299999999999</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>8981</v>
+        <v>9129.9</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>9830</v>
+        <v>10023</v>
       </c>
     </row>
     <row r="7">
@@ -12783,16 +12743,16 @@
         <v>8873.4</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>8785.1</v>
+        <v>8864.200000000001</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>8833.700000000001</v>
+        <v>9023.1</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>8371</v>
+        <v>8903.700000000001</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>8299.6</v>
+        <v>9400.200000000001</v>
       </c>
     </row>
     <row r="10">
@@ -13011,16 +12971,16 @@
         <v>2442.3</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2335.1</v>
+        <v>2344.8</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>2490.4</v>
+        <v>2500.3</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>2491.5</v>
+        <v>2515.4</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>2789.7</v>
+        <v>2849.6</v>
       </c>
     </row>
     <row r="22">
@@ -13070,22 +13030,22 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>4862.8</v>
+        <v>4994.4</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>4929.2</v>
+        <v>5038.7</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>5082.3</v>
+        <v>5144</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>4970.5</v>
+        <v>5088.7</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>4675.9</v>
+        <v>4824.8</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>5152.4</v>
+        <v>5345.4</v>
       </c>
     </row>
     <row r="25">
@@ -13329,16 +13289,16 @@
         <v>966.2</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>991.5</v>
+        <v>1001.2</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>1208.9</v>
+        <v>1218.8</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1240.4</v>
+        <v>1264.3</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>1535.9</v>
+        <v>1595.8</v>
       </c>
     </row>
     <row r="40">
@@ -13388,22 +13348,22 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>2742.7</v>
+        <v>2874.3</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>2848.2</v>
+        <v>2957.6</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>2723.9</v>
+        <v>2785.6</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>2659.4</v>
+        <v>2777.7</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>2491.3</v>
+        <v>2640.1</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>2597.1</v>
+        <v>2790.1</v>
       </c>
     </row>
     <row r="43">
@@ -13578,16 +13538,16 @@
         <v>3965.1</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>3802.4</v>
+        <v>3881.5</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>4011.6</v>
+        <v>4201</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>3918.5</v>
+        <v>4451.2</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>3666.3</v>
+        <v>4766.8</v>
       </c>
     </row>
     <row r="55">
@@ -13647,16 +13607,16 @@
         <v>0.3219</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>0.3207</v>
+        <v>0.3204</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>0.2823</v>
+        <v>0.2821</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>0.3108</v>
+        <v>0.3102</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>0.3105</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="58">
@@ -13706,22 +13666,22 @@
         </is>
       </c>
       <c r="B60" s="7" t="n">
-        <v>0.1195</v>
+        <v>0.1178</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>0.1289</v>
+        <v>0.1274</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>0.1294</v>
+        <v>0.1285</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>0.1495</v>
+        <v>0.1476</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>0.1554</v>
+        <v>0.1529</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0.1613</v>
+        <v>0.1582</v>
       </c>
     </row>
     <row r="61">
@@ -13737,16 +13697,16 @@
         <v>0.0779</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>0.0733</v>
+        <v>0.0727</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>0.0745</v>
+        <v>0.073</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0623</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>0.0639</v>
+        <v>0.0564</v>
       </c>
     </row>
     <row r="64">
@@ -13806,16 +13766,16 @@
         <v>0.2292</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>0.2176</v>
+        <v>0.2183</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>0.1921</v>
+        <v>0.1927</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>0.2022</v>
+        <v>0.2038</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>0.2268</v>
+        <v>0.2306</v>
       </c>
     </row>
     <row r="67">
@@ -13865,22 +13825,22 @@
         </is>
       </c>
       <c r="B69" s="7" t="n">
-        <v>0.5154</v>
+        <v>0.522</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>0.5586</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>0.5815</v>
+        <v>0.5844</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>0.546</v>
+        <v>0.5518</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>0.5206</v>
+        <v>0.5285</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>0.5242</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="70">
@@ -13896,16 +13856,16 @@
         <v>0.4752</v>
       </c>
       <c r="D70" s="7" t="n">
-        <v>0.4939</v>
+        <v>0.4895</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>0.4714</v>
+        <v>0.4615</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>0.4657</v>
+        <v>0.4378</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>0.4944</v>
+        <v>0.4365</v>
       </c>
     </row>
   </sheetData>

--- a/銀行債券_完整報表.xlsx
+++ b/銀行債券_完整報表.xlsx
@@ -9802,7 +9802,7 @@
         <v>956</v>
       </c>
       <c r="AD3" s="4" t="n">
-        <v>482</v>
+        <v>461</v>
       </c>
       <c r="AE3" s="4" t="n">
         <v>1732</v>
@@ -9882,7 +9882,7 @@
         <v>2095</v>
       </c>
       <c r="BH3" s="4" t="n">
-        <v>1164</v>
+        <v>1244</v>
       </c>
       <c r="BI3" s="4" t="n">
         <v>1719</v>
@@ -9971,7 +9971,7 @@
         <v>81</v>
       </c>
       <c r="AD4" s="4" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="4" t="n">
         <v>0</v>
@@ -10023,7 +10023,7 @@
         <v>136</v>
       </c>
       <c r="AX4" s="4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AY4" s="4" t="n">
         <v>0</v>
@@ -10051,7 +10051,7 @@
         <v>231</v>
       </c>
       <c r="BH4" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BI4" s="4" t="n">
         <v>0</v>
@@ -10192,7 +10192,7 @@
         <v>215</v>
       </c>
       <c r="AX5" s="4" t="n">
-        <v>118</v>
+        <v>154</v>
       </c>
       <c r="AY5" s="4" t="n">
         <v>399</v>
@@ -10220,7 +10220,7 @@
         <v>306</v>
       </c>
       <c r="BH5" s="4" t="n">
-        <v>193</v>
+        <v>244</v>
       </c>
       <c r="BI5" s="4" t="n">
         <v>297</v>
@@ -10259,7 +10259,7 @@
         <v>84</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="4" t="n">
@@ -10283,7 +10283,7 @@
         <v>369</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="U6" s="4" t="n">
         <v>492</v>
@@ -10309,7 +10309,7 @@
         <v>334</v>
       </c>
       <c r="AD6" s="4" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="4" t="n">
         <v>485</v>
@@ -11574,16 +11574,16 @@
         <v>8933.700000000001</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>8801.5</v>
+        <v>9394.1</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>9221.299999999999</v>
+        <v>9834.6</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>9129.9</v>
+        <v>9874</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>10023</v>
+        <v>10878</v>
       </c>
     </row>
     <row r="7">
@@ -12051,16 +12051,16 @@
         <v>7252.5</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>6987.9</v>
+        <v>7580.5</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>7376.7</v>
+        <v>7990.1</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>7123.9</v>
+        <v>7868</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>7904.1</v>
+        <v>8759.1</v>
       </c>
     </row>
     <row r="34">
@@ -12210,16 +12210,16 @@
         <v>0.0358</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>0.0419</v>
+        <v>0.0392</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>0.0306</v>
+        <v>0.0287</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>0.0554</v>
+        <v>0.0512</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>0.0398</v>
+        <v>0.0367</v>
       </c>
     </row>
     <row r="43">
@@ -12369,16 +12369,16 @@
         <v>0.1523</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0.1642</v>
+        <v>0.1538</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>0.1694</v>
+        <v>0.1589</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>0.1643</v>
+        <v>0.1519</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>0.1716</v>
+        <v>0.1581</v>
       </c>
     </row>
     <row r="52">
@@ -12528,16 +12528,16 @@
         <v>0.8118</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.8069</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>0.8</v>
+        <v>0.8124</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>0.7803</v>
+        <v>0.7968</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0.7886</v>
+        <v>0.8052</v>
       </c>
     </row>
     <row r="61">
@@ -12718,16 +12718,16 @@
         <v>8933.700000000001</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>8801.5</v>
+        <v>9394.1</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>9221.299999999999</v>
+        <v>9834.6</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>9129.9</v>
+        <v>9874</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>10023</v>
+        <v>10878</v>
       </c>
     </row>
     <row r="7">
@@ -12880,13 +12880,13 @@
         <v>1131.3</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1361.4</v>
+        <v>1379.4</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>1395.9</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>1585.3</v>
+        <v>1610.2</v>
       </c>
     </row>
     <row r="16">
@@ -13039,13 +13039,13 @@
         <v>5144</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>5088.7</v>
+        <v>5124.4</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>4824.8</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>5345.4</v>
+        <v>5396.1</v>
       </c>
     </row>
     <row r="25">
@@ -13357,13 +13357,13 @@
         <v>2785.6</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>2777.7</v>
+        <v>2813.3</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>2640.1</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>2790.1</v>
+        <v>2840.9</v>
       </c>
     </row>
     <row r="43">
@@ -13513,16 +13513,16 @@
         <v>2757.2</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>2526.2</v>
+        <v>3118.8</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>2771.2</v>
+        <v>3330.9</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>2909.2</v>
+        <v>3653.3</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>3092.3</v>
+        <v>3871.7</v>
       </c>
     </row>
     <row r="52">
@@ -13672,16 +13672,16 @@
         <v>0.1274</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>0.1285</v>
+        <v>0.1204</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>0.1476</v>
+        <v>0.1403</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>0.1529</v>
+        <v>0.1414</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0.1582</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="61">
@@ -13831,16 +13831,16 @@
         <v>0.5639999999999999</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>0.5844</v>
+        <v>0.5476</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>0.5518</v>
+        <v>0.5211</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>0.5285</v>
+        <v>0.4886</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>0.5333</v>
+        <v>0.4961</v>
       </c>
     </row>
     <row r="70">

--- a/銀行債券_完整報表.xlsx
+++ b/銀行債券_完整報表.xlsx
@@ -9747,7 +9747,9 @@
       <c r="G3" s="4" t="n">
         <v>1206</v>
       </c>
-      <c r="H3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I3" s="4" t="n">
         <v>1957</v>
       </c>
@@ -9797,7 +9799,9 @@
       <c r="AA3" s="4" t="n">
         <v>1463</v>
       </c>
-      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AB3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AC3" s="4" t="n">
         <v>956</v>
       </c>
@@ -9823,7 +9827,9 @@
       <c r="AK3" s="4" t="n">
         <v>3411</v>
       </c>
-      <c r="AL3" s="4" t="inlineStr"/>
+      <c r="AL3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AM3" s="4" t="n">
         <v>1524</v>
       </c>
@@ -9849,7 +9855,9 @@
       <c r="AU3" s="4" t="n">
         <v>3090</v>
       </c>
-      <c r="AV3" s="4" t="inlineStr"/>
+      <c r="AV3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AW3" s="4" t="n">
         <v>1085</v>
       </c>
@@ -9916,7 +9924,9 @@
       <c r="G4" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="H4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="n">
+        <v>13</v>
+      </c>
       <c r="I4" s="4" t="n">
         <v>355</v>
       </c>
@@ -9966,7 +9976,9 @@
       <c r="AA4" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AB4" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AC4" s="4" t="n">
         <v>81</v>
       </c>
@@ -9992,7 +10004,9 @@
       <c r="AK4" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="AL4" s="4" t="inlineStr"/>
+      <c r="AL4" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="AM4" s="4" t="n">
         <v>23</v>
       </c>
@@ -10018,7 +10032,9 @@
       <c r="AU4" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="AV4" s="4" t="inlineStr"/>
+      <c r="AV4" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="AW4" s="4" t="n">
         <v>136</v>
       </c>
@@ -10085,7 +10101,9 @@
       <c r="G5" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="H5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="n">
+        <v>275</v>
+      </c>
       <c r="I5" s="4" t="n">
         <v>63</v>
       </c>
@@ -10135,7 +10153,9 @@
       <c r="AA5" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="n">
+        <v>295</v>
+      </c>
       <c r="AC5" s="4" t="n">
         <v>104</v>
       </c>
@@ -10161,7 +10181,9 @@
       <c r="AK5" s="4" t="n">
         <v>132</v>
       </c>
-      <c r="AL5" s="4" t="inlineStr"/>
+      <c r="AL5" s="4" t="n">
+        <v>226</v>
+      </c>
       <c r="AM5" s="4" t="n">
         <v>180</v>
       </c>
@@ -10187,7 +10209,9 @@
       <c r="AU5" s="4" t="n">
         <v>89</v>
       </c>
-      <c r="AV5" s="4" t="inlineStr"/>
+      <c r="AV5" s="4" t="n">
+        <v>223</v>
+      </c>
       <c r="AW5" s="4" t="n">
         <v>215</v>
       </c>
@@ -10254,7 +10278,9 @@
       <c r="G6" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="n">
+        <v>53</v>
+      </c>
       <c r="I6" s="4" t="n">
         <v>84</v>
       </c>
@@ -10304,7 +10330,9 @@
       <c r="AA6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="AC6" s="4" t="n">
         <v>334</v>
       </c>
@@ -10330,7 +10358,9 @@
       <c r="AK6" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AL6" s="4" t="n">
+        <v>61</v>
+      </c>
       <c r="AM6" s="4" t="n">
         <v>608</v>
       </c>
@@ -10356,7 +10386,9 @@
       <c r="AU6" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="AV6" s="4" t="inlineStr"/>
+      <c r="AV6" s="4" t="n">
+        <v>84</v>
+      </c>
       <c r="AW6" s="4" t="n">
         <v>228</v>
       </c>
@@ -10423,7 +10455,9 @@
       <c r="G7" s="4" t="n">
         <v>541</v>
       </c>
-      <c r="H7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="n">
+        <v>712</v>
+      </c>
       <c r="I7" s="4" t="n">
         <v>709</v>
       </c>
@@ -10446,7 +10480,7 @@
         <v>330</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>822</v>
+        <v>812</v>
       </c>
       <c r="S7" s="4" t="n">
         <v>368</v>
@@ -10473,7 +10507,9 @@
       <c r="AA7" s="4" t="n">
         <v>185</v>
       </c>
-      <c r="AB7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="n">
+        <v>802</v>
+      </c>
       <c r="AC7" s="4" t="n">
         <v>741</v>
       </c>
@@ -10499,7 +10535,9 @@
       <c r="AK7" s="4" t="n">
         <v>633</v>
       </c>
-      <c r="AL7" s="4" t="inlineStr"/>
+      <c r="AL7" s="4" t="n">
+        <v>720</v>
+      </c>
       <c r="AM7" s="4" t="n">
         <v>882</v>
       </c>
@@ -10525,7 +10563,9 @@
       <c r="AU7" s="4" t="n">
         <v>938</v>
       </c>
-      <c r="AV7" s="4" t="inlineStr"/>
+      <c r="AV7" s="4" t="n">
+        <v>873</v>
+      </c>
       <c r="AW7" s="4" t="n">
         <v>1469</v>
       </c>
@@ -10552,7 +10592,7 @@
         <v>1464</v>
       </c>
       <c r="BF7" s="4" t="n">
-        <v>818</v>
+        <v>789</v>
       </c>
       <c r="BG7" s="4" t="n">
         <v>1668</v>
@@ -10592,7 +10632,9 @@
       <c r="G8" s="4" t="n">
         <v>176</v>
       </c>
-      <c r="H8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="n">
+        <v>1392</v>
+      </c>
       <c r="I8" s="4" t="n">
         <v>947</v>
       </c>
@@ -10615,7 +10657,7 @@
         <v>114</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="S8" s="4" t="n">
         <v>134</v>
@@ -10642,7 +10684,9 @@
       <c r="AA8" s="4" t="n">
         <v>106</v>
       </c>
-      <c r="AB8" s="4" t="inlineStr"/>
+      <c r="AB8" s="4" t="n">
+        <v>1326</v>
+      </c>
       <c r="AC8" s="4" t="n">
         <v>725</v>
       </c>
@@ -10668,7 +10712,9 @@
       <c r="AK8" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="AL8" s="4" t="inlineStr"/>
+      <c r="AL8" s="4" t="n">
+        <v>1327</v>
+      </c>
       <c r="AM8" s="4" t="n">
         <v>747</v>
       </c>
@@ -10694,7 +10740,9 @@
       <c r="AU8" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="AV8" s="4" t="inlineStr"/>
+      <c r="AV8" s="4" t="n">
+        <v>1172</v>
+      </c>
       <c r="AW8" s="4" t="n">
         <v>942</v>
       </c>
@@ -10721,7 +10769,7 @@
         <v>103</v>
       </c>
       <c r="BF8" s="4" t="n">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="BG8" s="4" t="n">
         <v>958</v>
@@ -10761,7 +10809,9 @@
       <c r="G9" s="4" t="n">
         <v>1485</v>
       </c>
-      <c r="H9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="n">
+        <v>929</v>
+      </c>
       <c r="I9" s="4" t="n">
         <v>626</v>
       </c>
@@ -10784,7 +10834,7 @@
         <v>1080</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="S9" s="4" t="n">
         <v>168</v>
@@ -10811,7 +10861,9 @@
       <c r="AA9" s="4" t="n">
         <v>979</v>
       </c>
-      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="n">
+        <v>915</v>
+      </c>
       <c r="AC9" s="4" t="n">
         <v>351</v>
       </c>
@@ -10837,7 +10889,9 @@
       <c r="AK9" s="4" t="n">
         <v>750</v>
       </c>
-      <c r="AL9" s="4" t="inlineStr"/>
+      <c r="AL9" s="4" t="n">
+        <v>926</v>
+      </c>
       <c r="AM9" s="4" t="n">
         <v>350</v>
       </c>
@@ -10863,7 +10917,9 @@
       <c r="AU9" s="4" t="n">
         <v>597</v>
       </c>
-      <c r="AV9" s="4" t="inlineStr"/>
+      <c r="AV9" s="4" t="n">
+        <v>977</v>
+      </c>
       <c r="AW9" s="4" t="n">
         <v>291</v>
       </c>
@@ -10890,7 +10946,7 @@
         <v>633</v>
       </c>
       <c r="BF9" s="4" t="n">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="BG9" s="4" t="n">
         <v>165</v>
@@ -10930,7 +10986,9 @@
       <c r="G10" s="4" t="n">
         <v>1803</v>
       </c>
-      <c r="H10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="n">
+        <v>31</v>
+      </c>
       <c r="I10" s="4" t="n">
         <v>96</v>
       </c>
@@ -10980,7 +11038,9 @@
       <c r="AA10" s="4" t="n">
         <v>2475</v>
       </c>
-      <c r="AB10" s="4" t="inlineStr"/>
+      <c r="AB10" s="4" t="n">
+        <v>179</v>
+      </c>
       <c r="AC10" s="4" t="n">
         <v>469</v>
       </c>
@@ -11006,7 +11066,9 @@
       <c r="AK10" s="4" t="n">
         <v>2742</v>
       </c>
-      <c r="AL10" s="4" t="inlineStr"/>
+      <c r="AL10" s="4" t="n">
+        <v>235</v>
+      </c>
       <c r="AM10" s="4" t="n">
         <v>612</v>
       </c>
@@ -11032,7 +11094,9 @@
       <c r="AU10" s="4" t="n">
         <v>2702</v>
       </c>
-      <c r="AV10" s="4" t="inlineStr"/>
+      <c r="AV10" s="4" t="n">
+        <v>325</v>
+      </c>
       <c r="AW10" s="4" t="n">
         <v>468</v>
       </c>
@@ -11099,7 +11163,9 @@
       <c r="G11" s="4" t="n">
         <v>571</v>
       </c>
-      <c r="H11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="n">
+        <v>24</v>
+      </c>
       <c r="I11" s="4" t="n">
         <v>123</v>
       </c>
@@ -11149,7 +11215,9 @@
       <c r="AA11" s="4" t="n">
         <v>785</v>
       </c>
-      <c r="AB11" s="4" t="inlineStr"/>
+      <c r="AB11" s="4" t="n">
+        <v>59</v>
+      </c>
       <c r="AC11" s="4" t="n">
         <v>258</v>
       </c>
@@ -11175,7 +11243,9 @@
       <c r="AK11" s="4" t="n">
         <v>784</v>
       </c>
-      <c r="AL11" s="4" t="inlineStr"/>
+      <c r="AL11" s="4" t="n">
+        <v>95</v>
+      </c>
       <c r="AM11" s="4" t="n">
         <v>252</v>
       </c>
@@ -11201,7 +11271,9 @@
       <c r="AU11" s="4" t="n">
         <v>1052</v>
       </c>
-      <c r="AV11" s="4" t="inlineStr"/>
+      <c r="AV11" s="4" t="n">
+        <v>124</v>
+      </c>
       <c r="AW11" s="4" t="n">
         <v>293</v>
       </c>
@@ -11268,7 +11340,9 @@
       <c r="G12" s="4" t="n">
         <v>175</v>
       </c>
-      <c r="H12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="n">
+        <v>299</v>
+      </c>
       <c r="I12" s="4" t="n">
         <v>106</v>
       </c>
@@ -11318,7 +11392,9 @@
       <c r="AA12" s="4" t="n">
         <v>437</v>
       </c>
-      <c r="AB12" s="4" t="inlineStr"/>
+      <c r="AB12" s="4" t="n">
+        <v>379</v>
+      </c>
       <c r="AC12" s="4" t="n">
         <v>511</v>
       </c>
@@ -11344,7 +11420,9 @@
       <c r="AK12" s="4" t="n">
         <v>640</v>
       </c>
-      <c r="AL12" s="4" t="inlineStr"/>
+      <c r="AL12" s="4" t="n">
+        <v>240</v>
+      </c>
       <c r="AM12" s="4" t="n">
         <v>893</v>
       </c>
@@ -11370,7 +11448,9 @@
       <c r="AU12" s="4" t="n">
         <v>671</v>
       </c>
-      <c r="AV12" s="4" t="inlineStr"/>
+      <c r="AV12" s="4" t="n">
+        <v>228</v>
+      </c>
       <c r="AW12" s="4" t="n">
         <v>924</v>
       </c>
@@ -11528,12 +11608,16 @@
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
+      <c r="C4" s="6" t="n">
+        <v>9969.4</v>
+      </c>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
+      <c r="E4" s="6" t="n">
+        <v>10385.3</v>
+      </c>
       <c r="F4" s="6" t="n"/>
       <c r="G4" s="6" t="n">
-        <v>11138.7</v>
+        <v>11020.3</v>
       </c>
     </row>
     <row r="5">
@@ -11687,12 +11771,16 @@
         </is>
       </c>
       <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
+      <c r="C13" s="6" t="n">
+        <v>290.9</v>
+      </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
+      <c r="E13" s="6" t="n">
+        <v>317.8</v>
+      </c>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n">
-        <v>424.5</v>
+        <v>424.9</v>
       </c>
     </row>
     <row r="14">
@@ -11846,12 +11934,16 @@
         </is>
       </c>
       <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
+      <c r="C22" s="6" t="n">
+        <v>3579.9</v>
+      </c>
       <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
+      <c r="E22" s="6" t="n">
+        <v>3636.9</v>
+      </c>
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="n">
-        <v>3488.3</v>
+        <v>3370.1</v>
       </c>
     </row>
     <row r="23">
@@ -12005,12 +12097,16 @@
         </is>
       </c>
       <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
+      <c r="C31" s="6" t="n">
+        <v>6098.6</v>
+      </c>
       <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
+      <c r="E31" s="6" t="n">
+        <v>6430.6</v>
+      </c>
       <c r="F31" s="6" t="n"/>
       <c r="G31" s="6" t="n">
-        <v>7225.9</v>
+        <v>7225.3</v>
       </c>
     </row>
     <row r="32">
@@ -12164,12 +12260,16 @@
         </is>
       </c>
       <c r="B40" s="7" t="n"/>
-      <c r="C40" s="7" t="n"/>
+      <c r="C40" s="7" t="n">
+        <v>0.0292</v>
+      </c>
       <c r="D40" s="7" t="n"/>
-      <c r="E40" s="7" t="n"/>
+      <c r="E40" s="7" t="n">
+        <v>0.0306</v>
+      </c>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n">
-        <v>0.0381</v>
+        <v>0.0386</v>
       </c>
     </row>
     <row r="41">
@@ -12323,12 +12423,16 @@
         </is>
       </c>
       <c r="B49" s="7" t="n"/>
-      <c r="C49" s="7" t="n"/>
+      <c r="C49" s="7" t="n">
+        <v>0.3591</v>
+      </c>
       <c r="D49" s="7" t="n"/>
-      <c r="E49" s="7" t="n"/>
+      <c r="E49" s="7" t="n">
+        <v>0.3502</v>
+      </c>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n">
-        <v>0.3132</v>
+        <v>0.3058</v>
       </c>
     </row>
     <row r="50">
@@ -12482,12 +12586,16 @@
         </is>
       </c>
       <c r="B58" s="7" t="n"/>
-      <c r="C58" s="7" t="n"/>
+      <c r="C58" s="7" t="n">
+        <v>0.6117</v>
+      </c>
       <c r="D58" s="7" t="n"/>
-      <c r="E58" s="7" t="n"/>
+      <c r="E58" s="7" t="n">
+        <v>0.6192</v>
+      </c>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.6556</v>
       </c>
     </row>
     <row r="59">
@@ -12672,12 +12780,16 @@
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
+      <c r="C4" s="6" t="n">
+        <v>9969.4</v>
+      </c>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
+      <c r="E4" s="6" t="n">
+        <v>10385.3</v>
+      </c>
       <c r="F4" s="6" t="n"/>
       <c r="G4" s="6" t="n">
-        <v>11138.7</v>
+        <v>11020.3</v>
       </c>
     </row>
     <row r="5">
@@ -12831,12 +12943,16 @@
         </is>
       </c>
       <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
+      <c r="C13" s="6" t="n">
+        <v>957.6</v>
+      </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
+      <c r="E13" s="6" t="n">
+        <v>1199.3</v>
+      </c>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n">
-        <v>1195.7</v>
+        <v>1167.1</v>
       </c>
     </row>
     <row r="14">
@@ -12990,12 +13106,16 @@
         </is>
       </c>
       <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
+      <c r="C22" s="6" t="n">
+        <v>2874.9</v>
+      </c>
       <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
+      <c r="E22" s="6" t="n">
+        <v>2809.8</v>
+      </c>
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="n">
-        <v>2679.2</v>
+        <v>2677.4</v>
       </c>
     </row>
     <row r="23">
@@ -13149,12 +13269,16 @@
         </is>
       </c>
       <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
+      <c r="C31" s="6" t="n">
+        <v>1227.3</v>
+      </c>
       <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
+      <c r="E31" s="6" t="n">
+        <v>1290</v>
+      </c>
       <c r="F31" s="6" t="n"/>
       <c r="G31" s="6" t="n">
-        <v>1215.4</v>
+        <v>1218.9</v>
       </c>
     </row>
     <row r="32">
@@ -13308,12 +13432,16 @@
         </is>
       </c>
       <c r="B40" s="6" t="n"/>
-      <c r="C40" s="6" t="n"/>
+      <c r="C40" s="6" t="n">
+        <v>1647.6</v>
+      </c>
       <c r="D40" s="6" t="n"/>
-      <c r="E40" s="6" t="n"/>
+      <c r="E40" s="6" t="n">
+        <v>1519.8</v>
+      </c>
       <c r="F40" s="6" t="n"/>
       <c r="G40" s="6" t="n">
-        <v>1463.7</v>
+        <v>1458.5</v>
       </c>
     </row>
     <row r="41">
@@ -13467,12 +13595,16 @@
         </is>
       </c>
       <c r="B49" s="6" t="n"/>
-      <c r="C49" s="6" t="n"/>
+      <c r="C49" s="6" t="n">
+        <v>6136.9</v>
+      </c>
       <c r="D49" s="6" t="n"/>
-      <c r="E49" s="6" t="n"/>
+      <c r="E49" s="6" t="n">
+        <v>6376.2</v>
+      </c>
       <c r="F49" s="6" t="n"/>
       <c r="G49" s="6" t="n">
-        <v>7263.8</v>
+        <v>7175.8</v>
       </c>
     </row>
     <row r="50">
@@ -13626,12 +13758,16 @@
         </is>
       </c>
       <c r="B58" s="7" t="n"/>
-      <c r="C58" s="7" t="n"/>
+      <c r="C58" s="7" t="n">
+        <v>0.0961</v>
+      </c>
       <c r="D58" s="7" t="n"/>
-      <c r="E58" s="7" t="n"/>
+      <c r="E58" s="7" t="n">
+        <v>0.1155</v>
+      </c>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n">
-        <v>0.1073</v>
+        <v>0.1059</v>
       </c>
     </row>
     <row r="59">
@@ -13785,12 +13921,16 @@
         </is>
       </c>
       <c r="B67" s="7" t="n"/>
-      <c r="C67" s="7" t="n"/>
+      <c r="C67" s="7" t="n">
+        <v>0.2884</v>
+      </c>
       <c r="D67" s="7" t="n"/>
-      <c r="E67" s="7" t="n"/>
+      <c r="E67" s="7" t="n">
+        <v>0.2706</v>
+      </c>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n">
-        <v>0.2405</v>
+        <v>0.243</v>
       </c>
     </row>
     <row r="68">

--- a/銀行債券_完整報表.xlsx
+++ b/銀行債券_完整報表.xlsx
@@ -9738,7 +9738,9 @@
       <c r="B3" s="4" t="n">
         <v>1316</v>
       </c>
-      <c r="C3" s="4" t="inlineStr"/>
+      <c r="C3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="D3" s="4" t="inlineStr"/>
       <c r="E3" s="4" t="n">
         <v>464</v>
@@ -9760,7 +9762,9 @@
       <c r="L3" s="4" t="n">
         <v>902</v>
       </c>
-      <c r="M3" s="4" t="inlineStr"/>
+      <c r="M3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="N3" s="4" t="n">
         <v>1817</v>
       </c>
@@ -9786,7 +9790,9 @@
       <c r="V3" s="4" t="n">
         <v>1516</v>
       </c>
-      <c r="W3" s="4" t="inlineStr"/>
+      <c r="W3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="X3" s="4" t="n">
         <v>1008</v>
       </c>
@@ -9814,7 +9820,9 @@
       <c r="AF3" s="4" t="n">
         <v>2099</v>
       </c>
-      <c r="AG3" s="4" t="inlineStr"/>
+      <c r="AG3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AH3" s="4" t="n">
         <v>1334</v>
       </c>
@@ -9842,7 +9850,9 @@
       <c r="AP3" s="4" t="n">
         <v>2918</v>
       </c>
-      <c r="AQ3" s="4" t="inlineStr"/>
+      <c r="AQ3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AR3" s="4" t="n">
         <v>1005</v>
       </c>
@@ -9870,7 +9880,9 @@
       <c r="AZ3" s="4" t="n">
         <v>1853</v>
       </c>
-      <c r="BA3" s="4" t="inlineStr"/>
+      <c r="BA3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="BB3" s="4" t="n">
         <v>1356</v>
       </c>
@@ -9915,7 +9927,9 @@
       <c r="B4" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="D4" s="4" t="inlineStr"/>
       <c r="E4" s="4" t="n">
         <v>138</v>
@@ -9937,7 +9951,9 @@
       <c r="L4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="N4" s="4" t="n">
         <v>239</v>
       </c>
@@ -9963,7 +9979,9 @@
       <c r="V4" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="W4" s="4" t="inlineStr"/>
+      <c r="W4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="X4" s="4" t="n">
         <v>26</v>
       </c>
@@ -9991,7 +10009,9 @@
       <c r="AF4" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG4" s="4" t="inlineStr"/>
+      <c r="AG4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AH4" s="4" t="n">
         <v>6</v>
       </c>
@@ -10019,7 +10039,9 @@
       <c r="AP4" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="AQ4" s="4" t="inlineStr"/>
+      <c r="AQ4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AR4" s="4" t="n">
         <v>29</v>
       </c>
@@ -10047,7 +10069,9 @@
       <c r="AZ4" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="BA4" s="4" t="inlineStr"/>
+      <c r="BA4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="BB4" s="4" t="n">
         <v>146</v>
       </c>
@@ -10092,7 +10116,9 @@
       <c r="B5" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="4" t="n">
         <v>207</v>
@@ -10114,7 +10140,9 @@
       <c r="L5" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="M5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="N5" s="4" t="n">
         <v>136</v>
       </c>
@@ -10140,7 +10168,9 @@
       <c r="V5" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="W5" s="4" t="inlineStr"/>
+      <c r="W5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="X5" s="4" t="n">
         <v>192</v>
       </c>
@@ -10168,7 +10198,9 @@
       <c r="AF5" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="AG5" s="4" t="inlineStr"/>
+      <c r="AG5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AH5" s="4" t="n">
         <v>203</v>
       </c>
@@ -10196,7 +10228,9 @@
       <c r="AP5" s="4" t="n">
         <v>141</v>
       </c>
-      <c r="AQ5" s="4" t="inlineStr"/>
+      <c r="AQ5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AR5" s="4" t="n">
         <v>80</v>
       </c>
@@ -10224,7 +10258,9 @@
       <c r="AZ5" s="4" t="n">
         <v>114</v>
       </c>
-      <c r="BA5" s="4" t="inlineStr"/>
+      <c r="BA5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="BB5" s="4" t="n">
         <v>259</v>
       </c>
@@ -10269,7 +10305,9 @@
       <c r="B6" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="C6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="D6" s="4" t="inlineStr"/>
       <c r="E6" s="4" t="n">
         <v>86</v>
@@ -10291,7 +10329,9 @@
       <c r="L6" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="M6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="N6" s="4" t="n">
         <v>234</v>
       </c>
@@ -10317,7 +10357,9 @@
       <c r="V6" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="W6" s="4" t="inlineStr"/>
+      <c r="W6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="X6" s="4" t="n">
         <v>378</v>
       </c>
@@ -10345,7 +10387,9 @@
       <c r="AF6" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="AG6" s="4" t="inlineStr"/>
+      <c r="AG6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AH6" s="4" t="n">
         <v>724</v>
       </c>
@@ -10373,7 +10417,9 @@
       <c r="AP6" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AQ6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AR6" s="4" t="n">
         <v>448</v>
       </c>
@@ -10387,7 +10433,7 @@
         <v>14</v>
       </c>
       <c r="AV6" s="4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AW6" s="4" t="n">
         <v>228</v>
@@ -10401,7 +10447,9 @@
       <c r="AZ6" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="BA6" s="4" t="inlineStr"/>
+      <c r="BA6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="BB6" s="4" t="n">
         <v>356</v>
       </c>
@@ -10446,7 +10494,9 @@
       <c r="B7" s="4" t="n">
         <v>445</v>
       </c>
-      <c r="C7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="n">
+        <v>732</v>
+      </c>
       <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="4" t="n">
         <v>111</v>
@@ -10456,7 +10506,7 @@
         <v>541</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>709</v>
@@ -10468,7 +10518,9 @@
       <c r="L7" s="4" t="n">
         <v>367</v>
       </c>
-      <c r="M7" s="4" t="inlineStr"/>
+      <c r="M7" s="4" t="n">
+        <v>822</v>
+      </c>
       <c r="N7" s="4" t="n">
         <v>416</v>
       </c>
@@ -10480,7 +10532,7 @@
         <v>330</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>812</v>
+        <v>822</v>
       </c>
       <c r="S7" s="4" t="n">
         <v>368</v>
@@ -10494,7 +10546,9 @@
       <c r="V7" s="4" t="n">
         <v>239</v>
       </c>
-      <c r="W7" s="4" t="inlineStr"/>
+      <c r="W7" s="4" t="n">
+        <v>878</v>
+      </c>
       <c r="X7" s="4" t="n">
         <v>691</v>
       </c>
@@ -10508,7 +10562,7 @@
         <v>185</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>802</v>
+        <v>854</v>
       </c>
       <c r="AC7" s="4" t="n">
         <v>741</v>
@@ -10522,7 +10576,9 @@
       <c r="AF7" s="4" t="n">
         <v>616</v>
       </c>
-      <c r="AG7" s="4" t="inlineStr"/>
+      <c r="AG7" s="4" t="n">
+        <v>855</v>
+      </c>
       <c r="AH7" s="4" t="n">
         <v>792</v>
       </c>
@@ -10536,7 +10592,7 @@
         <v>633</v>
       </c>
       <c r="AL7" s="4" t="n">
-        <v>720</v>
+        <v>763</v>
       </c>
       <c r="AM7" s="4" t="n">
         <v>882</v>
@@ -10550,7 +10606,9 @@
       <c r="AP7" s="4" t="n">
         <v>615</v>
       </c>
-      <c r="AQ7" s="4" t="inlineStr"/>
+      <c r="AQ7" s="4" t="n">
+        <v>795</v>
+      </c>
       <c r="AR7" s="4" t="n">
         <v>1137</v>
       </c>
@@ -10564,7 +10622,7 @@
         <v>938</v>
       </c>
       <c r="AV7" s="4" t="n">
-        <v>873</v>
+        <v>927</v>
       </c>
       <c r="AW7" s="4" t="n">
         <v>1469</v>
@@ -10578,7 +10636,9 @@
       <c r="AZ7" s="4" t="n">
         <v>1341</v>
       </c>
-      <c r="BA7" s="4" t="inlineStr"/>
+      <c r="BA7" s="4" t="n">
+        <v>752</v>
+      </c>
       <c r="BB7" s="4" t="n">
         <v>1564</v>
       </c>
@@ -10592,7 +10652,7 @@
         <v>1464</v>
       </c>
       <c r="BF7" s="4" t="n">
-        <v>789</v>
+        <v>818</v>
       </c>
       <c r="BG7" s="4" t="n">
         <v>1668</v>
@@ -10623,7 +10683,9 @@
       <c r="B8" s="4" t="n">
         <v>101</v>
       </c>
-      <c r="C8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="n">
+        <v>1314</v>
+      </c>
       <c r="D8" s="4" t="inlineStr"/>
       <c r="E8" s="4" t="n">
         <v>297</v>
@@ -10633,7 +10695,7 @@
         <v>176</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1392</v>
+        <v>1386</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>947</v>
@@ -10645,7 +10707,9 @@
       <c r="L8" s="4" t="n">
         <v>149</v>
       </c>
-      <c r="M8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="n">
+        <v>1407</v>
+      </c>
       <c r="N8" s="4" t="n">
         <v>1120</v>
       </c>
@@ -10657,7 +10721,7 @@
         <v>114</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="S8" s="4" t="n">
         <v>134</v>
@@ -10671,7 +10735,9 @@
       <c r="V8" s="4" t="n">
         <v>119</v>
       </c>
-      <c r="W8" s="4" t="inlineStr"/>
+      <c r="W8" s="4" t="n">
+        <v>1456</v>
+      </c>
       <c r="X8" s="4" t="n">
         <v>881</v>
       </c>
@@ -10685,7 +10751,7 @@
         <v>106</v>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>1326</v>
+        <v>1361</v>
       </c>
       <c r="AC8" s="4" t="n">
         <v>725</v>
@@ -10699,7 +10765,9 @@
       <c r="AF8" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="AG8" s="4" t="inlineStr"/>
+      <c r="AG8" s="4" t="n">
+        <v>1380</v>
+      </c>
       <c r="AH8" s="4" t="n">
         <v>832</v>
       </c>
@@ -10713,7 +10781,7 @@
         <v>50</v>
       </c>
       <c r="AL8" s="4" t="n">
-        <v>1327</v>
+        <v>1349</v>
       </c>
       <c r="AM8" s="4" t="n">
         <v>747</v>
@@ -10727,7 +10795,9 @@
       <c r="AP8" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="AQ8" s="4" t="inlineStr"/>
+      <c r="AQ8" s="4" t="n">
+        <v>1290</v>
+      </c>
       <c r="AR8" s="4" t="n">
         <v>902</v>
       </c>
@@ -10741,7 +10811,7 @@
         <v>78</v>
       </c>
       <c r="AV8" s="4" t="n">
-        <v>1172</v>
+        <v>1188</v>
       </c>
       <c r="AW8" s="4" t="n">
         <v>942</v>
@@ -10755,7 +10825,9 @@
       <c r="AZ8" s="4" t="n">
         <v>104</v>
       </c>
-      <c r="BA8" s="4" t="inlineStr"/>
+      <c r="BA8" s="4" t="n">
+        <v>1073</v>
+      </c>
       <c r="BB8" s="4" t="n">
         <v>962</v>
       </c>
@@ -10769,7 +10841,7 @@
         <v>103</v>
       </c>
       <c r="BF8" s="4" t="n">
-        <v>1051</v>
+        <v>1056</v>
       </c>
       <c r="BG8" s="4" t="n">
         <v>958</v>
@@ -10800,7 +10872,9 @@
       <c r="B9" s="4" t="n">
         <v>1445</v>
       </c>
-      <c r="C9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="n">
+        <v>894</v>
+      </c>
       <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="n">
         <v>444</v>
@@ -10810,7 +10884,7 @@
         <v>1485</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>626</v>
@@ -10822,7 +10896,9 @@
       <c r="L9" s="4" t="n">
         <v>1132</v>
       </c>
-      <c r="M9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="n">
+        <v>953</v>
+      </c>
       <c r="N9" s="4" t="n">
         <v>593</v>
       </c>
@@ -10834,7 +10910,7 @@
         <v>1080</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="S9" s="4" t="n">
         <v>168</v>
@@ -10848,7 +10924,9 @@
       <c r="V9" s="4" t="n">
         <v>1011</v>
       </c>
-      <c r="W9" s="4" t="inlineStr"/>
+      <c r="W9" s="4" t="n">
+        <v>1089</v>
+      </c>
       <c r="X9" s="4" t="n">
         <v>377</v>
       </c>
@@ -10862,7 +10940,7 @@
         <v>979</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>915</v>
+        <v>927</v>
       </c>
       <c r="AC9" s="4" t="n">
         <v>351</v>
@@ -10876,7 +10954,9 @@
       <c r="AF9" s="4" t="n">
         <v>929</v>
       </c>
-      <c r="AG9" s="4" t="inlineStr"/>
+      <c r="AG9" s="4" t="n">
+        <v>952</v>
+      </c>
       <c r="AH9" s="4" t="n">
         <v>378</v>
       </c>
@@ -10890,7 +10970,7 @@
         <v>750</v>
       </c>
       <c r="AL9" s="4" t="n">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="AM9" s="4" t="n">
         <v>350</v>
@@ -10904,7 +10984,9 @@
       <c r="AP9" s="4" t="n">
         <v>608</v>
       </c>
-      <c r="AQ9" s="4" t="inlineStr"/>
+      <c r="AQ9" s="4" t="n">
+        <v>979</v>
+      </c>
       <c r="AR9" s="4" t="n">
         <v>350</v>
       </c>
@@ -10932,7 +11014,9 @@
       <c r="AZ9" s="4" t="n">
         <v>570</v>
       </c>
-      <c r="BA9" s="4" t="inlineStr"/>
+      <c r="BA9" s="4" t="n">
+        <v>896</v>
+      </c>
       <c r="BB9" s="4" t="n">
         <v>215</v>
       </c>
@@ -10946,7 +11030,7 @@
         <v>633</v>
       </c>
       <c r="BF9" s="4" t="n">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="BG9" s="4" t="n">
         <v>165</v>
@@ -10977,7 +11061,9 @@
       <c r="B10" s="4" t="n">
         <v>1822</v>
       </c>
-      <c r="C10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="D10" s="4" t="inlineStr"/>
       <c r="E10" s="4" t="n">
         <v>439</v>
@@ -10999,7 +11085,9 @@
       <c r="L10" s="4" t="n">
         <v>1902</v>
       </c>
-      <c r="M10" s="4" t="inlineStr"/>
+      <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="N10" s="4" t="n">
         <v>288</v>
       </c>
@@ -11025,7 +11113,9 @@
       <c r="V10" s="4" t="n">
         <v>2151</v>
       </c>
-      <c r="W10" s="4" t="inlineStr"/>
+      <c r="W10" s="4" t="n">
+        <v>129</v>
+      </c>
       <c r="X10" s="4" t="n">
         <v>421</v>
       </c>
@@ -11053,7 +11143,9 @@
       <c r="AF10" s="4" t="n">
         <v>2749</v>
       </c>
-      <c r="AG10" s="4" t="inlineStr"/>
+      <c r="AG10" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AH10" s="4" t="n">
         <v>498</v>
       </c>
@@ -11081,7 +11173,9 @@
       <c r="AP10" s="4" t="n">
         <v>2813</v>
       </c>
-      <c r="AQ10" s="4" t="inlineStr"/>
+      <c r="AQ10" s="4" t="n">
+        <v>286</v>
+      </c>
       <c r="AR10" s="4" t="n">
         <v>444</v>
       </c>
@@ -11109,7 +11203,9 @@
       <c r="AZ10" s="4" t="n">
         <v>2438</v>
       </c>
-      <c r="BA10" s="4" t="inlineStr"/>
+      <c r="BA10" s="4" t="n">
+        <v>335</v>
+      </c>
       <c r="BB10" s="4" t="n">
         <v>446</v>
       </c>
@@ -11154,7 +11250,9 @@
       <c r="B11" s="4" t="n">
         <v>586</v>
       </c>
-      <c r="C11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="n">
         <v>1796</v>
@@ -11176,7 +11274,9 @@
       <c r="L11" s="4" t="n">
         <v>665</v>
       </c>
-      <c r="M11" s="4" t="inlineStr"/>
+      <c r="M11" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="N11" s="4" t="n">
         <v>137</v>
       </c>
@@ -11202,7 +11302,9 @@
       <c r="V11" s="4" t="n">
         <v>755</v>
       </c>
-      <c r="W11" s="4" t="inlineStr"/>
+      <c r="W11" s="4" t="n">
+        <v>50</v>
+      </c>
       <c r="X11" s="4" t="n">
         <v>166</v>
       </c>
@@ -11230,7 +11332,9 @@
       <c r="AF11" s="4" t="n">
         <v>797</v>
       </c>
-      <c r="AG11" s="4" t="inlineStr"/>
+      <c r="AG11" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AH11" s="4" t="n">
         <v>271</v>
       </c>
@@ -11258,7 +11362,9 @@
       <c r="AP11" s="4" t="n">
         <v>796</v>
       </c>
-      <c r="AQ11" s="4" t="inlineStr"/>
+      <c r="AQ11" s="4" t="n">
+        <v>103</v>
+      </c>
       <c r="AR11" s="4" t="n">
         <v>292</v>
       </c>
@@ -11286,7 +11392,9 @@
       <c r="AZ11" s="4" t="n">
         <v>1047</v>
       </c>
-      <c r="BA11" s="4" t="inlineStr"/>
+      <c r="BA11" s="4" t="n">
+        <v>97</v>
+      </c>
       <c r="BB11" s="4" t="n">
         <v>263</v>
       </c>
@@ -11331,7 +11439,9 @@
       <c r="B12" s="4" t="n">
         <v>162</v>
       </c>
-      <c r="C12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="D12" s="4" t="inlineStr"/>
       <c r="E12" s="4" t="n">
         <v>898</v>
@@ -11353,7 +11463,9 @@
       <c r="L12" s="4" t="n">
         <v>267</v>
       </c>
-      <c r="M12" s="4" t="inlineStr"/>
+      <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="N12" s="4" t="n">
         <v>178</v>
       </c>
@@ -11379,7 +11491,9 @@
       <c r="V12" s="4" t="n">
         <v>282</v>
       </c>
-      <c r="W12" s="4" t="inlineStr"/>
+      <c r="W12" s="4" t="n">
+        <v>318</v>
+      </c>
       <c r="X12" s="4" t="n">
         <v>484</v>
       </c>
@@ -11407,7 +11521,9 @@
       <c r="AF12" s="4" t="n">
         <v>547</v>
       </c>
-      <c r="AG12" s="4" t="inlineStr"/>
+      <c r="AG12" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AH12" s="4" t="n">
         <v>530</v>
       </c>
@@ -11435,7 +11551,9 @@
       <c r="AP12" s="4" t="n">
         <v>676</v>
       </c>
-      <c r="AQ12" s="4" t="inlineStr"/>
+      <c r="AQ12" s="4" t="n">
+        <v>236</v>
+      </c>
       <c r="AR12" s="4" t="n">
         <v>1052</v>
       </c>
@@ -11449,7 +11567,7 @@
         <v>671</v>
       </c>
       <c r="AV12" s="4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AW12" s="4" t="n">
         <v>924</v>
@@ -11463,7 +11581,9 @@
       <c r="AZ12" s="4" t="n">
         <v>626</v>
       </c>
-      <c r="BA12" s="4" t="inlineStr"/>
+      <c r="BA12" s="4" t="n">
+        <v>176</v>
+      </c>
       <c r="BB12" s="4" t="n">
         <v>666</v>
       </c>
@@ -11607,17 +11727,23 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="6" t="n">
+        <v>3956.6</v>
+      </c>
       <c r="C4" s="6" t="n">
-        <v>9969.4</v>
-      </c>
-      <c r="D4" s="6" t="n"/>
+        <v>10145.2</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>10007.5</v>
+      </c>
       <c r="E4" s="6" t="n">
-        <v>10385.3</v>
-      </c>
-      <c r="F4" s="6" t="n"/>
+        <v>10578.3</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>9022.6</v>
+      </c>
       <c r="G4" s="6" t="n">
-        <v>11020.3</v>
+        <v>11138.7</v>
       </c>
     </row>
     <row r="5">
@@ -11770,17 +11896,23 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n"/>
+      <c r="B13" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="C13" s="6" t="n">
-        <v>290.9</v>
-      </c>
-      <c r="D13" s="6" t="n"/>
+        <v>290.5</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="E13" s="6" t="n">
-        <v>317.8</v>
-      </c>
-      <c r="F13" s="6" t="n"/>
+        <v>317.3</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="G13" s="6" t="n">
-        <v>424.9</v>
+        <v>424.5</v>
       </c>
     </row>
     <row r="14">
@@ -11933,17 +12065,23 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
+      <c r="B22" s="6" t="n">
+        <v>3956.6</v>
+      </c>
       <c r="C22" s="6" t="n">
-        <v>3579.9</v>
-      </c>
-      <c r="D22" s="6" t="n"/>
+        <v>3755.5</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>3822.3</v>
+      </c>
       <c r="E22" s="6" t="n">
-        <v>3636.9</v>
-      </c>
-      <c r="F22" s="6" t="n"/>
+        <v>3829.9</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>3347.8</v>
+      </c>
       <c r="G22" s="6" t="n">
-        <v>3370.1</v>
+        <v>3488.3</v>
       </c>
     </row>
     <row r="23">
@@ -12096,17 +12234,23 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n"/>
+      <c r="B31" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="C31" s="6" t="n">
-        <v>6098.6</v>
-      </c>
-      <c r="D31" s="6" t="n"/>
+        <v>6099.1</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>6185.2</v>
+      </c>
       <c r="E31" s="6" t="n">
-        <v>6430.6</v>
-      </c>
-      <c r="F31" s="6" t="n"/>
+        <v>6431.1</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>5674.8</v>
+      </c>
       <c r="G31" s="6" t="n">
-        <v>7225.3</v>
+        <v>7225.9</v>
       </c>
     </row>
     <row r="32">
@@ -12259,17 +12403,23 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B40" s="7" t="n"/>
+      <c r="B40" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="C40" s="7" t="n">
-        <v>0.0292</v>
-      </c>
-      <c r="D40" s="7" t="n"/>
+        <v>0.0286</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="7" t="n">
-        <v>0.0306</v>
-      </c>
-      <c r="F40" s="7" t="n"/>
+        <v>0.03</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="G40" s="7" t="n">
-        <v>0.0386</v>
+        <v>0.0381</v>
       </c>
     </row>
     <row r="41">
@@ -12422,17 +12572,23 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B49" s="7" t="n"/>
+      <c r="B49" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="C49" s="7" t="n">
-        <v>0.3591</v>
-      </c>
-      <c r="D49" s="7" t="n"/>
+        <v>0.3702</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>0.3819</v>
+      </c>
       <c r="E49" s="7" t="n">
-        <v>0.3502</v>
-      </c>
-      <c r="F49" s="7" t="n"/>
+        <v>0.3621</v>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>0.371</v>
+      </c>
       <c r="G49" s="7" t="n">
-        <v>0.3058</v>
+        <v>0.3132</v>
       </c>
     </row>
     <row r="50">
@@ -12585,17 +12741,23 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B58" s="7" t="n"/>
+      <c r="B58" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="C58" s="7" t="n">
-        <v>0.6117</v>
-      </c>
-      <c r="D58" s="7" t="n"/>
+        <v>0.6012</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>0.6181</v>
+      </c>
       <c r="E58" s="7" t="n">
-        <v>0.6192</v>
-      </c>
-      <c r="F58" s="7" t="n"/>
+        <v>0.6079</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>0.629</v>
+      </c>
       <c r="G58" s="7" t="n">
-        <v>0.6556</v>
+        <v>0.6487000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -12779,17 +12941,23 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="6" t="n">
+        <v>3956.6</v>
+      </c>
       <c r="C4" s="6" t="n">
-        <v>9969.4</v>
-      </c>
-      <c r="D4" s="6" t="n"/>
+        <v>10145.2</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>10007.5</v>
+      </c>
       <c r="E4" s="6" t="n">
-        <v>10385.3</v>
-      </c>
-      <c r="F4" s="6" t="n"/>
+        <v>10578.3</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>9022.6</v>
+      </c>
       <c r="G4" s="6" t="n">
-        <v>11020.3</v>
+        <v>11138.7</v>
       </c>
     </row>
     <row r="5">
@@ -12942,17 +13110,23 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n"/>
+      <c r="B13" s="6" t="n">
+        <v>854.7</v>
+      </c>
       <c r="C13" s="6" t="n">
-        <v>957.6</v>
-      </c>
-      <c r="D13" s="6" t="n"/>
+        <v>1000.1</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1080.4</v>
+      </c>
       <c r="E13" s="6" t="n">
-        <v>1199.3</v>
-      </c>
-      <c r="F13" s="6" t="n"/>
+        <v>1253.1</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1086.7</v>
+      </c>
       <c r="G13" s="6" t="n">
-        <v>1167.1</v>
+        <v>1195.7</v>
       </c>
     </row>
     <row r="14">
@@ -13105,17 +13279,23 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
+      <c r="B22" s="6" t="n">
+        <v>2332</v>
+      </c>
       <c r="C22" s="6" t="n">
-        <v>2874.9</v>
-      </c>
-      <c r="D22" s="6" t="n"/>
+        <v>2901.9</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>2607.9</v>
+      </c>
       <c r="E22" s="6" t="n">
-        <v>2809.8</v>
-      </c>
-      <c r="F22" s="6" t="n"/>
+        <v>2825.4</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>2242.5</v>
+      </c>
       <c r="G22" s="6" t="n">
-        <v>2677.4</v>
+        <v>2679.2</v>
       </c>
     </row>
     <row r="23">
@@ -13268,17 +13448,23 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n"/>
+      <c r="B31" s="6" t="n">
+        <v>952.1</v>
+      </c>
       <c r="C31" s="6" t="n">
-        <v>1227.3</v>
-      </c>
-      <c r="D31" s="6" t="n"/>
+        <v>1231.5</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>1214.4</v>
+      </c>
       <c r="E31" s="6" t="n">
-        <v>1290</v>
-      </c>
-      <c r="F31" s="6" t="n"/>
+        <v>1289.7</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>1072</v>
+      </c>
       <c r="G31" s="6" t="n">
-        <v>1218.9</v>
+        <v>1215.4</v>
       </c>
     </row>
     <row r="32">
@@ -13431,17 +13617,23 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B40" s="6" t="n"/>
+      <c r="B40" s="6" t="n">
+        <v>1379.8</v>
+      </c>
       <c r="C40" s="6" t="n">
-        <v>1647.6</v>
-      </c>
-      <c r="D40" s="6" t="n"/>
+        <v>1670.4</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>1393.5</v>
+      </c>
       <c r="E40" s="6" t="n">
-        <v>1519.8</v>
-      </c>
-      <c r="F40" s="6" t="n"/>
+        <v>1535.7</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>1170.5</v>
+      </c>
       <c r="G40" s="6" t="n">
-        <v>1458.5</v>
+        <v>1463.7</v>
       </c>
     </row>
     <row r="41">
@@ -13594,17 +13786,23 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B49" s="6" t="n"/>
+      <c r="B49" s="6" t="n">
+        <v>769.9</v>
+      </c>
       <c r="C49" s="6" t="n">
-        <v>6136.9</v>
-      </c>
-      <c r="D49" s="6" t="n"/>
+        <v>6243.1</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>6319.3</v>
+      </c>
       <c r="E49" s="6" t="n">
-        <v>6376.2</v>
-      </c>
-      <c r="F49" s="6" t="n"/>
+        <v>6499.8</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>5693.4</v>
+      </c>
       <c r="G49" s="6" t="n">
-        <v>7175.8</v>
+        <v>7263.8</v>
       </c>
     </row>
     <row r="50">
@@ -13757,17 +13955,23 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B58" s="7" t="n"/>
+      <c r="B58" s="7" t="n">
+        <v>0.216</v>
+      </c>
       <c r="C58" s="7" t="n">
-        <v>0.0961</v>
-      </c>
-      <c r="D58" s="7" t="n"/>
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>0.108</v>
+      </c>
       <c r="E58" s="7" t="n">
-        <v>0.1155</v>
-      </c>
-      <c r="F58" s="7" t="n"/>
+        <v>0.1185</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>0.1204</v>
+      </c>
       <c r="G58" s="7" t="n">
-        <v>0.1059</v>
+        <v>0.1073</v>
       </c>
     </row>
     <row r="59">
@@ -13920,17 +14124,23 @@
           <t>兆豐</t>
         </is>
       </c>
-      <c r="B67" s="7" t="n"/>
+      <c r="B67" s="7" t="n">
+        <v>0.5894</v>
+      </c>
       <c r="C67" s="7" t="n">
-        <v>0.2884</v>
-      </c>
-      <c r="D67" s="7" t="n"/>
+        <v>0.286</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>0.2606</v>
+      </c>
       <c r="E67" s="7" t="n">
-        <v>0.2706</v>
-      </c>
-      <c r="F67" s="7" t="n"/>
+        <v>0.2671</v>
+      </c>
+      <c r="F67" s="7" t="n">
+        <v>0.2485</v>
+      </c>
       <c r="G67" s="7" t="n">
-        <v>0.243</v>
+        <v>0.2405</v>
       </c>
     </row>
     <row r="68">

--- a/銀行債券_完整報表.xlsx
+++ b/銀行債券_完整報表.xlsx
@@ -10535,7 +10535,7 @@
         <v>822</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>368</v>
+        <v>620</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>1</v>
@@ -10724,7 +10724,7 @@
         <v>1388</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>134</v>
+        <v>959</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>65</v>
@@ -10913,7 +10913,7 @@
         <v>921</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>168</v>
+        <v>615</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>0</v>

--- a/銀行債券_完整報表.xlsx
+++ b/銀行債券_完整報表.xlsx
@@ -9928,7 +9928,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D4" s="4" t="inlineStr"/>
       <c r="E4" s="4" t="n">
@@ -9952,7 +9952,7 @@
         <v>3</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N4" s="4" t="n">
         <v>239</v>
@@ -9980,7 +9980,7 @@
         <v>5</v>
       </c>
       <c r="W4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" s="4" t="n">
         <v>26</v>
@@ -10010,7 +10010,7 @@
         <v>15</v>
       </c>
       <c r="AG4" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH4" s="4" t="n">
         <v>6</v>
@@ -10040,7 +10040,7 @@
         <v>14</v>
       </c>
       <c r="AQ4" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR4" s="4" t="n">
         <v>29</v>
@@ -10070,7 +10070,7 @@
         <v>51</v>
       </c>
       <c r="BA4" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB4" s="4" t="n">
         <v>146</v>
@@ -10117,7 +10117,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="4" t="n">
@@ -10141,7 +10141,7 @@
         <v>14</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>136</v>
@@ -10169,7 +10169,7 @@
         <v>23</v>
       </c>
       <c r="W5" s="4" t="n">
-        <v>0</v>
+        <v>323</v>
       </c>
       <c r="X5" s="4" t="n">
         <v>192</v>
@@ -10199,7 +10199,7 @@
         <v>39</v>
       </c>
       <c r="AG5" s="4" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="AH5" s="4" t="n">
         <v>203</v>
@@ -10229,7 +10229,7 @@
         <v>141</v>
       </c>
       <c r="AQ5" s="4" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="AR5" s="4" t="n">
         <v>80</v>
@@ -10259,7 +10259,7 @@
         <v>114</v>
       </c>
       <c r="BA5" s="4" t="n">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="BB5" s="4" t="n">
         <v>259</v>
@@ -10306,7 +10306,7 @@
         <v>24</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="D6" s="4" t="inlineStr"/>
       <c r="E6" s="4" t="n">
@@ -10330,7 +10330,7 @@
         <v>6</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>234</v>
@@ -10358,7 +10358,7 @@
         <v>6</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X6" s="4" t="n">
         <v>378</v>
@@ -10388,7 +10388,7 @@
         <v>13</v>
       </c>
       <c r="AG6" s="4" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AH6" s="4" t="n">
         <v>724</v>
@@ -10418,7 +10418,7 @@
         <v>59</v>
       </c>
       <c r="AQ6" s="4" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AR6" s="4" t="n">
         <v>448</v>
@@ -10448,7 +10448,7 @@
         <v>55</v>
       </c>
       <c r="BA6" s="4" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="BB6" s="4" t="n">
         <v>356</v>
@@ -11062,7 +11062,7 @@
         <v>1822</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D10" s="4" t="inlineStr"/>
       <c r="E10" s="4" t="n">
@@ -11086,7 +11086,7 @@
         <v>1902</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>288</v>
@@ -11144,7 +11144,7 @@
         <v>2749</v>
       </c>
       <c r="AG10" s="4" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="AH10" s="4" t="n">
         <v>498</v>
@@ -11251,7 +11251,7 @@
         <v>586</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="n">
@@ -11275,7 +11275,7 @@
         <v>665</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>137</v>
@@ -11333,7 +11333,7 @@
         <v>797</v>
       </c>
       <c r="AG11" s="4" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AH11" s="4" t="n">
         <v>271</v>
@@ -11440,7 +11440,7 @@
         <v>162</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="D12" s="4" t="inlineStr"/>
       <c r="E12" s="4" t="n">
@@ -11464,7 +11464,7 @@
         <v>267</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0</v>
+        <v>309</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>178</v>
@@ -11522,7 +11522,7 @@
         <v>547</v>
       </c>
       <c r="AG12" s="4" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="AH12" s="4" t="n">
         <v>530</v>
@@ -11728,19 +11728,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>3956.6</v>
+        <v>10694</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>10145.2</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>10007.5</v>
+        <v>10235.1</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>10578.3</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>9022.6</v>
+        <v>9337.5</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>11138.7</v>
@@ -11897,19 +11897,19 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0</v>
+        <v>274.9</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>290.5</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0</v>
+        <v>227.6</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>317.3</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0</v>
+        <v>314.9</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>424.5</v>
@@ -12235,7 +12235,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0</v>
+        <v>6462.5</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>6099.1</v>
@@ -12404,19 +12404,19 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0</v>
+        <v>0.0257</v>
       </c>
       <c r="C40" s="7" t="n">
         <v>0.0286</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>0</v>
+        <v>0.0222</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>0.03</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>0</v>
+        <v>0.0337</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>0.0381</v>
@@ -12573,19 +12573,19 @@
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>1</v>
+        <v>0.37</v>
       </c>
       <c r="C49" s="7" t="n">
         <v>0.3702</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0.3819</v>
+        <v>0.3734</v>
       </c>
       <c r="E49" s="7" t="n">
         <v>0.3621</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>0.371</v>
+        <v>0.3585</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>0.3132</v>
@@ -12742,19 +12742,19 @@
         </is>
       </c>
       <c r="B58" s="7" t="n">
-        <v>0</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="C58" s="7" t="n">
         <v>0.6012</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>0.6181</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="E58" s="7" t="n">
         <v>0.6079</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>0.629</v>
+        <v>0.6077</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>0.6487000000000001</v>
@@ -12942,19 +12942,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>3956.6</v>
+        <v>10694</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>10145.2</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>10007.5</v>
+        <v>10235.1</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>10578.3</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>9022.6</v>
+        <v>9337.5</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>11138.7</v>
@@ -13111,19 +13111,19 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>854.7</v>
+        <v>1085.9</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>1000.1</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1080.4</v>
+        <v>1082</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>1253.1</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>1086.7</v>
+        <v>1091.1</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>1195.7</v>
@@ -13280,19 +13280,19 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>2332</v>
+        <v>2942.2</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>2901.9</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2607.9</v>
+        <v>2833.7</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>2825.4</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>2242.5</v>
+        <v>2553</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>2679.2</v>
@@ -13449,19 +13449,19 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>952.1</v>
+        <v>1242.1</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>1231.5</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>1214.4</v>
+        <v>1287.4</v>
       </c>
       <c r="E31" s="6" t="n">
         <v>1289.7</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1072</v>
+        <v>1156.2</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>1215.4</v>
@@ -13618,19 +13618,19 @@
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>1379.8</v>
+        <v>1700.1</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>1670.4</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>1393.5</v>
+        <v>1546.3</v>
       </c>
       <c r="E40" s="6" t="n">
         <v>1535.7</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>1170.5</v>
+        <v>1396.8</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>1463.7</v>
@@ -13787,19 +13787,19 @@
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>769.9</v>
+        <v>6665.9</v>
       </c>
       <c r="C49" s="6" t="n">
         <v>6243.1</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>6319.3</v>
+        <v>6319.4</v>
       </c>
       <c r="E49" s="6" t="n">
         <v>6499.8</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>5693.4</v>
+        <v>5693.5</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>7263.8</v>
@@ -13956,19 +13956,19 @@
         </is>
       </c>
       <c r="B58" s="7" t="n">
-        <v>0.216</v>
+        <v>0.1015</v>
       </c>
       <c r="C58" s="7" t="n">
         <v>0.09859999999999999</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>0.108</v>
+        <v>0.1057</v>
       </c>
       <c r="E58" s="7" t="n">
         <v>0.1185</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>0.1204</v>
+        <v>0.1168</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>0.1073</v>
@@ -14125,19 +14125,19 @@
         </is>
       </c>
       <c r="B67" s="7" t="n">
-        <v>0.5894</v>
+        <v>0.2751</v>
       </c>
       <c r="C67" s="7" t="n">
         <v>0.286</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>0.2606</v>
+        <v>0.2769</v>
       </c>
       <c r="E67" s="7" t="n">
         <v>0.2671</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>0.2485</v>
+        <v>0.2734</v>
       </c>
       <c r="G67" s="7" t="n">
         <v>0.2405</v>
